--- a/BASE_EXCEL_TEMPLATES/kr_la_air/KR_LA_AIR_2026_V00_SHIPMENTS.xlsx
+++ b/BASE_EXCEL_TEMPLATES/kr_la_air/KR_LA_AIR_2026_V00_SHIPMENTS.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ssapd\StudioProjects\백업 및 추가 자료 보관\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ssapd\StudioProjects\lkgroup_app\BASE_EXCEL_TEMPLATES\kr_la_air\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3088ADA1-C693-4FEA-9AC3-C89DA2140037}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE6551CF-C924-47F6-9A20-D6E643CD8963}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="908" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13500" yWindow="330" windowWidth="13815" windowHeight="15120" tabRatio="908" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Row data" sheetId="3" r:id="rId1"/>
@@ -22,7 +22,7 @@
     <sheet name="LKA XX" sheetId="1607" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Row data'!$H$8:$L$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Row data'!$H$8:$M$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'물품 입고 내역'!$B$5:$Q$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'시내, 지방배송'!$A$1:$F$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'LKA 01'!$A$1:$N$34</definedName>
@@ -430,7 +430,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1277" uniqueCount="902">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1340" uniqueCount="962">
   <si>
     <t>USD-KIP</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -4298,6 +4298,245 @@
   </si>
   <si>
     <t>박상용</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>전화번호</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>020 9169 2442</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>020 5623 8978</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>020 5919 4145/010 7645 7702/010 7979 ****</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>020 5903 6847</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>020 5551 9577 / 020 7760 2950</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>020 5655 7800 / 010 3010 1210</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>020 5215 1510</t>
+  </si>
+  <si>
+    <t>020 5959 1790</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>020 5906 1180</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>020 9550 5260</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>020 5987 8414</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>020 7794 7644</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>020 5243 3796 / 020 5718 8148</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>020 5965 1119 / 020 5965 1118</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>020 5947 3438</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>020 5231 3664</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>020 5680 8404</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>020 5213 8937</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>020 5809 6122</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>020 5968 0528</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>020 5648 0776</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>020 5997 7731 / 020 5526 6631</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>020 5718 0600</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>020 5801 6547</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>020 5699 1994</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>020 5468 6907</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>020 5927 0299</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>020 3456 2880</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>020 5633 4416</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>020 9171 8659</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>020 9340 9290</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>020 5813 5700</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>020 5177 1736 / 020 5286 3646</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>020 5571 9124</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>020 5665 3594 / 020 5642 8130 / 010 9866 1836 / 020 9209 0721 / 020 5552 7594</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>020 5214 7461</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>020 9638 3267</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>020 5955 8110</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>020 2927 1111</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>020 5228 4700</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>020 5999 8658</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>020 5552 0445 / 010 2602 0445</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>020 5889 2547</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>020 5885 6611</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>020 9996 0101</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>020 2251 3322</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>020 5999 6416</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>020 5913 4280 / 020 5578 0230</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>020 9911 0640 / 010 4531 8081</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>020 9865 4347</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>020 9107 9368</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>020 5424 5141 / 020 5554 2263</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>020 5849 9599</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>020 2340 3361</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>020 5847 7710 / 020 9887 7426</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>020 5862 2221</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>020 2328 9789</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>020 5697 7988</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>020 5158 7003 / 010 6338 2369</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -5147,7 +5386,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="287">
+  <cellXfs count="291">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -5691,10 +5930,61 @@
     <xf numFmtId="0" fontId="52" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="13" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="15" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="4" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -5706,61 +5996,16 @@
     <xf numFmtId="0" fontId="52" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="13" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="17" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="15" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="53" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="40" fillId="14" borderId="4" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5778,43 +6023,43 @@
     <xf numFmtId="0" fontId="40" fillId="14" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="17" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5822,9 +6067,6 @@
     </xf>
     <xf numFmtId="0" fontId="20" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="20" fillId="2" borderId="2" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5847,9 +6089,6 @@
     <xf numFmtId="14" fontId="21" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -5858,6 +6097,87 @@
     </xf>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5925,89 +6245,20 @@
     <xf numFmtId="0" fontId="63" fillId="11" borderId="14" xfId="3" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="49" fontId="31" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="12">
@@ -6126,7 +6377,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="$A$13:$F$31" spid="_x0000_s103583"/>
+                  <a14:cameraTool cellRange="$A$13:$F$31" spid="_x0000_s103584"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -6805,7 +7056,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="$A$1:$N$34" spid="_x0000_s102635"/>
+                  <a14:cameraTool cellRange="$A$1:$N$34" spid="_x0000_s102636"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -7478,7 +7729,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="$A$1:$N$34" spid="_x0000_s110640"/>
+                  <a14:cameraTool cellRange="$A$1:$N$34" spid="_x0000_s110641"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -7865,7 +8116,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="B1:Y70"/>
+  <dimension ref="B1:AB70"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.25"/>
   <cols>
     <col min="1" max="1" width="3.875" style="62" customWidth="1"/>
@@ -7876,41 +8127,45 @@
     <col min="7" max="7" width="6.125" style="62" customWidth="1"/>
     <col min="8" max="8" width="15" style="62" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9.75" style="62" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.75" style="62" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.75" style="62" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.625" style="62" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="3.625" style="80" customWidth="1"/>
-    <col min="14" max="14" width="15.5" style="80" customWidth="1"/>
-    <col min="15" max="15" width="9.875" style="80" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="26.125" style="80" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7.75" style="80" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9.75" style="80" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="15.25" style="80" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="3" style="80" customWidth="1"/>
-    <col min="21" max="21" width="34.25" style="80" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="22.5" style="80" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="7.75" style="80" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="9.75" style="80" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="37.25" style="80" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9" style="62"/>
+    <col min="10" max="10" width="9.75" style="62" customWidth="1"/>
+    <col min="11" max="11" width="7.75" style="62" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.75" style="62" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.625" style="62" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="3.625" style="80" customWidth="1"/>
+    <col min="15" max="15" width="15.5" style="80" customWidth="1"/>
+    <col min="16" max="16" width="9.875" style="80" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="26.125" style="80" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="26.125" style="80" customWidth="1"/>
+    <col min="19" max="19" width="7.75" style="80" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9.75" style="80" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="15.25" style="80" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="3" style="80" customWidth="1"/>
+    <col min="23" max="23" width="34.25" style="80" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="22.5" style="80" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="22.5" style="80" customWidth="1"/>
+    <col min="26" max="26" width="7.75" style="80" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="9.75" style="80" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="37.25" style="80" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9" style="62"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:25">
-      <c r="B1" s="217" t="s">
+    <row r="1" spans="2:28">
+      <c r="B1" s="186" t="s">
         <v>59</v>
       </c>
-      <c r="C1" s="217"/>
-      <c r="D1" s="217"/>
-      <c r="E1" s="217"/>
-      <c r="H1" s="218" t="s">
+      <c r="C1" s="186"/>
+      <c r="D1" s="186"/>
+      <c r="E1" s="186"/>
+      <c r="H1" s="187" t="s">
         <v>89</v>
       </c>
-      <c r="I1" s="218"/>
-      <c r="J1" s="218"/>
-      <c r="K1" s="218"/>
-      <c r="L1" s="218"/>
+      <c r="I1" s="187"/>
+      <c r="J1" s="187"/>
+      <c r="K1" s="187"/>
+      <c r="L1" s="187"/>
+      <c r="M1" s="187"/>
     </row>
-    <row r="2" spans="2:25">
+    <row r="2" spans="2:28">
       <c r="B2" s="63" t="s">
         <v>55</v>
       </c>
@@ -7928,8 +8183,9 @@
       <c r="J2" s="80"/>
       <c r="K2" s="80"/>
       <c r="L2" s="80"/>
+      <c r="M2" s="80"/>
     </row>
-    <row r="3" spans="2:25">
+    <row r="3" spans="2:28">
       <c r="B3" s="64" t="s">
         <v>0</v>
       </c>
@@ -7943,26 +8199,29 @@
         <f>C3+D3</f>
         <v>24000</v>
       </c>
-      <c r="H3" s="216" t="s">
+      <c r="H3" s="184" t="s">
         <v>328</v>
       </c>
-      <c r="I3" s="216"/>
-      <c r="J3" s="216"/>
-      <c r="K3" s="216"/>
-      <c r="N3" s="216" t="s">
+      <c r="I3" s="184"/>
+      <c r="J3" s="184"/>
+      <c r="K3" s="184"/>
+      <c r="L3" s="184"/>
+      <c r="O3" s="184" t="s">
         <v>204</v>
       </c>
-      <c r="O3" s="216"/>
-      <c r="P3" s="216"/>
-      <c r="Q3" s="216"/>
-      <c r="U3" s="216" t="s">
+      <c r="P3" s="184"/>
+      <c r="Q3" s="184"/>
+      <c r="R3" s="184"/>
+      <c r="S3" s="184"/>
+      <c r="W3" s="184" t="s">
         <v>815</v>
       </c>
-      <c r="V3" s="216"/>
-      <c r="W3" s="216"/>
-      <c r="X3" s="216"/>
+      <c r="X3" s="184"/>
+      <c r="Y3" s="184"/>
+      <c r="Z3" s="184"/>
+      <c r="AA3" s="184"/>
     </row>
-    <row r="4" spans="2:25">
+    <row r="4" spans="2:28">
       <c r="B4" s="67" t="s">
         <v>2</v>
       </c>
@@ -7976,33 +8235,36 @@
         <f>C4+D4</f>
         <v>34</v>
       </c>
-      <c r="H4" s="219" t="s">
+      <c r="H4" s="182" t="s">
         <v>90</v>
       </c>
-      <c r="I4" s="220"/>
-      <c r="J4" s="219" t="s">
+      <c r="I4" s="183"/>
+      <c r="J4" s="287"/>
+      <c r="K4" s="182" t="s">
         <v>91</v>
       </c>
-      <c r="K4" s="220"/>
-      <c r="L4" s="80"/>
-      <c r="N4" s="219" t="s">
+      <c r="L4" s="183"/>
+      <c r="M4" s="80"/>
+      <c r="O4" s="182" t="s">
         <v>90</v>
       </c>
-      <c r="O4" s="220"/>
-      <c r="P4" s="219" t="s">
+      <c r="P4" s="183"/>
+      <c r="Q4" s="182" t="s">
         <v>91</v>
       </c>
-      <c r="Q4" s="220"/>
-      <c r="U4" s="219" t="s">
+      <c r="R4" s="288"/>
+      <c r="S4" s="183"/>
+      <c r="W4" s="182" t="s">
         <v>90</v>
       </c>
-      <c r="V4" s="220"/>
-      <c r="W4" s="219" t="s">
+      <c r="X4" s="183"/>
+      <c r="Y4" s="287"/>
+      <c r="Z4" s="182" t="s">
         <v>91</v>
       </c>
-      <c r="X4" s="220"/>
+      <c r="AA4" s="183"/>
     </row>
-    <row r="5" spans="2:25">
+    <row r="5" spans="2:28">
       <c r="B5" s="69" t="s">
         <v>1</v>
       </c>
@@ -8022,29 +8284,25 @@
       <c r="I5" s="77" t="s">
         <v>93</v>
       </c>
-      <c r="J5" s="77" t="s">
+      <c r="J5" s="77"/>
+      <c r="K5" s="77" t="s">
         <v>92</v>
       </c>
-      <c r="K5" s="77" t="s">
+      <c r="L5" s="77" t="s">
         <v>93</v>
       </c>
-      <c r="L5" s="80"/>
-      <c r="N5" s="77" t="s">
+      <c r="M5" s="80"/>
+      <c r="O5" s="77" t="s">
         <v>92</v>
       </c>
-      <c r="O5" s="77" t="s">
+      <c r="P5" s="77" t="s">
         <v>93</v>
       </c>
-      <c r="P5" s="77" t="s">
+      <c r="Q5" s="77" t="s">
         <v>92</v>
       </c>
-      <c r="Q5" s="77" t="s">
-        <v>93</v>
-      </c>
-      <c r="U5" s="77" t="s">
-        <v>92</v>
-      </c>
-      <c r="V5" s="77" t="s">
+      <c r="R5" s="77"/>
+      <c r="S5" s="77" t="s">
         <v>93</v>
       </c>
       <c r="W5" s="77" t="s">
@@ -8053,180 +8311,208 @@
       <c r="X5" s="77" t="s">
         <v>93</v>
       </c>
+      <c r="Y5" s="77"/>
+      <c r="Z5" s="77" t="s">
+        <v>92</v>
+      </c>
+      <c r="AA5" s="77" t="s">
+        <v>93</v>
+      </c>
     </row>
-    <row r="6" spans="2:25">
+    <row r="6" spans="2:28">
       <c r="H6" s="78">
         <v>0.2</v>
       </c>
       <c r="I6" s="78">
         <v>0.3</v>
       </c>
-      <c r="J6" s="78">
+      <c r="J6" s="78"/>
+      <c r="K6" s="78">
         <v>0.05</v>
       </c>
-      <c r="K6" s="78">
+      <c r="L6" s="78">
         <v>0.1</v>
       </c>
-      <c r="L6" s="80"/>
-      <c r="N6" s="78">
+      <c r="M6" s="80"/>
+      <c r="O6" s="78">
         <v>0.2</v>
       </c>
-      <c r="O6" s="78">
+      <c r="P6" s="78">
         <v>0.3</v>
       </c>
-      <c r="P6" s="78">
+      <c r="Q6" s="78">
         <v>0.05</v>
       </c>
-      <c r="Q6" s="78">
+      <c r="R6" s="78"/>
+      <c r="S6" s="78">
         <v>0.1</v>
       </c>
-      <c r="U6" s="78" t="s">
+      <c r="W6" s="78" t="s">
         <v>95</v>
       </c>
-      <c r="V6" s="78">
+      <c r="X6" s="78">
         <v>0.2</v>
       </c>
-      <c r="W6" s="78">
+      <c r="Y6" s="78"/>
+      <c r="Z6" s="78">
         <v>0.05</v>
       </c>
-      <c r="X6" s="78">
+      <c r="AA6" s="78">
         <v>0.1</v>
       </c>
     </row>
-    <row r="7" spans="2:25">
+    <row r="7" spans="2:28">
       <c r="H7" s="80"/>
       <c r="I7" s="80"/>
       <c r="J7" s="80"/>
       <c r="K7" s="80"/>
       <c r="L7" s="80"/>
+      <c r="M7" s="80"/>
     </row>
-    <row r="8" spans="2:25">
-      <c r="B8" s="214" t="s">
+    <row r="8" spans="2:28">
+      <c r="B8" s="185" t="s">
         <v>320</v>
       </c>
-      <c r="C8" s="214"/>
-      <c r="D8" s="214"/>
-      <c r="E8" s="214"/>
+      <c r="C8" s="185"/>
+      <c r="D8" s="185"/>
+      <c r="E8" s="185"/>
       <c r="H8" s="63" t="s">
         <v>94</v>
       </c>
       <c r="I8" s="63"/>
       <c r="J8" s="63" t="s">
+        <v>902</v>
+      </c>
+      <c r="K8" s="63" t="s">
         <v>131</v>
       </c>
-      <c r="K8" s="63" t="s">
+      <c r="L8" s="63" t="s">
         <v>132</v>
       </c>
-      <c r="L8" s="63" t="s">
+      <c r="M8" s="63" t="s">
         <v>206</v>
       </c>
-      <c r="N8" s="63" t="s">
+      <c r="O8" s="63" t="s">
         <v>94</v>
       </c>
-      <c r="O8" s="63"/>
-      <c r="P8" s="63" t="s">
+      <c r="P8" s="63"/>
+      <c r="Q8" s="63" t="s">
         <v>507</v>
       </c>
-      <c r="Q8" s="63" t="s">
+      <c r="R8" s="63" t="s">
+        <v>902</v>
+      </c>
+      <c r="S8" s="63" t="s">
         <v>508</v>
       </c>
-      <c r="R8" s="63" t="s">
+      <c r="T8" s="63" t="s">
         <v>509</v>
       </c>
-      <c r="S8" s="63" t="s">
+      <c r="U8" s="63" t="s">
         <v>510</v>
       </c>
-      <c r="U8" s="63" t="s">
+      <c r="W8" s="63" t="s">
         <v>94</v>
       </c>
-      <c r="V8" s="63"/>
-      <c r="W8" s="63" t="s">
+      <c r="X8" s="63"/>
+      <c r="Y8" s="63"/>
+      <c r="Z8" s="63" t="s">
         <v>131</v>
       </c>
-      <c r="X8" s="63" t="s">
+      <c r="AA8" s="63" t="s">
         <v>132</v>
       </c>
-      <c r="Y8" s="63" t="s">
+      <c r="AB8" s="63" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="9" spans="2:25">
-      <c r="B9" s="214" t="s">
+    <row r="9" spans="2:28">
+      <c r="B9" s="185" t="s">
         <v>719</v>
       </c>
-      <c r="C9" s="214"/>
-      <c r="D9" s="214"/>
-      <c r="E9" s="214"/>
+      <c r="C9" s="185"/>
+      <c r="D9" s="185"/>
+      <c r="E9" s="185"/>
       <c r="H9" s="63" t="s">
         <v>108</v>
       </c>
       <c r="I9" s="63"/>
-      <c r="J9" s="81">
+      <c r="J9" s="63"/>
+      <c r="K9" s="81">
         <v>0.05</v>
       </c>
-      <c r="K9" s="82"/>
       <c r="L9" s="82"/>
-      <c r="N9" s="180" t="s">
+      <c r="M9" s="82"/>
+      <c r="O9" s="180" t="s">
         <v>889</v>
       </c>
-      <c r="O9" s="79" t="s">
+      <c r="P9" s="79" t="s">
         <v>191</v>
       </c>
-      <c r="P9" s="79" t="s">
+      <c r="Q9" s="79" t="s">
         <v>134</v>
       </c>
-      <c r="Q9" s="91">
+      <c r="R9" s="79"/>
+      <c r="S9" s="91">
         <v>0.05</v>
       </c>
-      <c r="R9" s="92"/>
-      <c r="S9" s="92"/>
-      <c r="U9" s="63" t="s">
+      <c r="T9" s="92"/>
+      <c r="U9" s="92"/>
+      <c r="W9" s="63" t="s">
         <v>98</v>
       </c>
-      <c r="V9" s="63" t="s">
+      <c r="X9" s="63" t="s">
         <v>99</v>
       </c>
-      <c r="W9" s="91">
+      <c r="Y9" s="63" t="s">
+        <v>941</v>
+      </c>
+      <c r="Z9" s="91">
         <v>0.05</v>
       </c>
-      <c r="X9" s="92"/>
-      <c r="Y9" s="92"/>
+      <c r="AA9" s="92"/>
+      <c r="AB9" s="92"/>
     </row>
-    <row r="10" spans="2:25">
+    <row r="10" spans="2:28">
       <c r="H10" s="63" t="s">
         <v>554</v>
       </c>
       <c r="I10" s="63"/>
-      <c r="J10" s="81">
+      <c r="J10" s="63"/>
+      <c r="K10" s="81">
         <v>0.05</v>
       </c>
-      <c r="K10" s="82"/>
       <c r="L10" s="82"/>
-      <c r="N10" s="79" t="s">
+      <c r="M10" s="82"/>
+      <c r="O10" s="79" t="s">
         <v>175</v>
       </c>
-      <c r="O10" s="79" t="s">
+      <c r="P10" s="79" t="s">
         <v>193</v>
       </c>
-      <c r="P10" s="79" t="s">
+      <c r="Q10" s="79" t="s">
         <v>136</v>
       </c>
-      <c r="Q10" s="91">
+      <c r="R10" s="79"/>
+      <c r="S10" s="91">
         <v>0.05</v>
       </c>
-      <c r="R10" s="92"/>
-      <c r="S10" s="92"/>
-      <c r="U10" s="63" t="s">
+      <c r="T10" s="92"/>
+      <c r="U10" s="92"/>
+      <c r="W10" s="63" t="s">
         <v>376</v>
       </c>
-      <c r="V10" s="63"/>
-      <c r="W10" s="91">
+      <c r="X10" s="63"/>
+      <c r="Y10" s="63" t="s">
+        <v>942</v>
+      </c>
+      <c r="Z10" s="91">
         <v>0.05</v>
       </c>
-      <c r="X10" s="92"/>
-      <c r="Y10" s="92"/>
+      <c r="AA10" s="92"/>
+      <c r="AB10" s="92"/>
     </row>
-    <row r="11" spans="2:25">
+    <row r="11" spans="2:28">
       <c r="B11" s="62" t="s">
         <v>727</v>
       </c>
@@ -8235,38 +8521,43 @@
         <v>127</v>
       </c>
       <c r="I11" s="63"/>
-      <c r="J11" s="81">
+      <c r="J11" s="63"/>
+      <c r="K11" s="81">
         <v>0.05</v>
       </c>
-      <c r="K11" s="92"/>
       <c r="L11" s="92"/>
-      <c r="N11" s="79" t="s">
+      <c r="M11" s="92"/>
+      <c r="O11" s="79" t="s">
         <v>178</v>
       </c>
-      <c r="O11" s="79" t="s">
+      <c r="P11" s="79" t="s">
         <v>195</v>
       </c>
-      <c r="P11" s="79" t="s">
+      <c r="Q11" s="79" t="s">
         <v>138</v>
       </c>
-      <c r="Q11" s="91">
+      <c r="R11" s="79"/>
+      <c r="S11" s="91">
         <v>0.05</v>
       </c>
-      <c r="R11" s="92"/>
-      <c r="S11" s="92"/>
-      <c r="U11" s="63" t="s">
+      <c r="T11" s="92"/>
+      <c r="U11" s="92"/>
+      <c r="W11" s="63" t="s">
         <v>379</v>
       </c>
-      <c r="V11" s="63" t="s">
+      <c r="X11" s="63" t="s">
         <v>380</v>
       </c>
-      <c r="W11" s="91">
+      <c r="Y11" s="63" t="s">
+        <v>943</v>
+      </c>
+      <c r="Z11" s="91">
         <v>0.05</v>
       </c>
-      <c r="X11" s="92"/>
-      <c r="Y11" s="92"/>
+      <c r="AA11" s="92"/>
+      <c r="AB11" s="92"/>
     </row>
-    <row r="12" spans="2:25">
+    <row r="12" spans="2:28">
       <c r="B12" s="62" t="s">
         <v>728</v>
       </c>
@@ -8277,70 +8568,84 @@
       <c r="I12" s="63" t="s">
         <v>480</v>
       </c>
-      <c r="J12" s="81">
+      <c r="J12" s="63"/>
+      <c r="K12" s="81">
         <v>0.05</v>
       </c>
-      <c r="K12" s="92"/>
       <c r="L12" s="92"/>
-      <c r="N12" s="149" t="s">
+      <c r="M12" s="92"/>
+      <c r="O12" s="149" t="s">
         <v>511</v>
       </c>
-      <c r="O12" s="79" t="s">
+      <c r="P12" s="79" t="s">
         <v>191</v>
       </c>
-      <c r="P12" s="79" t="s">
+      <c r="Q12" s="79" t="s">
         <v>890</v>
       </c>
-      <c r="Q12" s="91">
+      <c r="R12" s="79" t="s">
+        <v>927</v>
+      </c>
+      <c r="S12" s="91">
         <v>0.05</v>
       </c>
-      <c r="R12" s="92"/>
-      <c r="S12" s="92"/>
-      <c r="U12" s="63" t="s">
+      <c r="T12" s="92"/>
+      <c r="U12" s="92"/>
+      <c r="W12" s="63" t="s">
         <v>217</v>
       </c>
-      <c r="V12" s="63"/>
-      <c r="W12" s="91">
+      <c r="X12" s="63"/>
+      <c r="Y12" s="63" t="s">
+        <v>944</v>
+      </c>
+      <c r="Z12" s="91">
         <v>0.05</v>
       </c>
-      <c r="X12" s="92"/>
-      <c r="Y12" s="92"/>
+      <c r="AA12" s="92"/>
+      <c r="AB12" s="92"/>
     </row>
-    <row r="13" spans="2:25">
+    <row r="13" spans="2:28">
       <c r="H13" s="63" t="s">
         <v>120</v>
       </c>
       <c r="I13" s="63"/>
-      <c r="J13" s="81">
+      <c r="J13" s="63"/>
+      <c r="K13" s="81">
         <v>0.05</v>
       </c>
-      <c r="K13" s="92"/>
       <c r="L13" s="92"/>
-      <c r="N13" s="149" t="s">
+      <c r="M13" s="92"/>
+      <c r="O13" s="149" t="s">
         <v>493</v>
       </c>
-      <c r="O13" s="79" t="s">
+      <c r="P13" s="79" t="s">
         <v>191</v>
       </c>
-      <c r="P13" s="79" t="s">
+      <c r="Q13" s="79" t="s">
         <v>140</v>
       </c>
-      <c r="Q13" s="91">
+      <c r="R13" s="79" t="s">
+        <v>928</v>
+      </c>
+      <c r="S13" s="91">
         <v>0.05</v>
       </c>
-      <c r="R13" s="92"/>
-      <c r="S13" s="92"/>
-      <c r="U13" s="63" t="s">
+      <c r="T13" s="92"/>
+      <c r="U13" s="92"/>
+      <c r="W13" s="63" t="s">
         <v>133</v>
       </c>
-      <c r="V13" s="63"/>
-      <c r="W13" s="91">
+      <c r="X13" s="63"/>
+      <c r="Y13" s="63" t="s">
+        <v>945</v>
+      </c>
+      <c r="Z13" s="91">
         <v>0.3</v>
       </c>
-      <c r="X13" s="92"/>
-      <c r="Y13" s="92"/>
+      <c r="AA13" s="92"/>
+      <c r="AB13" s="92"/>
     </row>
-    <row r="14" spans="2:25">
+    <row r="14" spans="2:28">
       <c r="B14" s="62" t="s">
         <v>369</v>
       </c>
@@ -8348,38 +8653,43 @@
         <v>473</v>
       </c>
       <c r="I14" s="63"/>
-      <c r="J14" s="81">
+      <c r="J14" s="63"/>
+      <c r="K14" s="81">
         <v>0.05</v>
       </c>
-      <c r="K14" s="82"/>
       <c r="L14" s="82"/>
-      <c r="N14" s="149" t="s">
+      <c r="M14" s="82"/>
+      <c r="O14" s="149" t="s">
         <v>512</v>
       </c>
-      <c r="O14" s="149" t="s">
+      <c r="P14" s="149" t="s">
         <v>513</v>
       </c>
-      <c r="P14" s="79" t="s">
+      <c r="Q14" s="79" t="s">
         <v>514</v>
       </c>
-      <c r="Q14" s="91">
+      <c r="R14" s="149"/>
+      <c r="S14" s="91">
         <v>0.05</v>
       </c>
-      <c r="R14" s="92"/>
-      <c r="S14" s="92"/>
-      <c r="U14" s="63" t="s">
+      <c r="T14" s="92"/>
+      <c r="U14" s="92"/>
+      <c r="W14" s="63" t="s">
         <v>96</v>
       </c>
-      <c r="V14" s="63" t="s">
+      <c r="X14" s="63" t="s">
         <v>97</v>
       </c>
-      <c r="W14" s="91">
+      <c r="Y14" s="63" t="s">
+        <v>946</v>
+      </c>
+      <c r="Z14" s="91">
         <v>0.05</v>
       </c>
-      <c r="X14" s="92"/>
-      <c r="Y14" s="92"/>
+      <c r="AA14" s="92"/>
+      <c r="AB14" s="92"/>
     </row>
-    <row r="15" spans="2:25">
+    <row r="15" spans="2:28">
       <c r="B15" s="62" t="s">
         <v>23</v>
       </c>
@@ -8391,36 +8701,41 @@
         <v>126</v>
       </c>
       <c r="I15" s="63"/>
-      <c r="J15" s="81">
+      <c r="J15" s="63"/>
+      <c r="K15" s="81">
         <v>0.05</v>
       </c>
-      <c r="K15" s="92"/>
       <c r="L15" s="92"/>
-      <c r="N15" s="79" t="s">
+      <c r="M15" s="92"/>
+      <c r="O15" s="79" t="s">
         <v>179</v>
       </c>
-      <c r="O15" s="79" t="s">
+      <c r="P15" s="79" t="s">
         <v>191</v>
       </c>
-      <c r="P15" s="79" t="s">
+      <c r="Q15" s="79" t="s">
         <v>139</v>
       </c>
-      <c r="Q15" s="91">
+      <c r="R15" s="79"/>
+      <c r="S15" s="91">
         <v>0.05</v>
       </c>
-      <c r="R15" s="92"/>
-      <c r="S15" s="92"/>
-      <c r="U15" s="63" t="s">
+      <c r="T15" s="92"/>
+      <c r="U15" s="92"/>
+      <c r="W15" s="63" t="s">
         <v>321</v>
       </c>
-      <c r="V15" s="63"/>
-      <c r="W15" s="91">
+      <c r="X15" s="63"/>
+      <c r="Y15" s="63" t="s">
+        <v>947</v>
+      </c>
+      <c r="Z15" s="91">
         <v>0.05</v>
       </c>
-      <c r="X15" s="92"/>
-      <c r="Y15" s="92"/>
+      <c r="AA15" s="92"/>
+      <c r="AB15" s="92"/>
     </row>
-    <row r="16" spans="2:25">
+    <row r="16" spans="2:28">
       <c r="B16" s="62" t="s">
         <v>24</v>
       </c>
@@ -8434,177 +8749,206 @@
         <v>110</v>
       </c>
       <c r="I16" s="63"/>
-      <c r="J16" s="81">
+      <c r="J16" s="63"/>
+      <c r="K16" s="81">
         <v>0.05</v>
       </c>
-      <c r="K16" s="92"/>
       <c r="L16" s="92"/>
-      <c r="N16" s="79" t="s">
+      <c r="M16" s="92"/>
+      <c r="O16" s="79" t="s">
         <v>181</v>
       </c>
-      <c r="O16" s="79" t="s">
+      <c r="P16" s="79" t="s">
         <v>195</v>
       </c>
-      <c r="P16" s="150" t="s">
+      <c r="Q16" s="150" t="s">
         <v>145</v>
       </c>
-      <c r="Q16" s="91">
+      <c r="R16" s="79"/>
+      <c r="S16" s="91">
         <v>0.05</v>
       </c>
-      <c r="R16" s="92"/>
-      <c r="S16" s="92"/>
-      <c r="U16" s="63" t="s">
+      <c r="T16" s="92"/>
+      <c r="U16" s="92"/>
+      <c r="W16" s="63" t="s">
         <v>210</v>
       </c>
-      <c r="V16" s="63"/>
-      <c r="W16" s="91">
+      <c r="X16" s="63"/>
+      <c r="Y16" s="63"/>
+      <c r="Z16" s="91">
         <v>0.05</v>
       </c>
-      <c r="X16" s="92"/>
-      <c r="Y16" s="92"/>
+      <c r="AA16" s="92"/>
+      <c r="AB16" s="92"/>
     </row>
-    <row r="17" spans="2:25">
+    <row r="17" spans="2:28">
       <c r="C17" s="73"/>
       <c r="H17" s="63" t="s">
         <v>116</v>
       </c>
       <c r="I17" s="63"/>
-      <c r="J17" s="81">
+      <c r="J17" s="63" t="s">
+        <v>903</v>
+      </c>
+      <c r="K17" s="81">
         <v>0.05</v>
       </c>
-      <c r="K17" s="92"/>
       <c r="L17" s="92"/>
-      <c r="N17" s="79" t="s">
+      <c r="M17" s="92"/>
+      <c r="O17" s="79" t="s">
         <v>174</v>
       </c>
-      <c r="O17" s="79" t="s">
+      <c r="P17" s="79" t="s">
         <v>192</v>
       </c>
-      <c r="P17" s="79" t="s">
+      <c r="Q17" s="79" t="s">
         <v>135</v>
       </c>
-      <c r="Q17" s="91">
+      <c r="R17" s="79" t="s">
+        <v>929</v>
+      </c>
+      <c r="S17" s="91">
         <v>0.05</v>
       </c>
-      <c r="R17" s="92"/>
-      <c r="S17" s="92"/>
-      <c r="U17" s="63" t="s">
+      <c r="T17" s="92"/>
+      <c r="U17" s="92"/>
+      <c r="W17" s="63" t="s">
         <v>154</v>
       </c>
-      <c r="V17" s="63"/>
-      <c r="W17" s="91">
+      <c r="X17" s="63"/>
+      <c r="Y17" s="63" t="s">
+        <v>948</v>
+      </c>
+      <c r="Z17" s="91">
         <v>0.05</v>
       </c>
-      <c r="X17" s="92"/>
-      <c r="Y17" s="92"/>
+      <c r="AA17" s="92"/>
+      <c r="AB17" s="92"/>
     </row>
-    <row r="18" spans="2:25">
+    <row r="18" spans="2:28">
       <c r="B18" s="62" t="s">
         <v>157</v>
       </c>
       <c r="C18" s="72">
-        <f>K67+R46+X20+X30+X44+X60</f>
+        <f>L67+T46+AA20+AA30+AA44+AA60</f>
         <v>0</v>
       </c>
       <c r="H18" s="77" t="s">
         <v>481</v>
       </c>
       <c r="I18" s="63"/>
-      <c r="J18" s="81">
+      <c r="J18" s="63"/>
+      <c r="K18" s="81">
         <v>0.2</v>
       </c>
-      <c r="K18" s="82"/>
       <c r="L18" s="82"/>
-      <c r="N18" s="79" t="s">
+      <c r="M18" s="82"/>
+      <c r="O18" s="79" t="s">
         <v>188</v>
       </c>
-      <c r="O18" s="79" t="s">
+      <c r="P18" s="79" t="s">
         <v>201</v>
       </c>
-      <c r="P18" s="79" t="s">
+      <c r="Q18" s="79" t="s">
         <v>151</v>
       </c>
-      <c r="Q18" s="91">
+      <c r="R18" s="289" t="s">
+        <v>930</v>
+      </c>
+      <c r="S18" s="91">
         <v>0.05</v>
       </c>
-      <c r="R18" s="92"/>
-      <c r="S18" s="92"/>
-      <c r="U18" s="63"/>
-      <c r="V18" s="63"/>
-      <c r="W18" s="91"/>
-      <c r="X18" s="92"/>
-      <c r="Y18" s="92"/>
+      <c r="T18" s="92"/>
+      <c r="U18" s="92"/>
+      <c r="W18" s="63"/>
+      <c r="X18" s="63"/>
+      <c r="Y18" s="63" t="s">
+        <v>949</v>
+      </c>
+      <c r="Z18" s="91"/>
+      <c r="AA18" s="92"/>
+      <c r="AB18" s="92"/>
     </row>
-    <row r="19" spans="2:25">
+    <row r="19" spans="2:28">
       <c r="H19" s="63" t="s">
         <v>130</v>
       </c>
       <c r="I19" s="63"/>
-      <c r="J19" s="81">
+      <c r="J19" s="63"/>
+      <c r="K19" s="81">
         <v>0.05</v>
       </c>
-      <c r="K19" s="92"/>
       <c r="L19" s="92"/>
-      <c r="N19" s="149" t="s">
+      <c r="M19" s="92"/>
+      <c r="O19" s="149" t="s">
         <v>515</v>
       </c>
-      <c r="O19" s="79" t="s">
+      <c r="P19" s="79" t="s">
         <v>191</v>
       </c>
-      <c r="P19" s="79" t="s">
+      <c r="Q19" s="79" t="s">
         <v>141</v>
       </c>
-      <c r="Q19" s="91">
+      <c r="R19" s="79" t="s">
+        <v>931</v>
+      </c>
+      <c r="S19" s="91">
         <v>0.05</v>
       </c>
-      <c r="R19" s="92"/>
-      <c r="S19" s="92"/>
-      <c r="U19" s="63"/>
-      <c r="V19" s="63"/>
-      <c r="W19" s="91"/>
-      <c r="X19" s="92"/>
-      <c r="Y19" s="92"/>
+      <c r="T19" s="92"/>
+      <c r="U19" s="92"/>
+      <c r="W19" s="63"/>
+      <c r="X19" s="63"/>
+      <c r="Y19" s="63"/>
+      <c r="Z19" s="91"/>
+      <c r="AA19" s="92"/>
+      <c r="AB19" s="92"/>
     </row>
-    <row r="20" spans="2:25">
+    <row r="20" spans="2:28">
       <c r="C20" s="111"/>
       <c r="D20" s="113"/>
       <c r="H20" s="63" t="s">
         <v>482</v>
       </c>
       <c r="I20" s="63"/>
-      <c r="J20" s="81">
+      <c r="J20" s="63"/>
+      <c r="K20" s="81">
         <v>0.05</v>
       </c>
-      <c r="K20" s="92"/>
-      <c r="L20" s="92" t="s">
+      <c r="L20" s="92"/>
+      <c r="M20" s="92" t="s">
         <v>367</v>
       </c>
-      <c r="N20" s="160" t="s">
+      <c r="O20" s="160" t="s">
         <v>516</v>
       </c>
-      <c r="O20" s="79" t="s">
+      <c r="P20" s="79" t="s">
         <v>191</v>
       </c>
-      <c r="P20" s="79" t="s">
+      <c r="Q20" s="79" t="s">
         <v>329</v>
       </c>
-      <c r="Q20" s="91">
+      <c r="R20" s="79" t="s">
+        <v>939</v>
+      </c>
+      <c r="S20" s="91">
         <v>0.05</v>
       </c>
-      <c r="R20" s="92"/>
-      <c r="S20" s="92"/>
-      <c r="U20" s="215" t="s">
+      <c r="T20" s="92"/>
+      <c r="U20" s="92"/>
+      <c r="W20" s="181" t="s">
         <v>156</v>
       </c>
-      <c r="V20" s="215"/>
-      <c r="W20" s="215"/>
-      <c r="X20" s="92">
-        <f>SUM(X9:X19)</f>
+      <c r="X20" s="181"/>
+      <c r="Y20" s="181"/>
+      <c r="Z20" s="181"/>
+      <c r="AA20" s="92">
+        <f>SUM(AA9:AA19)</f>
         <v>0</v>
       </c>
-      <c r="Y20" s="92"/>
+      <c r="AB20" s="92"/>
     </row>
-    <row r="21" spans="2:25">
+    <row r="21" spans="2:28">
       <c r="B21" s="62" t="s">
         <v>211</v>
       </c>
@@ -8612,27 +8956,33 @@
         <v>740</v>
       </c>
       <c r="I21" s="63"/>
-      <c r="J21" s="81">
+      <c r="J21" s="63" t="s">
+        <v>904</v>
+      </c>
+      <c r="K21" s="81">
         <v>0.05</v>
       </c>
-      <c r="K21" s="92"/>
       <c r="L21" s="92"/>
-      <c r="N21" s="79" t="s">
+      <c r="M21" s="92"/>
+      <c r="O21" s="79" t="s">
         <v>185</v>
       </c>
-      <c r="O21" s="79" t="s">
+      <c r="P21" s="79" t="s">
         <v>191</v>
       </c>
-      <c r="P21" s="79" t="s">
+      <c r="Q21" s="79" t="s">
         <v>149</v>
       </c>
-      <c r="Q21" s="91">
+      <c r="R21" s="79" t="s">
+        <v>932</v>
+      </c>
+      <c r="S21" s="91">
         <v>0.05</v>
       </c>
-      <c r="R21" s="92"/>
-      <c r="S21" s="92"/>
+      <c r="T21" s="92"/>
+      <c r="U21" s="92"/>
     </row>
-    <row r="22" spans="2:25" ht="15.75" customHeight="1">
+    <row r="22" spans="2:28" ht="15.75" customHeight="1">
       <c r="B22" s="62" t="s">
         <v>373</v>
       </c>
@@ -8646,73 +8996,85 @@
         <v>76</v>
       </c>
       <c r="I22" s="63"/>
-      <c r="J22" s="81">
+      <c r="J22" s="63" t="s">
+        <v>905</v>
+      </c>
+      <c r="K22" s="81">
         <v>0.05</v>
       </c>
-      <c r="K22" s="92"/>
       <c r="L22" s="92"/>
-      <c r="N22" s="149" t="s">
+      <c r="M22" s="92"/>
+      <c r="O22" s="149" t="s">
         <v>517</v>
       </c>
-      <c r="O22" s="149" t="s">
+      <c r="P22" s="149" t="s">
         <v>518</v>
       </c>
-      <c r="P22" s="79" t="s">
+      <c r="Q22" s="79" t="s">
         <v>147</v>
       </c>
-      <c r="Q22" s="91">
+      <c r="R22" s="149"/>
+      <c r="S22" s="91">
         <v>0.05</v>
       </c>
-      <c r="R22" s="92"/>
-      <c r="S22" s="92"/>
-      <c r="U22" s="216" t="s">
+      <c r="T22" s="92"/>
+      <c r="U22" s="92"/>
+      <c r="W22" s="184" t="s">
         <v>497</v>
       </c>
-      <c r="V22" s="216"/>
-      <c r="W22" s="216"/>
-      <c r="X22" s="216"/>
+      <c r="X22" s="184"/>
+      <c r="Y22" s="184"/>
+      <c r="Z22" s="184"/>
+      <c r="AA22" s="184"/>
     </row>
-    <row r="23" spans="2:25">
+    <row r="23" spans="2:28">
       <c r="D23" s="111"/>
       <c r="E23" s="112"/>
       <c r="H23" s="63" t="s">
         <v>129</v>
       </c>
       <c r="I23" s="63"/>
-      <c r="J23" s="81">
+      <c r="J23" s="63" t="s">
+        <v>627</v>
+      </c>
+      <c r="K23" s="81">
         <v>0.05</v>
       </c>
-      <c r="K23" s="92"/>
       <c r="L23" s="92"/>
-      <c r="N23" s="79" t="s">
+      <c r="M23" s="92"/>
+      <c r="O23" s="79" t="s">
         <v>183</v>
       </c>
-      <c r="O23" s="79" t="s">
+      <c r="P23" s="79" t="s">
         <v>198</v>
       </c>
-      <c r="P23" s="79" t="s">
+      <c r="Q23" s="79" t="s">
         <v>147</v>
       </c>
-      <c r="Q23" s="91">
+      <c r="R23" s="79" t="s">
+        <v>933</v>
+      </c>
+      <c r="S23" s="91">
         <v>0.05</v>
       </c>
-      <c r="R23" s="92"/>
-      <c r="S23" s="92"/>
-      <c r="U23" s="63" t="s">
+      <c r="T23" s="92"/>
+      <c r="U23" s="92"/>
+      <c r="W23" s="63" t="s">
         <v>94</v>
       </c>
-      <c r="V23" s="63"/>
-      <c r="W23" s="63" t="s">
+      <c r="X23" s="63"/>
+      <c r="Y23" s="63"/>
+      <c r="Z23" s="63" t="s">
         <v>131</v>
       </c>
-      <c r="X23" s="63" t="s">
+      <c r="AA23" s="63" t="s">
         <v>132</v>
       </c>
-      <c r="Y23" s="63" t="s">
+      <c r="AB23" s="63" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="24" spans="2:25">
+    <row r="24" spans="2:28">
       <c r="D24" s="111"/>
       <c r="H24" s="63" t="s">
         <v>474</v>
@@ -8720,150 +9082,180 @@
       <c r="I24" s="63" t="s">
         <v>483</v>
       </c>
-      <c r="J24" s="81">
+      <c r="J24" s="63" t="s">
+        <v>906</v>
+      </c>
+      <c r="K24" s="81">
         <v>0.05</v>
       </c>
-      <c r="K24" s="92"/>
       <c r="L24" s="92"/>
-      <c r="N24" s="79" t="s">
+      <c r="M24" s="92"/>
+      <c r="O24" s="79" t="s">
         <v>184</v>
       </c>
-      <c r="O24" s="79" t="s">
+      <c r="P24" s="79" t="s">
         <v>199</v>
       </c>
-      <c r="P24" s="79" t="s">
+      <c r="Q24" s="79" t="s">
         <v>148</v>
       </c>
-      <c r="Q24" s="91">
+      <c r="R24" s="79" t="s">
+        <v>934</v>
+      </c>
+      <c r="S24" s="91">
         <v>0.05</v>
       </c>
-      <c r="R24" s="92"/>
-      <c r="S24" s="92"/>
-      <c r="U24" s="63" t="s">
+      <c r="T24" s="92"/>
+      <c r="U24" s="92"/>
+      <c r="W24" s="63" t="s">
         <v>498</v>
       </c>
-      <c r="V24" s="63" t="s">
+      <c r="X24" s="63" t="s">
         <v>499</v>
       </c>
-      <c r="W24" s="91">
+      <c r="Y24" s="63"/>
+      <c r="Z24" s="91">
         <v>0.05</v>
       </c>
-      <c r="X24" s="92"/>
-      <c r="Y24" s="92"/>
+      <c r="AA24" s="92"/>
+      <c r="AB24" s="92"/>
     </row>
-    <row r="25" spans="2:25">
+    <row r="25" spans="2:28">
       <c r="H25" s="63" t="s">
         <v>107</v>
       </c>
       <c r="I25" s="63"/>
-      <c r="J25" s="81">
+      <c r="J25" s="63"/>
+      <c r="K25" s="81">
         <v>0.05</v>
       </c>
-      <c r="K25" s="92"/>
       <c r="L25" s="92"/>
-      <c r="N25" s="149" t="s">
+      <c r="M25" s="92"/>
+      <c r="O25" s="149" t="s">
         <v>494</v>
       </c>
-      <c r="O25" s="79" t="s">
+      <c r="P25" s="79" t="s">
         <v>191</v>
       </c>
-      <c r="P25" s="79" t="s">
+      <c r="Q25" s="79" t="s">
         <v>142</v>
       </c>
-      <c r="Q25" s="91">
+      <c r="R25" s="290" t="s">
+        <v>935</v>
+      </c>
+      <c r="S25" s="91">
         <v>0.05</v>
       </c>
-      <c r="R25" s="92"/>
-      <c r="S25" s="92"/>
-      <c r="U25" s="63" t="s">
+      <c r="T25" s="92"/>
+      <c r="U25" s="92"/>
+      <c r="W25" s="63" t="s">
         <v>684</v>
       </c>
-      <c r="V25" s="63" t="s">
+      <c r="X25" s="63" t="s">
         <v>685</v>
       </c>
-      <c r="W25" s="91">
+      <c r="Y25" s="63" t="s">
+        <v>950</v>
+      </c>
+      <c r="Z25" s="91">
         <v>0.05</v>
       </c>
-      <c r="X25" s="92"/>
-      <c r="Y25" s="92"/>
+      <c r="AA25" s="92"/>
+      <c r="AB25" s="92"/>
     </row>
-    <row r="26" spans="2:25">
+    <row r="26" spans="2:28">
       <c r="H26" s="63" t="s">
         <v>484</v>
       </c>
       <c r="I26" s="63" t="s">
         <v>485</v>
       </c>
-      <c r="J26" s="81">
+      <c r="J26" s="63" t="s">
+        <v>907</v>
+      </c>
+      <c r="K26" s="81">
         <v>0.05</v>
       </c>
-      <c r="K26" s="92"/>
       <c r="L26" s="92"/>
-      <c r="N26" s="79" t="s">
+      <c r="M26" s="92"/>
+      <c r="O26" s="79" t="s">
         <v>180</v>
       </c>
-      <c r="O26" s="79" t="s">
+      <c r="P26" s="79" t="s">
         <v>195</v>
       </c>
-      <c r="P26" s="79" t="s">
+      <c r="Q26" s="79" t="s">
         <v>143</v>
       </c>
-      <c r="Q26" s="91">
+      <c r="R26" s="79" t="s">
+        <v>936</v>
+      </c>
+      <c r="S26" s="91">
         <v>0.05</v>
       </c>
-      <c r="R26" s="92"/>
-      <c r="S26" s="92"/>
-      <c r="T26" s="84"/>
-      <c r="U26" s="63" t="s">
+      <c r="T26" s="92"/>
+      <c r="U26" s="92"/>
+      <c r="V26" s="84"/>
+      <c r="W26" s="63" t="s">
         <v>758</v>
       </c>
-      <c r="V26" s="63" t="s">
+      <c r="X26" s="63" t="s">
         <v>759</v>
       </c>
-      <c r="W26" s="91">
+      <c r="Y26" s="63" t="s">
+        <v>951</v>
+      </c>
+      <c r="Z26" s="91">
         <v>0.05</v>
       </c>
-      <c r="X26" s="92"/>
-      <c r="Y26" s="92"/>
+      <c r="AA26" s="92"/>
+      <c r="AB26" s="92"/>
     </row>
-    <row r="27" spans="2:25">
+    <row r="27" spans="2:28">
       <c r="C27" s="114"/>
       <c r="H27" s="63" t="s">
         <v>78</v>
       </c>
       <c r="I27" s="63"/>
-      <c r="J27" s="81">
+      <c r="J27" s="63" t="s">
+        <v>908</v>
+      </c>
+      <c r="K27" s="81">
         <v>0.05</v>
       </c>
-      <c r="K27" s="92"/>
       <c r="L27" s="92"/>
-      <c r="N27" s="79" t="s">
+      <c r="M27" s="92"/>
+      <c r="O27" s="79" t="s">
         <v>182</v>
       </c>
-      <c r="O27" s="79" t="s">
+      <c r="P27" s="79" t="s">
         <v>191</v>
       </c>
-      <c r="P27" s="79" t="s">
+      <c r="Q27" s="79" t="s">
         <v>146</v>
       </c>
-      <c r="Q27" s="91">
+      <c r="R27" s="79"/>
+      <c r="S27" s="91">
         <v>0.05</v>
       </c>
-      <c r="R27" s="92"/>
-      <c r="S27" s="92"/>
-      <c r="U27" s="63" t="s">
+      <c r="T27" s="92"/>
+      <c r="U27" s="92"/>
+      <c r="W27" s="63" t="s">
         <v>901</v>
       </c>
-      <c r="V27" s="63" t="s">
+      <c r="X27" s="63" t="s">
         <v>767</v>
       </c>
-      <c r="W27" s="91">
+      <c r="Y27" s="63" t="s">
+        <v>952</v>
+      </c>
+      <c r="Z27" s="91">
         <v>0.05</v>
       </c>
-      <c r="X27" s="92"/>
-      <c r="Y27" s="92"/>
+      <c r="AA27" s="92"/>
+      <c r="AB27" s="92"/>
     </row>
-    <row r="28" spans="2:25">
+    <row r="28" spans="2:28">
       <c r="D28" s="120">
         <f>SUM(D23:D27)</f>
         <v>0</v>
@@ -8876,68 +9268,80 @@
         <v>104</v>
       </c>
       <c r="I28" s="63"/>
-      <c r="J28" s="81">
+      <c r="J28" s="63" t="s">
+        <v>909</v>
+      </c>
+      <c r="K28" s="81">
         <v>0.05</v>
       </c>
-      <c r="K28" s="92"/>
       <c r="L28" s="92"/>
-      <c r="N28" s="79" t="s">
+      <c r="M28" s="92"/>
+      <c r="O28" s="79" t="s">
         <v>177</v>
       </c>
-      <c r="O28" s="79" t="s">
+      <c r="P28" s="79" t="s">
         <v>191</v>
       </c>
-      <c r="P28" s="79" t="s">
+      <c r="Q28" s="79" t="s">
         <v>137</v>
       </c>
-      <c r="Q28" s="91">
+      <c r="R28" s="79"/>
+      <c r="S28" s="91">
         <v>0.05</v>
       </c>
-      <c r="R28" s="92"/>
-      <c r="S28" s="92"/>
-      <c r="U28" s="63" t="s">
+      <c r="T28" s="92"/>
+      <c r="U28" s="92"/>
+      <c r="W28" s="63" t="s">
         <v>370</v>
       </c>
-      <c r="V28" s="63" t="s">
+      <c r="X28" s="63" t="s">
         <v>371</v>
       </c>
-      <c r="W28" s="91">
+      <c r="Y28" s="63" t="s">
+        <v>953</v>
+      </c>
+      <c r="Z28" s="91">
         <v>0.1</v>
       </c>
-      <c r="X28" s="92"/>
-      <c r="Y28" s="92" t="s">
+      <c r="AA28" s="92"/>
+      <c r="AB28" s="92" t="s">
         <v>372</v>
       </c>
     </row>
-    <row r="29" spans="2:25" ht="51.75">
+    <row r="29" spans="2:28" ht="51.75">
       <c r="H29" s="63" t="s">
         <v>115</v>
       </c>
       <c r="I29" s="63"/>
-      <c r="J29" s="81">
+      <c r="J29" s="63"/>
+      <c r="K29" s="81">
         <v>0.05</v>
       </c>
-      <c r="K29" s="92"/>
       <c r="L29" s="92"/>
-      <c r="N29" s="153" t="s">
+      <c r="M29" s="92"/>
+      <c r="O29" s="153" t="s">
         <v>768</v>
       </c>
-      <c r="O29" s="63"/>
-      <c r="P29" s="63" t="s">
+      <c r="P29" s="63"/>
+      <c r="Q29" s="63" t="s">
         <v>102</v>
       </c>
-      <c r="Q29" s="91">
+      <c r="R29" s="63" t="s">
+        <v>937</v>
+      </c>
+      <c r="S29" s="91">
         <v>0.05</v>
       </c>
-      <c r="R29" s="92"/>
-      <c r="S29" s="92"/>
-      <c r="U29" s="63"/>
-      <c r="V29" s="63"/>
-      <c r="W29" s="91"/>
-      <c r="X29" s="92"/>
-      <c r="Y29" s="92"/>
+      <c r="T29" s="92"/>
+      <c r="U29" s="92"/>
+      <c r="W29" s="63"/>
+      <c r="X29" s="63"/>
+      <c r="Y29" s="63"/>
+      <c r="Z29" s="91"/>
+      <c r="AA29" s="92"/>
+      <c r="AB29" s="92"/>
     </row>
-    <row r="30" spans="2:25">
+    <row r="30" spans="2:28">
       <c r="B30" s="115" t="s">
         <v>212</v>
       </c>
@@ -8949,944 +9353,1087 @@
         <v>475</v>
       </c>
       <c r="I30" s="63"/>
-      <c r="J30" s="81">
+      <c r="J30" s="63"/>
+      <c r="K30" s="81">
         <v>0.05</v>
       </c>
-      <c r="K30" s="92"/>
       <c r="L30" s="92"/>
-      <c r="N30" s="79" t="s">
+      <c r="M30" s="92"/>
+      <c r="O30" s="79" t="s">
         <v>176</v>
       </c>
-      <c r="O30" s="79" t="s">
+      <c r="P30" s="79" t="s">
         <v>194</v>
       </c>
-      <c r="P30" s="79" t="s">
+      <c r="Q30" s="79" t="s">
         <v>136</v>
       </c>
-      <c r="Q30" s="91">
+      <c r="R30" s="79" t="s">
+        <v>940</v>
+      </c>
+      <c r="S30" s="91">
         <v>0.05</v>
       </c>
-      <c r="R30" s="92"/>
-      <c r="S30" s="92"/>
-      <c r="U30" s="215" t="s">
+      <c r="T30" s="92"/>
+      <c r="U30" s="92"/>
+      <c r="W30" s="181" t="s">
         <v>156</v>
       </c>
-      <c r="V30" s="215"/>
-      <c r="W30" s="215"/>
-      <c r="X30" s="92">
-        <f>SUM(X24:X29)</f>
+      <c r="X30" s="181"/>
+      <c r="Y30" s="181"/>
+      <c r="Z30" s="181"/>
+      <c r="AA30" s="92">
+        <f>SUM(AA24:AA29)</f>
         <v>0</v>
       </c>
-      <c r="Y30" s="92"/>
+      <c r="AB30" s="92"/>
     </row>
-    <row r="31" spans="2:25">
+    <row r="31" spans="2:28">
       <c r="H31" s="63" t="s">
         <v>112</v>
       </c>
       <c r="I31" s="63" t="s">
         <v>506</v>
       </c>
-      <c r="J31" s="81">
+      <c r="J31" s="63"/>
+      <c r="K31" s="81">
         <v>0.05</v>
       </c>
-      <c r="K31" s="92"/>
       <c r="L31" s="92"/>
-      <c r="N31" s="79" t="s">
+      <c r="M31" s="92"/>
+      <c r="O31" s="79" t="s">
         <v>189</v>
       </c>
-      <c r="O31" s="79" t="s">
+      <c r="P31" s="79" t="s">
         <v>202</v>
       </c>
-      <c r="P31" s="149" t="s">
+      <c r="Q31" s="149" t="s">
         <v>153</v>
       </c>
-      <c r="Q31" s="91">
+      <c r="R31" s="79"/>
+      <c r="S31" s="91">
         <v>0.05</v>
       </c>
-      <c r="R31" s="92"/>
-      <c r="S31" s="92"/>
+      <c r="T31" s="92"/>
+      <c r="U31" s="92"/>
     </row>
-    <row r="32" spans="2:25">
+    <row r="32" spans="2:28">
       <c r="H32" s="63" t="s">
         <v>113</v>
       </c>
       <c r="I32" s="63"/>
-      <c r="J32" s="81">
+      <c r="J32" s="63" t="s">
+        <v>910</v>
+      </c>
+      <c r="K32" s="81">
         <v>0.05</v>
       </c>
-      <c r="K32" s="92"/>
-      <c r="L32" s="92" t="s">
+      <c r="L32" s="92"/>
+      <c r="M32" s="92" t="s">
         <v>331</v>
       </c>
-      <c r="N32" s="79" t="s">
+      <c r="O32" s="79" t="s">
         <v>190</v>
       </c>
-      <c r="O32" s="79" t="s">
+      <c r="P32" s="79" t="s">
         <v>202</v>
       </c>
-      <c r="P32" s="79" t="s">
+      <c r="Q32" s="79" t="s">
         <v>152</v>
       </c>
-      <c r="Q32" s="91">
+      <c r="R32" s="79"/>
+      <c r="S32" s="91">
         <v>0.05</v>
       </c>
-      <c r="R32" s="92"/>
-      <c r="S32" s="92"/>
-      <c r="U32" s="216" t="s">
+      <c r="T32" s="92"/>
+      <c r="U32" s="92"/>
+      <c r="W32" s="184" t="s">
         <v>205</v>
       </c>
-      <c r="V32" s="216"/>
-      <c r="W32" s="216"/>
-      <c r="X32" s="216"/>
-      <c r="Y32" s="62"/>
+      <c r="X32" s="184"/>
+      <c r="Y32" s="184"/>
+      <c r="Z32" s="184"/>
+      <c r="AA32" s="184"/>
+      <c r="AB32" s="62"/>
     </row>
-    <row r="33" spans="8:25">
+    <row r="33" spans="8:28">
       <c r="H33" s="63" t="s">
         <v>505</v>
       </c>
       <c r="I33" s="63"/>
-      <c r="J33" s="81">
+      <c r="J33" s="63"/>
+      <c r="K33" s="81">
         <v>0.05</v>
       </c>
-      <c r="K33" s="92"/>
       <c r="L33" s="92"/>
-      <c r="N33" s="79" t="s">
+      <c r="M33" s="92"/>
+      <c r="O33" s="79" t="s">
         <v>81</v>
       </c>
-      <c r="O33" s="79" t="s">
+      <c r="P33" s="79" t="s">
         <v>196</v>
       </c>
-      <c r="P33" s="79" t="s">
+      <c r="Q33" s="79" t="s">
         <v>814</v>
       </c>
-      <c r="Q33" s="91">
+      <c r="R33" s="79"/>
+      <c r="S33" s="91">
         <v>0.05</v>
       </c>
-      <c r="R33" s="92"/>
-      <c r="S33" s="92"/>
-      <c r="U33" s="63" t="s">
+      <c r="T33" s="92"/>
+      <c r="U33" s="92"/>
+      <c r="W33" s="63" t="s">
         <v>94</v>
       </c>
-      <c r="V33" s="63" t="s">
+      <c r="X33" s="63" t="s">
         <v>100</v>
       </c>
-      <c r="W33" s="63" t="s">
+      <c r="Y33" s="63"/>
+      <c r="Z33" s="63" t="s">
         <v>131</v>
       </c>
-      <c r="X33" s="63" t="s">
+      <c r="AA33" s="63" t="s">
         <v>132</v>
       </c>
-      <c r="Y33" s="63" t="s">
+      <c r="AB33" s="63" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="34" spans="8:25">
+    <row r="34" spans="8:28">
       <c r="H34" s="63" t="s">
         <v>842</v>
       </c>
       <c r="I34" s="63"/>
-      <c r="J34" s="81">
+      <c r="J34" s="63" t="s">
+        <v>911</v>
+      </c>
+      <c r="K34" s="81">
         <v>0.05</v>
       </c>
-      <c r="K34" s="82"/>
       <c r="L34" s="82"/>
-      <c r="N34" s="79" t="s">
+      <c r="M34" s="82"/>
+      <c r="O34" s="79" t="s">
         <v>504</v>
       </c>
-      <c r="O34" s="79" t="s">
+      <c r="P34" s="79" t="s">
         <v>197</v>
       </c>
-      <c r="P34" s="79" t="s">
+      <c r="Q34" s="79" t="s">
         <v>144</v>
       </c>
-      <c r="Q34" s="91">
+      <c r="R34" s="79"/>
+      <c r="S34" s="91">
         <v>0.05</v>
       </c>
-      <c r="R34" s="92"/>
-      <c r="S34" s="92"/>
-      <c r="U34" s="63" t="s">
+      <c r="T34" s="92"/>
+      <c r="U34" s="92"/>
+      <c r="W34" s="63" t="s">
         <v>45</v>
       </c>
-      <c r="V34" s="63" t="s">
+      <c r="X34" s="63" t="s">
         <v>103</v>
       </c>
-      <c r="W34" s="83">
+      <c r="Y34" s="63"/>
+      <c r="Z34" s="83">
         <v>0.05</v>
       </c>
-      <c r="X34" s="92"/>
-      <c r="Y34" s="77"/>
+      <c r="AA34" s="92"/>
+      <c r="AB34" s="77"/>
     </row>
-    <row r="35" spans="8:25">
+    <row r="35" spans="8:28">
       <c r="H35" s="63" t="s">
         <v>476</v>
       </c>
       <c r="I35" s="63"/>
-      <c r="J35" s="81">
+      <c r="J35" s="63" t="s">
+        <v>715</v>
+      </c>
+      <c r="K35" s="81">
         <v>0.05</v>
       </c>
-      <c r="K35" s="82"/>
-      <c r="L35" s="82" t="s">
+      <c r="L35" s="82"/>
+      <c r="M35" s="82" t="s">
         <v>384</v>
       </c>
-      <c r="N35" s="79" t="s">
+      <c r="O35" s="79" t="s">
         <v>187</v>
       </c>
-      <c r="O35" s="79" t="s">
+      <c r="P35" s="79" t="s">
         <v>200</v>
       </c>
-      <c r="P35" s="79" t="s">
+      <c r="Q35" s="79" t="s">
         <v>173</v>
       </c>
-      <c r="Q35" s="91">
+      <c r="R35" s="79"/>
+      <c r="S35" s="91">
         <v>0.05</v>
       </c>
-      <c r="R35" s="92"/>
-      <c r="S35" s="92"/>
-      <c r="U35" s="63" t="s">
+      <c r="T35" s="92"/>
+      <c r="U35" s="92"/>
+      <c r="W35" s="63" t="s">
         <v>319</v>
       </c>
-      <c r="V35" s="63"/>
-      <c r="W35" s="83">
+      <c r="X35" s="63"/>
+      <c r="Y35" s="63" t="s">
+        <v>954</v>
+      </c>
+      <c r="Z35" s="83">
         <v>0.05</v>
       </c>
-      <c r="X35" s="92"/>
-      <c r="Y35" s="77"/>
+      <c r="AA35" s="92"/>
+      <c r="AB35" s="77"/>
     </row>
-    <row r="36" spans="8:25">
+    <row r="36" spans="8:28">
       <c r="H36" s="63" t="s">
         <v>733</v>
       </c>
       <c r="I36" s="63"/>
-      <c r="J36" s="81">
+      <c r="J36" s="63" t="s">
+        <v>912</v>
+      </c>
+      <c r="K36" s="81">
         <v>0.05</v>
       </c>
-      <c r="K36" s="92"/>
-      <c r="L36" s="92" t="s">
+      <c r="L36" s="92"/>
+      <c r="M36" s="92" t="s">
         <v>207</v>
       </c>
-      <c r="N36" s="79" t="s">
+      <c r="O36" s="79" t="s">
         <v>186</v>
       </c>
-      <c r="O36" s="79" t="s">
+      <c r="P36" s="79" t="s">
         <v>195</v>
       </c>
-      <c r="P36" s="79" t="s">
+      <c r="Q36" s="79" t="s">
         <v>150</v>
       </c>
-      <c r="Q36" s="91">
+      <c r="R36" s="79"/>
+      <c r="S36" s="91">
         <v>0.05</v>
       </c>
-      <c r="R36" s="92"/>
-      <c r="S36" s="92"/>
-      <c r="U36" s="63" t="s">
+      <c r="T36" s="92"/>
+      <c r="U36" s="92"/>
+      <c r="W36" s="63" t="s">
         <v>155</v>
       </c>
-      <c r="V36" s="63" t="s">
+      <c r="X36" s="63" t="s">
         <v>101</v>
       </c>
-      <c r="W36" s="83">
+      <c r="Y36" s="63" t="s">
+        <v>955</v>
+      </c>
+      <c r="Z36" s="83">
         <v>0.05</v>
       </c>
-      <c r="X36" s="92"/>
-      <c r="Y36" s="77"/>
+      <c r="AA36" s="92"/>
+      <c r="AB36" s="77"/>
     </row>
-    <row r="37" spans="8:25">
+    <row r="37" spans="8:28">
       <c r="H37" s="63" t="s">
         <v>547</v>
       </c>
       <c r="I37" s="63"/>
-      <c r="J37" s="81">
+      <c r="J37" s="63" t="s">
+        <v>913</v>
+      </c>
+      <c r="K37" s="81">
         <v>0.05</v>
       </c>
-      <c r="K37" s="92"/>
       <c r="L37" s="92"/>
-      <c r="N37" s="149" t="s">
+      <c r="M37" s="92"/>
+      <c r="O37" s="149" t="s">
         <v>495</v>
       </c>
-      <c r="O37" s="149" t="s">
+      <c r="P37" s="149" t="s">
         <v>519</v>
       </c>
-      <c r="P37" s="79" t="s">
+      <c r="Q37" s="79" t="s">
         <v>496</v>
       </c>
-      <c r="Q37" s="91">
+      <c r="R37" s="149" t="s">
+        <v>938</v>
+      </c>
+      <c r="S37" s="91">
         <v>0.05</v>
       </c>
-      <c r="R37" s="92"/>
-      <c r="S37" s="92"/>
-      <c r="U37" s="63" t="s">
+      <c r="T37" s="92"/>
+      <c r="U37" s="92"/>
+      <c r="W37" s="63" t="s">
         <v>503</v>
       </c>
-      <c r="V37" s="63"/>
-      <c r="W37" s="83">
+      <c r="X37" s="63"/>
+      <c r="Y37" s="63" t="s">
+        <v>956</v>
+      </c>
+      <c r="Z37" s="83">
         <v>0.05</v>
       </c>
-      <c r="X37" s="92"/>
-      <c r="Y37" s="77" t="s">
+      <c r="AA37" s="92"/>
+      <c r="AB37" s="77" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="38" spans="8:25">
+    <row r="38" spans="8:28">
       <c r="H38" s="63" t="s">
         <v>486</v>
       </c>
       <c r="I38" s="63"/>
-      <c r="J38" s="81">
+      <c r="J38" s="63" t="s">
+        <v>914</v>
+      </c>
+      <c r="K38" s="81">
         <v>0.05</v>
       </c>
-      <c r="K38" s="92"/>
       <c r="L38" s="92"/>
-      <c r="N38" s="149" t="s">
+      <c r="M38" s="92"/>
+      <c r="O38" s="149" t="s">
         <v>520</v>
       </c>
-      <c r="O38" s="149" t="s">
+      <c r="P38" s="149" t="s">
         <v>521</v>
       </c>
-      <c r="P38" s="149" t="s">
+      <c r="Q38" s="149" t="s">
         <v>522</v>
       </c>
-      <c r="Q38" s="91">
+      <c r="R38" s="149"/>
+      <c r="S38" s="91">
         <v>0.05</v>
       </c>
-      <c r="R38" s="92"/>
-      <c r="S38" s="92"/>
-      <c r="U38" s="63" t="s">
+      <c r="T38" s="92"/>
+      <c r="U38" s="92"/>
+      <c r="W38" s="63" t="s">
         <v>502</v>
       </c>
-      <c r="V38" s="63" t="s">
+      <c r="X38" s="63" t="s">
         <v>208</v>
       </c>
-      <c r="W38" s="83">
+      <c r="Y38" s="63"/>
+      <c r="Z38" s="83">
         <v>0.05</v>
       </c>
-      <c r="X38" s="63"/>
-      <c r="Y38" s="92" t="s">
+      <c r="AA38" s="63"/>
+      <c r="AB38" s="92" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="39" spans="8:25">
+    <row r="39" spans="8:28">
       <c r="H39" s="63" t="s">
         <v>487</v>
       </c>
       <c r="I39" s="63"/>
-      <c r="J39" s="91">
+      <c r="J39" s="63" t="s">
+        <v>915</v>
+      </c>
+      <c r="K39" s="91">
         <v>0.05</v>
       </c>
-      <c r="K39" s="92"/>
-      <c r="L39" s="92" t="s">
+      <c r="L39" s="92"/>
+      <c r="M39" s="92" t="s">
         <v>869</v>
       </c>
-      <c r="N39" s="149" t="s">
+      <c r="O39" s="149" t="s">
         <v>523</v>
       </c>
-      <c r="O39" s="149" t="s">
+      <c r="P39" s="149" t="s">
         <v>524</v>
       </c>
-      <c r="P39" s="79" t="s">
+      <c r="Q39" s="79" t="s">
         <v>525</v>
       </c>
-      <c r="Q39" s="91">
+      <c r="R39" s="149"/>
+      <c r="S39" s="91">
         <v>0.05</v>
       </c>
-      <c r="R39" s="92"/>
-      <c r="S39" s="92"/>
-      <c r="U39" s="63" t="s">
+      <c r="T39" s="92"/>
+      <c r="U39" s="92"/>
+      <c r="W39" s="63" t="s">
         <v>500</v>
-      </c>
-      <c r="V39" s="63"/>
-      <c r="W39" s="83">
-        <v>0.05</v>
       </c>
       <c r="X39" s="63"/>
       <c r="Y39" s="63" t="s">
+        <v>957</v>
+      </c>
+      <c r="Z39" s="83">
+        <v>0.05</v>
+      </c>
+      <c r="AA39" s="63"/>
+      <c r="AB39" s="63" t="s">
         <v>501</v>
       </c>
     </row>
-    <row r="40" spans="8:25" ht="34.5">
+    <row r="40" spans="8:28" ht="34.5">
       <c r="H40" s="63" t="s">
         <v>492</v>
       </c>
       <c r="I40" s="63"/>
-      <c r="J40" s="91">
+      <c r="J40" s="63" t="s">
+        <v>916</v>
+      </c>
+      <c r="K40" s="91">
         <v>0.05</v>
       </c>
-      <c r="K40" s="92"/>
       <c r="L40" s="92"/>
-      <c r="N40" s="149" t="s">
+      <c r="M40" s="92"/>
+      <c r="O40" s="149" t="s">
         <v>526</v>
       </c>
-      <c r="O40" s="149" t="s">
+      <c r="P40" s="149" t="s">
         <v>527</v>
       </c>
-      <c r="P40" s="149" t="s">
+      <c r="Q40" s="149" t="s">
         <v>528</v>
       </c>
-      <c r="Q40" s="91">
+      <c r="R40" s="149"/>
+      <c r="S40" s="91">
         <v>0.05</v>
       </c>
-      <c r="R40" s="92"/>
-      <c r="S40" s="92"/>
-      <c r="U40" s="153" t="s">
+      <c r="T40" s="92"/>
+      <c r="U40" s="92"/>
+      <c r="W40" s="153" t="s">
         <v>540</v>
       </c>
-      <c r="V40" s="63" t="s">
+      <c r="X40" s="63" t="s">
         <v>541</v>
       </c>
-      <c r="W40" s="83">
+      <c r="Y40" s="63" t="s">
+        <v>958</v>
+      </c>
+      <c r="Z40" s="83">
         <v>0.05</v>
       </c>
-      <c r="X40" s="92"/>
-      <c r="Y40" s="77" t="s">
+      <c r="AA40" s="92"/>
+      <c r="AB40" s="77" t="s">
         <v>542</v>
       </c>
     </row>
-    <row r="41" spans="8:25">
+    <row r="41" spans="8:28">
       <c r="H41" s="63" t="s">
         <v>477</v>
       </c>
       <c r="I41" s="63"/>
-      <c r="J41" s="91">
+      <c r="J41" s="63" t="s">
+        <v>917</v>
+      </c>
+      <c r="K41" s="91">
         <v>0.05</v>
       </c>
-      <c r="K41" s="92"/>
       <c r="L41" s="92"/>
-      <c r="N41" s="149" t="s">
+      <c r="M41" s="92"/>
+      <c r="O41" s="149" t="s">
         <v>529</v>
       </c>
-      <c r="O41" s="149" t="s">
+      <c r="P41" s="149" t="s">
         <v>530</v>
       </c>
-      <c r="P41" s="149" t="s">
+      <c r="Q41" s="149" t="s">
         <v>531</v>
       </c>
-      <c r="Q41" s="91">
+      <c r="R41" s="149"/>
+      <c r="S41" s="91">
         <v>0.05</v>
       </c>
-      <c r="R41" s="92"/>
-      <c r="S41" s="92"/>
-      <c r="U41" s="153" t="s">
+      <c r="T41" s="92"/>
+      <c r="U41" s="92"/>
+      <c r="W41" s="153" t="s">
         <v>543</v>
       </c>
-      <c r="V41" s="63" t="s">
+      <c r="X41" s="63" t="s">
         <v>544</v>
       </c>
-      <c r="W41" s="83">
+      <c r="Y41" s="153" t="s">
+        <v>959</v>
+      </c>
+      <c r="Z41" s="83">
         <v>0.05</v>
       </c>
-      <c r="X41" s="92"/>
-      <c r="Y41" s="77"/>
+      <c r="AA41" s="92"/>
+      <c r="AB41" s="77"/>
     </row>
-    <row r="42" spans="8:25">
+    <row r="42" spans="8:28">
       <c r="H42" s="63" t="s">
         <v>105</v>
       </c>
       <c r="I42" s="63"/>
-      <c r="J42" s="81">
+      <c r="J42" s="63"/>
+      <c r="K42" s="81">
         <v>0.05</v>
       </c>
-      <c r="K42" s="92"/>
       <c r="L42" s="92"/>
-      <c r="N42" s="149" t="s">
+      <c r="M42" s="92"/>
+      <c r="O42" s="149" t="s">
         <v>532</v>
       </c>
-      <c r="O42" s="149" t="s">
+      <c r="P42" s="149" t="s">
         <v>533</v>
       </c>
-      <c r="P42" s="149" t="s">
+      <c r="Q42" s="149" t="s">
         <v>534</v>
       </c>
-      <c r="Q42" s="91">
+      <c r="R42" s="149"/>
+      <c r="S42" s="91">
         <v>0.05</v>
       </c>
-      <c r="R42" s="92"/>
-      <c r="S42" s="92"/>
-      <c r="U42" s="63" t="s">
+      <c r="T42" s="92"/>
+      <c r="U42" s="92"/>
+      <c r="W42" s="63" t="s">
         <v>548</v>
       </c>
-      <c r="V42" s="63" t="s">
+      <c r="X42" s="63" t="s">
         <v>545</v>
       </c>
-      <c r="W42" s="83">
+      <c r="Y42" s="153" t="s">
+        <v>960</v>
+      </c>
+      <c r="Z42" s="83">
         <v>0.05</v>
       </c>
-      <c r="X42" s="63"/>
-      <c r="Y42" s="63" t="s">
+      <c r="AA42" s="63"/>
+      <c r="AB42" s="63" t="s">
         <v>546</v>
       </c>
     </row>
-    <row r="43" spans="8:25">
+    <row r="43" spans="8:28">
       <c r="H43" s="63" t="s">
         <v>109</v>
       </c>
       <c r="I43" s="63"/>
-      <c r="J43" s="81">
+      <c r="J43" s="63"/>
+      <c r="K43" s="81">
         <v>0.05</v>
       </c>
-      <c r="K43" s="92"/>
       <c r="L43" s="92"/>
-      <c r="N43" s="149" t="s">
+      <c r="M43" s="92"/>
+      <c r="O43" s="149" t="s">
         <v>535</v>
       </c>
-      <c r="O43" s="149" t="s">
+      <c r="P43" s="149" t="s">
         <v>536</v>
       </c>
-      <c r="P43" s="149" t="s">
+      <c r="Q43" s="149" t="s">
         <v>537</v>
       </c>
-      <c r="Q43" s="91">
+      <c r="R43" s="149"/>
+      <c r="S43" s="91">
         <v>0.05</v>
       </c>
-      <c r="R43" s="92"/>
-      <c r="S43" s="92"/>
-      <c r="U43" s="63"/>
-      <c r="V43" s="63"/>
-      <c r="W43" s="83"/>
-      <c r="X43" s="92"/>
-      <c r="Y43" s="77"/>
+      <c r="T43" s="92"/>
+      <c r="U43" s="92"/>
+      <c r="W43" s="63"/>
+      <c r="X43" s="63"/>
+      <c r="Y43" s="63" t="s">
+        <v>961</v>
+      </c>
+      <c r="Z43" s="83"/>
+      <c r="AA43" s="92"/>
+      <c r="AB43" s="77"/>
     </row>
-    <row r="44" spans="8:25">
+    <row r="44" spans="8:28">
       <c r="H44" s="63" t="s">
         <v>106</v>
       </c>
       <c r="I44" s="63"/>
-      <c r="J44" s="81">
+      <c r="J44" s="63"/>
+      <c r="K44" s="81">
         <v>0.05</v>
       </c>
-      <c r="K44" s="92"/>
       <c r="L44" s="92"/>
-      <c r="N44" s="149" t="s">
+      <c r="M44" s="92"/>
+      <c r="O44" s="149" t="s">
         <v>538</v>
       </c>
-      <c r="O44" s="149" t="s">
+      <c r="P44" s="149" t="s">
         <v>536</v>
       </c>
-      <c r="P44" s="79" t="s">
+      <c r="Q44" s="79" t="s">
         <v>539</v>
       </c>
-      <c r="Q44" s="91">
+      <c r="R44" s="149"/>
+      <c r="S44" s="91">
         <v>0.05</v>
       </c>
-      <c r="R44" s="92"/>
-      <c r="S44" s="92"/>
-      <c r="U44" s="215" t="s">
+      <c r="T44" s="92"/>
+      <c r="U44" s="92"/>
+      <c r="W44" s="181" t="s">
         <v>156</v>
       </c>
-      <c r="V44" s="215"/>
-      <c r="W44" s="215"/>
-      <c r="X44" s="92">
-        <f>SUM(X34:X43)</f>
+      <c r="X44" s="181"/>
+      <c r="Y44" s="181"/>
+      <c r="Z44" s="181"/>
+      <c r="AA44" s="92">
+        <f>SUM(AA34:AA43)</f>
         <v>0</v>
       </c>
-      <c r="Y44" s="77"/>
+      <c r="AB44" s="77"/>
     </row>
-    <row r="45" spans="8:25">
+    <row r="45" spans="8:28">
       <c r="H45" s="63" t="s">
         <v>121</v>
       </c>
       <c r="I45" s="63"/>
-      <c r="J45" s="81">
+      <c r="J45" s="63"/>
+      <c r="K45" s="81">
         <v>0.05</v>
       </c>
-      <c r="K45" s="82"/>
       <c r="L45" s="82"/>
-      <c r="N45" s="63"/>
+      <c r="M45" s="82"/>
       <c r="O45" s="63"/>
       <c r="P45" s="63"/>
-      <c r="Q45" s="91"/>
-      <c r="R45" s="92"/>
-      <c r="S45" s="92"/>
+      <c r="Q45" s="63"/>
+      <c r="R45" s="63"/>
+      <c r="S45" s="91"/>
+      <c r="T45" s="92"/>
+      <c r="U45" s="92"/>
     </row>
-    <row r="46" spans="8:25">
+    <row r="46" spans="8:28">
       <c r="H46" s="63" t="s">
         <v>478</v>
       </c>
       <c r="I46" s="63"/>
-      <c r="J46" s="81">
+      <c r="J46" s="63" t="s">
+        <v>918</v>
+      </c>
+      <c r="K46" s="81">
         <v>0.05</v>
       </c>
-      <c r="K46" s="82"/>
       <c r="L46" s="82"/>
-      <c r="N46" s="215" t="s">
+      <c r="M46" s="82"/>
+      <c r="O46" s="181" t="s">
         <v>156</v>
       </c>
-      <c r="O46" s="215"/>
-      <c r="P46" s="215"/>
-      <c r="Q46" s="215"/>
-      <c r="R46" s="82">
-        <f>SUM(R9:R45)</f>
+      <c r="P46" s="181"/>
+      <c r="Q46" s="181"/>
+      <c r="R46" s="181"/>
+      <c r="S46" s="181"/>
+      <c r="T46" s="82">
+        <f>SUM(T9:T45)</f>
         <v>0</v>
       </c>
-      <c r="S46" s="82"/>
+      <c r="U46" s="82"/>
     </row>
-    <row r="47" spans="8:25">
+    <row r="47" spans="8:28">
       <c r="H47" s="63" t="s">
         <v>117</v>
       </c>
       <c r="I47" s="63"/>
-      <c r="J47" s="81">
+      <c r="J47" s="63"/>
+      <c r="K47" s="81">
         <v>0.05</v>
       </c>
-      <c r="K47" s="82"/>
       <c r="L47" s="82"/>
-      <c r="U47" s="216" t="s">
+      <c r="M47" s="82"/>
+      <c r="W47" s="184" t="s">
         <v>549</v>
       </c>
-      <c r="V47" s="216"/>
-      <c r="W47" s="216"/>
-      <c r="X47" s="216"/>
-      <c r="Y47" s="62"/>
+      <c r="X47" s="184"/>
+      <c r="Y47" s="184"/>
+      <c r="Z47" s="184"/>
+      <c r="AA47" s="184"/>
+      <c r="AB47" s="62"/>
     </row>
-    <row r="48" spans="8:25">
+    <row r="48" spans="8:28">
       <c r="H48" s="63" t="s">
         <v>128</v>
       </c>
       <c r="I48" s="63"/>
-      <c r="J48" s="81">
+      <c r="J48" s="63"/>
+      <c r="K48" s="81">
         <v>0.05</v>
       </c>
-      <c r="K48" s="82"/>
       <c r="L48" s="82"/>
-      <c r="U48" s="63" t="s">
+      <c r="M48" s="82"/>
+      <c r="W48" s="63" t="s">
         <v>550</v>
       </c>
-      <c r="V48" s="63" t="s">
+      <c r="X48" s="63" t="s">
         <v>100</v>
       </c>
-      <c r="W48" s="63" t="s">
+      <c r="Y48" s="63"/>
+      <c r="Z48" s="63" t="s">
         <v>131</v>
       </c>
-      <c r="X48" s="63" t="s">
+      <c r="AA48" s="63" t="s">
         <v>551</v>
       </c>
-      <c r="Y48" s="63" t="s">
+      <c r="AB48" s="63" t="s">
         <v>552</v>
       </c>
     </row>
-    <row r="49" spans="8:25">
+    <row r="49" spans="8:28">
       <c r="H49" s="63" t="s">
         <v>119</v>
       </c>
       <c r="I49" s="63"/>
-      <c r="J49" s="81">
+      <c r="J49" s="63"/>
+      <c r="K49" s="81">
         <v>0.05</v>
       </c>
-      <c r="K49" s="82"/>
       <c r="L49" s="82"/>
-      <c r="U49" s="63"/>
-      <c r="V49" s="63"/>
-      <c r="W49" s="83"/>
-      <c r="X49" s="92"/>
-      <c r="Y49" s="77"/>
+      <c r="M49" s="82"/>
+      <c r="W49" s="63"/>
+      <c r="X49" s="63"/>
+      <c r="Y49" s="63"/>
+      <c r="Z49" s="83"/>
+      <c r="AA49" s="92"/>
+      <c r="AB49" s="77"/>
     </row>
-    <row r="50" spans="8:25">
+    <row r="50" spans="8:28">
       <c r="H50" s="63" t="s">
         <v>122</v>
       </c>
       <c r="I50" s="63"/>
-      <c r="J50" s="81">
+      <c r="J50" s="63" t="s">
+        <v>919</v>
+      </c>
+      <c r="K50" s="81">
         <v>0.05</v>
       </c>
-      <c r="K50" s="82"/>
       <c r="L50" s="82"/>
-      <c r="N50" s="62"/>
+      <c r="M50" s="82"/>
       <c r="O50" s="62"/>
       <c r="P50" s="62"/>
       <c r="Q50" s="62"/>
-      <c r="U50" s="63"/>
-      <c r="V50" s="63"/>
-      <c r="W50" s="83"/>
-      <c r="X50" s="92"/>
-      <c r="Y50" s="77"/>
+      <c r="R50" s="62"/>
+      <c r="S50" s="62"/>
+      <c r="W50" s="63"/>
+      <c r="X50" s="63"/>
+      <c r="Y50" s="63"/>
+      <c r="Z50" s="83"/>
+      <c r="AA50" s="92"/>
+      <c r="AB50" s="77"/>
     </row>
-    <row r="51" spans="8:25">
+    <row r="51" spans="8:28">
       <c r="H51" s="63" t="s">
         <v>118</v>
       </c>
       <c r="I51" s="63"/>
-      <c r="J51" s="81">
+      <c r="J51" s="63"/>
+      <c r="K51" s="81">
         <v>0.05</v>
       </c>
-      <c r="K51" s="82"/>
       <c r="L51" s="82"/>
-      <c r="U51" s="63"/>
-      <c r="V51" s="63"/>
-      <c r="W51" s="83"/>
-      <c r="X51" s="92"/>
-      <c r="Y51" s="78"/>
+      <c r="M51" s="82"/>
+      <c r="W51" s="63"/>
+      <c r="X51" s="63"/>
+      <c r="Y51" s="63"/>
+      <c r="Z51" s="83"/>
+      <c r="AA51" s="92"/>
+      <c r="AB51" s="78"/>
     </row>
-    <row r="52" spans="8:25">
+    <row r="52" spans="8:28">
       <c r="H52" s="63" t="s">
         <v>125</v>
       </c>
       <c r="I52" s="63"/>
-      <c r="J52" s="81">
+      <c r="J52" s="63"/>
+      <c r="K52" s="81">
         <v>0.05</v>
       </c>
-      <c r="K52" s="82"/>
       <c r="L52" s="82"/>
-      <c r="U52" s="63"/>
-      <c r="V52" s="63"/>
-      <c r="W52" s="83"/>
-      <c r="X52" s="92"/>
-      <c r="Y52" s="77"/>
+      <c r="M52" s="82"/>
+      <c r="W52" s="63"/>
+      <c r="X52" s="63"/>
+      <c r="Y52" s="63"/>
+      <c r="Z52" s="83"/>
+      <c r="AA52" s="92"/>
+      <c r="AB52" s="77"/>
     </row>
-    <row r="53" spans="8:25">
+    <row r="53" spans="8:28">
       <c r="H53" s="63" t="s">
         <v>479</v>
       </c>
       <c r="I53" s="63"/>
-      <c r="J53" s="81">
+      <c r="J53" s="63"/>
+      <c r="K53" s="81">
         <v>0.05</v>
       </c>
-      <c r="K53" s="82"/>
       <c r="L53" s="82"/>
-      <c r="U53" s="63"/>
-      <c r="V53" s="63"/>
-      <c r="W53" s="83"/>
+      <c r="M53" s="82"/>
+      <c r="W53" s="63"/>
       <c r="X53" s="63"/>
       <c r="Y53" s="63"/>
+      <c r="Z53" s="83"/>
+      <c r="AA53" s="63"/>
+      <c r="AB53" s="63"/>
     </row>
-    <row r="54" spans="8:25">
+    <row r="54" spans="8:28">
       <c r="H54" s="63" t="s">
         <v>111</v>
       </c>
       <c r="I54" s="63"/>
-      <c r="J54" s="81">
+      <c r="J54" s="63" t="s">
+        <v>920</v>
+      </c>
+      <c r="K54" s="81">
         <v>0.05</v>
       </c>
-      <c r="K54" s="82"/>
       <c r="L54" s="82"/>
-      <c r="U54" s="63"/>
-      <c r="V54" s="63"/>
-      <c r="W54" s="83"/>
+      <c r="M54" s="82"/>
+      <c r="W54" s="63"/>
       <c r="X54" s="63"/>
       <c r="Y54" s="63"/>
+      <c r="Z54" s="83"/>
+      <c r="AA54" s="63"/>
+      <c r="AB54" s="63"/>
     </row>
-    <row r="55" spans="8:25">
+    <row r="55" spans="8:28">
       <c r="H55" s="63" t="s">
         <v>124</v>
       </c>
       <c r="I55" s="63"/>
-      <c r="J55" s="81">
+      <c r="J55" s="63"/>
+      <c r="K55" s="81">
         <v>0.05</v>
       </c>
-      <c r="K55" s="82"/>
       <c r="L55" s="82"/>
-      <c r="U55" s="63"/>
-      <c r="V55" s="63"/>
-      <c r="W55" s="83"/>
+      <c r="M55" s="82"/>
+      <c r="W55" s="63"/>
       <c r="X55" s="63"/>
       <c r="Y55" s="63"/>
+      <c r="Z55" s="83"/>
+      <c r="AA55" s="63"/>
+      <c r="AB55" s="63"/>
     </row>
-    <row r="56" spans="8:25">
+    <row r="56" spans="8:28">
       <c r="H56" s="63" t="s">
         <v>114</v>
       </c>
       <c r="I56" s="63"/>
-      <c r="J56" s="81">
+      <c r="J56" s="63"/>
+      <c r="K56" s="81">
         <v>0.05</v>
       </c>
-      <c r="K56" s="82"/>
       <c r="L56" s="82"/>
-      <c r="U56" s="153"/>
-      <c r="V56" s="63"/>
-      <c r="W56" s="83"/>
-      <c r="X56" s="92"/>
-      <c r="Y56" s="77"/>
+      <c r="M56" s="82"/>
+      <c r="W56" s="153"/>
+      <c r="X56" s="63"/>
+      <c r="Y56" s="63"/>
+      <c r="Z56" s="83"/>
+      <c r="AA56" s="92"/>
+      <c r="AB56" s="77"/>
     </row>
-    <row r="57" spans="8:25">
+    <row r="57" spans="8:28">
       <c r="H57" s="63" t="s">
         <v>488</v>
       </c>
       <c r="I57" s="63"/>
-      <c r="J57" s="81">
+      <c r="J57" s="63" t="s">
+        <v>921</v>
+      </c>
+      <c r="K57" s="81">
         <v>0.05</v>
       </c>
-      <c r="K57" s="82"/>
       <c r="L57" s="82"/>
-      <c r="U57" s="153"/>
-      <c r="V57" s="63"/>
-      <c r="W57" s="83"/>
-      <c r="X57" s="92"/>
-      <c r="Y57" s="77"/>
+      <c r="M57" s="82"/>
+      <c r="W57" s="153"/>
+      <c r="X57" s="63"/>
+      <c r="Y57" s="63"/>
+      <c r="Z57" s="83"/>
+      <c r="AA57" s="92"/>
+      <c r="AB57" s="77"/>
     </row>
-    <row r="58" spans="8:25">
+    <row r="58" spans="8:28">
       <c r="H58" s="63" t="s">
         <v>489</v>
       </c>
       <c r="I58" s="63"/>
-      <c r="J58" s="81">
+      <c r="J58" s="63"/>
+      <c r="K58" s="81">
         <v>0.05</v>
       </c>
-      <c r="K58" s="82"/>
       <c r="L58" s="82"/>
-      <c r="U58" s="63"/>
-      <c r="V58" s="63"/>
-      <c r="W58" s="83"/>
-      <c r="X58" s="92"/>
-      <c r="Y58" s="77"/>
+      <c r="M58" s="82"/>
+      <c r="W58" s="63"/>
+      <c r="X58" s="63"/>
+      <c r="Y58" s="63"/>
+      <c r="Z58" s="83"/>
+      <c r="AA58" s="92"/>
+      <c r="AB58" s="77"/>
     </row>
-    <row r="59" spans="8:25">
+    <row r="59" spans="8:28">
       <c r="H59" s="63" t="s">
         <v>123</v>
       </c>
       <c r="I59" s="63"/>
-      <c r="J59" s="81">
+      <c r="J59" s="63"/>
+      <c r="K59" s="81">
         <v>0.05</v>
       </c>
-      <c r="K59" s="82"/>
       <c r="L59" s="82"/>
-      <c r="U59" s="63"/>
-      <c r="V59" s="63"/>
-      <c r="W59" s="83"/>
-      <c r="X59" s="92"/>
-      <c r="Y59" s="77"/>
+      <c r="M59" s="82"/>
+      <c r="W59" s="63"/>
+      <c r="X59" s="63"/>
+      <c r="Y59" s="63"/>
+      <c r="Z59" s="83"/>
+      <c r="AA59" s="92"/>
+      <c r="AB59" s="77"/>
     </row>
-    <row r="60" spans="8:25">
+    <row r="60" spans="8:28">
       <c r="H60" s="63" t="s">
         <v>490</v>
       </c>
       <c r="I60" s="63"/>
-      <c r="J60" s="81">
+      <c r="J60" s="63" t="s">
+        <v>922</v>
+      </c>
+      <c r="K60" s="81">
         <v>0.05</v>
       </c>
-      <c r="K60" s="82"/>
       <c r="L60" s="82"/>
-      <c r="U60" s="215" t="s">
+      <c r="M60" s="82"/>
+      <c r="W60" s="181" t="s">
         <v>553</v>
       </c>
-      <c r="V60" s="215"/>
-      <c r="W60" s="215"/>
-      <c r="X60" s="92">
-        <f>SUM(X49:X59)</f>
+      <c r="X60" s="181"/>
+      <c r="Y60" s="181"/>
+      <c r="Z60" s="181"/>
+      <c r="AA60" s="92">
+        <f>SUM(AA49:AA59)</f>
         <v>0</v>
       </c>
-      <c r="Y60" s="77"/>
+      <c r="AB60" s="77"/>
     </row>
-    <row r="61" spans="8:25">
+    <row r="61" spans="8:28">
       <c r="H61" s="63" t="s">
         <v>491</v>
       </c>
       <c r="I61" s="63"/>
-      <c r="J61" s="81">
+      <c r="J61" s="63"/>
+      <c r="K61" s="81">
         <v>0.05</v>
       </c>
-      <c r="K61" s="82"/>
       <c r="L61" s="82"/>
+      <c r="M61" s="82"/>
     </row>
-    <row r="62" spans="8:25" ht="34.5">
+    <row r="62" spans="8:28" ht="34.5">
       <c r="H62" s="153" t="s">
         <v>717</v>
       </c>
       <c r="I62" s="63"/>
-      <c r="J62" s="81">
+      <c r="J62" s="63" t="s">
+        <v>923</v>
+      </c>
+      <c r="K62" s="81">
         <v>0.05</v>
       </c>
-      <c r="K62" s="82"/>
       <c r="L62" s="82"/>
+      <c r="M62" s="82"/>
     </row>
-    <row r="63" spans="8:25">
+    <row r="63" spans="8:28">
       <c r="H63" s="153" t="s">
         <v>718</v>
       </c>
       <c r="I63" s="63"/>
-      <c r="J63" s="81">
+      <c r="J63" s="63" t="s">
+        <v>924</v>
+      </c>
+      <c r="K63" s="81">
         <v>0.05</v>
       </c>
-      <c r="K63" s="82"/>
       <c r="L63" s="82"/>
+      <c r="M63" s="82"/>
     </row>
-    <row r="64" spans="8:25">
+    <row r="64" spans="8:28">
       <c r="H64" s="153" t="s">
         <v>760</v>
       </c>
       <c r="I64" s="63"/>
-      <c r="J64" s="81">
+      <c r="J64" s="63" t="s">
+        <v>925</v>
+      </c>
+      <c r="K64" s="81">
         <v>0.05</v>
       </c>
-      <c r="K64" s="82"/>
       <c r="L64" s="82"/>
+      <c r="M64" s="82"/>
     </row>
-    <row r="65" spans="8:12">
+    <row r="65" spans="8:13">
       <c r="H65" s="153" t="s">
         <v>855</v>
       </c>
       <c r="I65" s="63"/>
-      <c r="J65" s="81">
+      <c r="J65" s="63" t="s">
+        <v>926</v>
+      </c>
+      <c r="K65" s="81">
         <v>0.05</v>
       </c>
-      <c r="K65" s="82"/>
       <c r="L65" s="82"/>
+      <c r="M65" s="82"/>
     </row>
-    <row r="66" spans="8:12">
+    <row r="66" spans="8:13">
       <c r="H66" s="63"/>
       <c r="I66" s="63"/>
-      <c r="J66" s="81"/>
-      <c r="K66" s="82"/>
+      <c r="J66" s="63"/>
+      <c r="K66" s="81"/>
       <c r="L66" s="82"/>
+      <c r="M66" s="82"/>
     </row>
-    <row r="67" spans="8:12">
-      <c r="H67" s="215" t="s">
+    <row r="67" spans="8:13">
+      <c r="H67" s="181" t="s">
         <v>156</v>
       </c>
-      <c r="I67" s="215"/>
-      <c r="J67" s="215"/>
-      <c r="K67" s="85">
-        <f>SUM(K9:K66)</f>
+      <c r="I67" s="181"/>
+      <c r="J67" s="181"/>
+      <c r="K67" s="181"/>
+      <c r="L67" s="85">
+        <f>SUM(L9:L66)</f>
         <v>0</v>
       </c>
-      <c r="L67" s="85"/>
+      <c r="M67" s="85"/>
     </row>
-    <row r="68" spans="8:12">
+    <row r="68" spans="8:13">
       <c r="H68" s="80"/>
       <c r="I68" s="80"/>
       <c r="J68" s="80"/>
       <c r="K68" s="80"/>
       <c r="L68" s="80"/>
+      <c r="M68" s="80"/>
     </row>
-    <row r="69" spans="8:12">
+    <row r="69" spans="8:13">
       <c r="H69" s="80"/>
       <c r="I69" s="80"/>
       <c r="J69" s="80"/>
       <c r="K69" s="80"/>
       <c r="L69" s="80"/>
+      <c r="M69" s="80"/>
     </row>
-    <row r="70" spans="8:12">
+    <row r="70" spans="8:13">
       <c r="H70" s="80"/>
       <c r="I70" s="80"/>
       <c r="J70" s="80"/>
       <c r="K70" s="80"/>
       <c r="L70" s="80"/>
+      <c r="M70" s="80"/>
     </row>
   </sheetData>
-  <autoFilter ref="H8:L8" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="H9:L58">
+  <autoFilter ref="H8:M8" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="H9:M58">
       <sortCondition ref="H8"/>
     </sortState>
   </autoFilter>
   <mergeCells count="22">
-    <mergeCell ref="H67:J67"/>
-    <mergeCell ref="N4:O4"/>
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="U4:V4"/>
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="W20:Z20"/>
+    <mergeCell ref="W32:AA32"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="H1:M1"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="O3:S3"/>
+    <mergeCell ref="W3:AA3"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="H67:K67"/>
+    <mergeCell ref="O4:P4"/>
+    <mergeCell ref="Q4:S4"/>
+    <mergeCell ref="W4:X4"/>
     <mergeCell ref="H4:I4"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="U44:W44"/>
-    <mergeCell ref="U22:X22"/>
-    <mergeCell ref="U30:W30"/>
-    <mergeCell ref="W4:X4"/>
-    <mergeCell ref="N46:Q46"/>
-    <mergeCell ref="U47:X47"/>
-    <mergeCell ref="U60:W60"/>
-    <mergeCell ref="B9:E9"/>
-    <mergeCell ref="U20:W20"/>
-    <mergeCell ref="U32:X32"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="H1:L1"/>
-    <mergeCell ref="H3:K3"/>
-    <mergeCell ref="N3:Q3"/>
-    <mergeCell ref="U3:X3"/>
-    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="W44:Z44"/>
+    <mergeCell ref="W22:AA22"/>
+    <mergeCell ref="W30:Z30"/>
+    <mergeCell ref="Z4:AA4"/>
+    <mergeCell ref="O46:S46"/>
+    <mergeCell ref="W47:AA47"/>
+    <mergeCell ref="W60:Z60"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9935,16 +10482,16 @@
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="181">
+      <c r="A2" s="196">
         <v>1</v>
       </c>
-      <c r="B2" s="182" t="s">
+      <c r="B2" s="197" t="s">
         <v>559</v>
       </c>
-      <c r="C2" s="182" t="s">
+      <c r="C2" s="197" t="s">
         <v>560</v>
       </c>
-      <c r="D2" s="183" t="s">
+      <c r="D2" s="200" t="s">
         <v>561</v>
       </c>
       <c r="E2" s="130" t="s">
@@ -9955,26 +10502,26 @@
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="181"/>
-      <c r="B3" s="182"/>
-      <c r="C3" s="182"/>
-      <c r="D3" s="182"/>
+      <c r="A3" s="196"/>
+      <c r="B3" s="197"/>
+      <c r="C3" s="197"/>
+      <c r="D3" s="197"/>
       <c r="E3" s="156" t="s">
         <v>337</v>
       </c>
       <c r="F3" s="156"/>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="181">
+      <c r="A4" s="196">
         <v>2</v>
       </c>
-      <c r="B4" s="182" t="s">
+      <c r="B4" s="197" t="s">
         <v>564</v>
       </c>
-      <c r="C4" s="182" t="s">
+      <c r="C4" s="197" t="s">
         <v>338</v>
       </c>
-      <c r="D4" s="183" t="s">
+      <c r="D4" s="200" t="s">
         <v>698</v>
       </c>
       <c r="E4" s="130" t="s">
@@ -9985,26 +10532,26 @@
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="181"/>
-      <c r="B5" s="182"/>
-      <c r="C5" s="182"/>
-      <c r="D5" s="182"/>
+      <c r="A5" s="196"/>
+      <c r="B5" s="197"/>
+      <c r="C5" s="197"/>
+      <c r="D5" s="197"/>
       <c r="E5" s="156" t="s">
         <v>337</v>
       </c>
       <c r="F5" s="156"/>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="181">
+      <c r="A6" s="196">
         <v>3</v>
       </c>
-      <c r="B6" s="204" t="s">
+      <c r="B6" s="205" t="s">
         <v>858</v>
       </c>
-      <c r="C6" s="186" t="s">
+      <c r="C6" s="198" t="s">
         <v>339</v>
       </c>
-      <c r="D6" s="195" t="s">
+      <c r="D6" s="194" t="s">
         <v>566</v>
       </c>
       <c r="E6" s="130" t="s">
@@ -10015,26 +10562,26 @@
       </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="181"/>
-      <c r="B7" s="204"/>
-      <c r="C7" s="186"/>
-      <c r="D7" s="193"/>
+      <c r="A7" s="196"/>
+      <c r="B7" s="205"/>
+      <c r="C7" s="198"/>
+      <c r="D7" s="213"/>
       <c r="E7" s="156" t="s">
         <v>337</v>
       </c>
       <c r="F7" s="156"/>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="181">
+      <c r="A8" s="196">
         <v>4</v>
       </c>
-      <c r="B8" s="182" t="s">
+      <c r="B8" s="197" t="s">
         <v>568</v>
       </c>
-      <c r="C8" s="182" t="s">
+      <c r="C8" s="197" t="s">
         <v>340</v>
       </c>
-      <c r="D8" s="182" t="s">
+      <c r="D8" s="197" t="s">
         <v>699</v>
       </c>
       <c r="E8" s="130" t="s">
@@ -10045,26 +10592,26 @@
       </c>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="181"/>
-      <c r="B9" s="182"/>
-      <c r="C9" s="182"/>
-      <c r="D9" s="182"/>
+      <c r="A9" s="196"/>
+      <c r="B9" s="197"/>
+      <c r="C9" s="197"/>
+      <c r="D9" s="197"/>
       <c r="E9" s="156" t="s">
         <v>337</v>
       </c>
       <c r="F9" s="156"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="181">
+      <c r="A10" s="196">
         <v>5</v>
       </c>
-      <c r="B10" s="200" t="s">
+      <c r="B10" s="212" t="s">
         <v>482</v>
       </c>
-      <c r="C10" s="201" t="s">
+      <c r="C10" s="214" t="s">
         <v>341</v>
       </c>
-      <c r="D10" s="203" t="s">
+      <c r="D10" s="216" t="s">
         <v>700</v>
       </c>
       <c r="E10" s="130" t="s">
@@ -10075,26 +10622,26 @@
       </c>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="181"/>
-      <c r="B11" s="193"/>
-      <c r="C11" s="202"/>
-      <c r="D11" s="202"/>
+      <c r="A11" s="196"/>
+      <c r="B11" s="213"/>
+      <c r="C11" s="215"/>
+      <c r="D11" s="215"/>
       <c r="E11" s="156" t="s">
         <v>337</v>
       </c>
       <c r="F11" s="156"/>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="181">
+      <c r="A12" s="196">
         <v>6</v>
       </c>
-      <c r="B12" s="182" t="s">
+      <c r="B12" s="197" t="s">
         <v>570</v>
       </c>
-      <c r="C12" s="186" t="s">
+      <c r="C12" s="198" t="s">
         <v>343</v>
       </c>
-      <c r="D12" s="183" t="s">
+      <c r="D12" s="200" t="s">
         <v>701</v>
       </c>
       <c r="E12" s="130" t="s">
@@ -10105,26 +10652,26 @@
       </c>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="181"/>
-      <c r="B13" s="182"/>
-      <c r="C13" s="186"/>
-      <c r="D13" s="182"/>
+      <c r="A13" s="196"/>
+      <c r="B13" s="197"/>
+      <c r="C13" s="198"/>
+      <c r="D13" s="197"/>
       <c r="E13" s="156" t="s">
         <v>337</v>
       </c>
       <c r="F13" s="156"/>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="181">
+      <c r="A14" s="196">
         <v>7</v>
       </c>
-      <c r="B14" s="182" t="s">
+      <c r="B14" s="197" t="s">
         <v>571</v>
       </c>
-      <c r="C14" s="182" t="s">
+      <c r="C14" s="197" t="s">
         <v>345</v>
       </c>
-      <c r="D14" s="183" t="s">
+      <c r="D14" s="200" t="s">
         <v>572</v>
       </c>
       <c r="E14" s="130" t="s">
@@ -10135,26 +10682,26 @@
       </c>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="181"/>
-      <c r="B15" s="182"/>
-      <c r="C15" s="182"/>
-      <c r="D15" s="182"/>
+      <c r="A15" s="196"/>
+      <c r="B15" s="197"/>
+      <c r="C15" s="197"/>
+      <c r="D15" s="197"/>
       <c r="E15" s="156" t="s">
         <v>337</v>
       </c>
       <c r="F15" s="156"/>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="181">
+      <c r="A16" s="196">
         <v>8</v>
       </c>
-      <c r="B16" s="182" t="s">
+      <c r="B16" s="197" t="s">
         <v>574</v>
       </c>
-      <c r="C16" s="182" t="s">
+      <c r="C16" s="197" t="s">
         <v>575</v>
       </c>
-      <c r="D16" s="183" t="s">
+      <c r="D16" s="200" t="s">
         <v>883</v>
       </c>
       <c r="E16" s="130" t="s">
@@ -10165,26 +10712,26 @@
       </c>
     </row>
     <row r="17" spans="1:6">
-      <c r="A17" s="181"/>
-      <c r="B17" s="182"/>
-      <c r="C17" s="182"/>
-      <c r="D17" s="182"/>
+      <c r="A17" s="196"/>
+      <c r="B17" s="197"/>
+      <c r="C17" s="197"/>
+      <c r="D17" s="197"/>
       <c r="E17" s="156" t="s">
         <v>337</v>
       </c>
       <c r="F17" s="156"/>
     </row>
     <row r="18" spans="1:6">
-      <c r="A18" s="181">
+      <c r="A18" s="196">
         <v>9</v>
       </c>
-      <c r="B18" s="182" t="s">
+      <c r="B18" s="197" t="s">
         <v>576</v>
       </c>
-      <c r="C18" s="182" t="s">
+      <c r="C18" s="197" t="s">
         <v>347</v>
       </c>
-      <c r="D18" s="183" t="s">
+      <c r="D18" s="200" t="s">
         <v>884</v>
       </c>
       <c r="E18" s="130" t="s">
@@ -10195,26 +10742,26 @@
       </c>
     </row>
     <row r="19" spans="1:6">
-      <c r="A19" s="181"/>
-      <c r="B19" s="182"/>
-      <c r="C19" s="182"/>
-      <c r="D19" s="182"/>
+      <c r="A19" s="196"/>
+      <c r="B19" s="197"/>
+      <c r="C19" s="197"/>
+      <c r="D19" s="197"/>
       <c r="E19" s="156" t="s">
         <v>337</v>
       </c>
       <c r="F19" s="156"/>
     </row>
     <row r="20" spans="1:6">
-      <c r="A20" s="181">
+      <c r="A20" s="196">
         <v>10</v>
       </c>
-      <c r="B20" s="182" t="s">
+      <c r="B20" s="197" t="s">
         <v>577</v>
       </c>
-      <c r="C20" s="182" t="s">
+      <c r="C20" s="197" t="s">
         <v>349</v>
       </c>
-      <c r="D20" s="183" t="s">
+      <c r="D20" s="200" t="s">
         <v>702</v>
       </c>
       <c r="E20" s="130" t="s">
@@ -10225,26 +10772,26 @@
       </c>
     </row>
     <row r="21" spans="1:6">
-      <c r="A21" s="181"/>
-      <c r="B21" s="182"/>
-      <c r="C21" s="182"/>
-      <c r="D21" s="182"/>
+      <c r="A21" s="196"/>
+      <c r="B21" s="197"/>
+      <c r="C21" s="197"/>
+      <c r="D21" s="197"/>
       <c r="E21" s="156" t="s">
         <v>337</v>
       </c>
       <c r="F21" s="156"/>
     </row>
     <row r="22" spans="1:6">
-      <c r="A22" s="181">
+      <c r="A22" s="196">
         <v>11</v>
       </c>
-      <c r="B22" s="182" t="s">
+      <c r="B22" s="197" t="s">
         <v>579</v>
       </c>
-      <c r="C22" s="182" t="s">
+      <c r="C22" s="197" t="s">
         <v>350</v>
       </c>
-      <c r="D22" s="183" t="s">
+      <c r="D22" s="200" t="s">
         <v>703</v>
       </c>
       <c r="E22" s="130" t="s">
@@ -10255,26 +10802,26 @@
       </c>
     </row>
     <row r="23" spans="1:6">
-      <c r="A23" s="181"/>
-      <c r="B23" s="182"/>
-      <c r="C23" s="182"/>
-      <c r="D23" s="182"/>
+      <c r="A23" s="196"/>
+      <c r="B23" s="197"/>
+      <c r="C23" s="197"/>
+      <c r="D23" s="197"/>
       <c r="E23" s="156" t="s">
         <v>337</v>
       </c>
       <c r="F23" s="156"/>
     </row>
     <row r="24" spans="1:6">
-      <c r="A24" s="181">
+      <c r="A24" s="196">
         <v>12</v>
       </c>
-      <c r="B24" s="200" t="s">
+      <c r="B24" s="212" t="s">
         <v>581</v>
       </c>
-      <c r="C24" s="201" t="s">
+      <c r="C24" s="214" t="s">
         <v>582</v>
       </c>
-      <c r="D24" s="195" t="s">
+      <c r="D24" s="194" t="s">
         <v>583</v>
       </c>
       <c r="E24" s="130" t="s">
@@ -10285,26 +10832,26 @@
       </c>
     </row>
     <row r="25" spans="1:6">
-      <c r="A25" s="181"/>
-      <c r="B25" s="193"/>
-      <c r="C25" s="202"/>
-      <c r="D25" s="202"/>
+      <c r="A25" s="196"/>
+      <c r="B25" s="213"/>
+      <c r="C25" s="215"/>
+      <c r="D25" s="215"/>
       <c r="E25" s="156" t="s">
         <v>337</v>
       </c>
       <c r="F25" s="156"/>
     </row>
     <row r="26" spans="1:6">
-      <c r="A26" s="181">
+      <c r="A26" s="196">
         <v>13</v>
       </c>
-      <c r="B26" s="182" t="s">
+      <c r="B26" s="197" t="s">
         <v>585</v>
       </c>
-      <c r="C26" s="182" t="s">
+      <c r="C26" s="197" t="s">
         <v>351</v>
       </c>
-      <c r="D26" s="183" t="s">
+      <c r="D26" s="200" t="s">
         <v>704</v>
       </c>
       <c r="E26" s="130" t="s">
@@ -10315,26 +10862,26 @@
       </c>
     </row>
     <row r="27" spans="1:6">
-      <c r="A27" s="181"/>
-      <c r="B27" s="182"/>
-      <c r="C27" s="182"/>
-      <c r="D27" s="182"/>
+      <c r="A27" s="196"/>
+      <c r="B27" s="197"/>
+      <c r="C27" s="197"/>
+      <c r="D27" s="197"/>
       <c r="E27" s="156" t="s">
         <v>337</v>
       </c>
       <c r="F27" s="156"/>
     </row>
     <row r="28" spans="1:6">
-      <c r="A28" s="181">
+      <c r="A28" s="196">
         <v>14</v>
       </c>
-      <c r="B28" s="182" t="s">
+      <c r="B28" s="197" t="s">
         <v>586</v>
       </c>
-      <c r="C28" s="186" t="s">
+      <c r="C28" s="198" t="s">
         <v>353</v>
       </c>
-      <c r="D28" s="183" t="s">
+      <c r="D28" s="200" t="s">
         <v>885</v>
       </c>
       <c r="E28" s="156" t="s">
@@ -10345,10 +10892,10 @@
       </c>
     </row>
     <row r="29" spans="1:6">
-      <c r="A29" s="181"/>
-      <c r="B29" s="182"/>
-      <c r="C29" s="186"/>
-      <c r="D29" s="182"/>
+      <c r="A29" s="196"/>
+      <c r="B29" s="197"/>
+      <c r="C29" s="198"/>
+      <c r="D29" s="197"/>
       <c r="E29" s="156" t="s">
         <v>337</v>
       </c>
@@ -10358,13 +10905,13 @@
       <c r="A30" s="188">
         <v>15</v>
       </c>
-      <c r="B30" s="191" t="s">
+      <c r="B30" s="190" t="s">
         <v>733</v>
       </c>
-      <c r="C30" s="194" t="s">
+      <c r="C30" s="219" t="s">
         <v>688</v>
       </c>
-      <c r="D30" s="195" t="s">
+      <c r="D30" s="194" t="s">
         <v>587</v>
       </c>
       <c r="E30" s="130" t="s">
@@ -10375,10 +10922,10 @@
       </c>
     </row>
     <row r="31" spans="1:6">
-      <c r="A31" s="189"/>
-      <c r="B31" s="192"/>
-      <c r="C31" s="192"/>
-      <c r="D31" s="196"/>
+      <c r="A31" s="217"/>
+      <c r="B31" s="218"/>
+      <c r="C31" s="218"/>
+      <c r="D31" s="220"/>
       <c r="E31" s="132" t="s">
         <v>337</v>
       </c>
@@ -10387,10 +10934,10 @@
       </c>
     </row>
     <row r="32" spans="1:6" ht="93.75">
-      <c r="A32" s="190"/>
-      <c r="B32" s="193"/>
-      <c r="C32" s="193"/>
-      <c r="D32" s="197"/>
+      <c r="A32" s="189"/>
+      <c r="B32" s="213"/>
+      <c r="C32" s="213"/>
+      <c r="D32" s="195"/>
       <c r="E32" s="161" t="s">
         <v>734</v>
       </c>
@@ -10399,16 +10946,16 @@
       </c>
     </row>
     <row r="33" spans="1:6">
-      <c r="A33" s="181">
+      <c r="A33" s="196">
         <v>16</v>
       </c>
-      <c r="B33" s="182" t="s">
+      <c r="B33" s="197" t="s">
         <v>589</v>
       </c>
-      <c r="C33" s="182" t="s">
+      <c r="C33" s="197" t="s">
         <v>381</v>
       </c>
-      <c r="D33" s="183" t="s">
+      <c r="D33" s="200" t="s">
         <v>705</v>
       </c>
       <c r="E33" s="130" t="s">
@@ -10419,26 +10966,26 @@
       </c>
     </row>
     <row r="34" spans="1:6">
-      <c r="A34" s="181"/>
-      <c r="B34" s="182"/>
-      <c r="C34" s="182"/>
-      <c r="D34" s="182"/>
+      <c r="A34" s="196"/>
+      <c r="B34" s="197"/>
+      <c r="C34" s="197"/>
+      <c r="D34" s="197"/>
       <c r="E34" s="156" t="s">
         <v>337</v>
       </c>
       <c r="F34" s="156"/>
     </row>
     <row r="35" spans="1:6">
-      <c r="A35" s="181">
+      <c r="A35" s="196">
         <v>17</v>
       </c>
-      <c r="B35" s="182" t="s">
+      <c r="B35" s="197" t="s">
         <v>591</v>
       </c>
-      <c r="C35" s="186" t="s">
+      <c r="C35" s="198" t="s">
         <v>356</v>
       </c>
-      <c r="D35" s="183" t="s">
+      <c r="D35" s="200" t="s">
         <v>706</v>
       </c>
       <c r="E35" s="130" t="s">
@@ -10449,26 +10996,26 @@
       </c>
     </row>
     <row r="36" spans="1:6">
-      <c r="A36" s="181"/>
-      <c r="B36" s="182"/>
-      <c r="C36" s="186"/>
-      <c r="D36" s="182"/>
+      <c r="A36" s="196"/>
+      <c r="B36" s="197"/>
+      <c r="C36" s="198"/>
+      <c r="D36" s="197"/>
       <c r="E36" s="156" t="s">
         <v>337</v>
       </c>
       <c r="F36" s="156"/>
     </row>
     <row r="37" spans="1:6">
-      <c r="A37" s="181">
+      <c r="A37" s="196">
         <v>18</v>
       </c>
-      <c r="B37" s="204" t="s">
+      <c r="B37" s="205" t="s">
         <v>502</v>
       </c>
-      <c r="C37" s="182" t="s">
+      <c r="C37" s="197" t="s">
         <v>357</v>
       </c>
-      <c r="D37" s="183" t="s">
+      <c r="D37" s="200" t="s">
         <v>707</v>
       </c>
       <c r="E37" s="132" t="s">
@@ -10479,10 +11026,10 @@
       </c>
     </row>
     <row r="38" spans="1:6">
-      <c r="A38" s="181"/>
-      <c r="B38" s="182"/>
-      <c r="C38" s="182"/>
-      <c r="D38" s="182"/>
+      <c r="A38" s="196"/>
+      <c r="B38" s="197"/>
+      <c r="C38" s="197"/>
+      <c r="D38" s="197"/>
       <c r="E38" s="156" t="s">
         <v>337</v>
       </c>
@@ -10491,16 +11038,16 @@
       </c>
     </row>
     <row r="39" spans="1:6">
-      <c r="A39" s="181">
+      <c r="A39" s="196">
         <v>19</v>
       </c>
-      <c r="B39" s="182" t="s">
+      <c r="B39" s="197" t="s">
         <v>595</v>
       </c>
-      <c r="C39" s="182" t="s">
+      <c r="C39" s="197" t="s">
         <v>358</v>
       </c>
-      <c r="D39" s="183" t="s">
+      <c r="D39" s="200" t="s">
         <v>708</v>
       </c>
       <c r="E39" s="130" t="s">
@@ -10511,26 +11058,26 @@
       </c>
     </row>
     <row r="40" spans="1:6">
-      <c r="A40" s="181"/>
-      <c r="B40" s="182"/>
-      <c r="C40" s="182"/>
-      <c r="D40" s="182"/>
+      <c r="A40" s="196"/>
+      <c r="B40" s="197"/>
+      <c r="C40" s="197"/>
+      <c r="D40" s="197"/>
       <c r="E40" s="156" t="s">
         <v>337</v>
       </c>
       <c r="F40" s="156"/>
     </row>
     <row r="41" spans="1:6">
-      <c r="A41" s="181">
+      <c r="A41" s="196">
         <v>20</v>
       </c>
-      <c r="B41" s="182" t="s">
+      <c r="B41" s="197" t="s">
         <v>596</v>
       </c>
-      <c r="C41" s="182" t="s">
+      <c r="C41" s="197" t="s">
         <v>359</v>
       </c>
-      <c r="D41" s="183" t="s">
+      <c r="D41" s="200" t="s">
         <v>709</v>
       </c>
       <c r="E41" s="130" t="s">
@@ -10541,26 +11088,26 @@
       </c>
     </row>
     <row r="42" spans="1:6">
-      <c r="A42" s="181"/>
-      <c r="B42" s="182"/>
-      <c r="C42" s="182"/>
-      <c r="D42" s="182"/>
+      <c r="A42" s="196"/>
+      <c r="B42" s="197"/>
+      <c r="C42" s="197"/>
+      <c r="D42" s="197"/>
       <c r="E42" s="156" t="s">
         <v>337</v>
       </c>
       <c r="F42" s="156"/>
     </row>
     <row r="43" spans="1:6">
-      <c r="A43" s="181">
+      <c r="A43" s="196">
         <v>21</v>
       </c>
-      <c r="B43" s="182" t="s">
+      <c r="B43" s="197" t="s">
         <v>598</v>
       </c>
-      <c r="C43" s="182" t="s">
+      <c r="C43" s="197" t="s">
         <v>599</v>
       </c>
-      <c r="D43" s="183" t="s">
+      <c r="D43" s="200" t="s">
         <v>600</v>
       </c>
       <c r="E43" s="130" t="s">
@@ -10571,26 +11118,26 @@
       </c>
     </row>
     <row r="44" spans="1:6">
-      <c r="A44" s="181"/>
-      <c r="B44" s="182"/>
-      <c r="C44" s="182"/>
-      <c r="D44" s="182"/>
+      <c r="A44" s="196"/>
+      <c r="B44" s="197"/>
+      <c r="C44" s="197"/>
+      <c r="D44" s="197"/>
       <c r="E44" s="156" t="s">
         <v>337</v>
       </c>
       <c r="F44" s="156"/>
     </row>
     <row r="45" spans="1:6">
-      <c r="A45" s="181">
+      <c r="A45" s="196">
         <v>22</v>
       </c>
-      <c r="B45" s="182" t="s">
+      <c r="B45" s="197" t="s">
         <v>602</v>
       </c>
-      <c r="C45" s="182" t="s">
+      <c r="C45" s="197" t="s">
         <v>360</v>
       </c>
-      <c r="D45" s="183" t="s">
+      <c r="D45" s="200" t="s">
         <v>710</v>
       </c>
       <c r="E45" s="130" t="s">
@@ -10601,26 +11148,26 @@
       </c>
     </row>
     <row r="46" spans="1:6">
-      <c r="A46" s="181"/>
-      <c r="B46" s="182"/>
-      <c r="C46" s="182"/>
-      <c r="D46" s="182"/>
+      <c r="A46" s="196"/>
+      <c r="B46" s="197"/>
+      <c r="C46" s="197"/>
+      <c r="D46" s="197"/>
       <c r="E46" s="156" t="s">
         <v>337</v>
       </c>
       <c r="F46" s="156"/>
     </row>
     <row r="47" spans="1:6">
-      <c r="A47" s="181">
+      <c r="A47" s="196">
         <v>23</v>
       </c>
-      <c r="B47" s="182" t="s">
+      <c r="B47" s="197" t="s">
         <v>604</v>
       </c>
-      <c r="C47" s="182" t="s">
+      <c r="C47" s="197" t="s">
         <v>361</v>
       </c>
-      <c r="D47" s="183" t="s">
+      <c r="D47" s="200" t="s">
         <v>711</v>
       </c>
       <c r="E47" s="130" t="s">
@@ -10631,26 +11178,26 @@
       </c>
     </row>
     <row r="48" spans="1:6">
-      <c r="A48" s="181"/>
-      <c r="B48" s="182"/>
-      <c r="C48" s="182"/>
-      <c r="D48" s="182"/>
+      <c r="A48" s="196"/>
+      <c r="B48" s="197"/>
+      <c r="C48" s="197"/>
+      <c r="D48" s="197"/>
       <c r="E48" s="156" t="s">
         <v>337</v>
       </c>
       <c r="F48" s="156"/>
     </row>
     <row r="49" spans="1:6">
-      <c r="A49" s="181">
+      <c r="A49" s="196">
         <v>24</v>
       </c>
-      <c r="B49" s="182" t="s">
+      <c r="B49" s="197" t="s">
         <v>605</v>
       </c>
-      <c r="C49" s="182" t="s">
+      <c r="C49" s="197" t="s">
         <v>363</v>
       </c>
-      <c r="D49" s="183" t="s">
+      <c r="D49" s="200" t="s">
         <v>712</v>
       </c>
       <c r="E49" s="130" t="s">
@@ -10661,26 +11208,26 @@
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="A50" s="181"/>
-      <c r="B50" s="182"/>
-      <c r="C50" s="182"/>
-      <c r="D50" s="182"/>
+      <c r="A50" s="196"/>
+      <c r="B50" s="197"/>
+      <c r="C50" s="197"/>
+      <c r="D50" s="197"/>
       <c r="E50" s="156" t="s">
         <v>337</v>
       </c>
       <c r="F50" s="156"/>
     </row>
     <row r="51" spans="1:6">
-      <c r="A51" s="181">
+      <c r="A51" s="196">
         <v>25</v>
       </c>
-      <c r="B51" s="182" t="s">
+      <c r="B51" s="197" t="s">
         <v>607</v>
       </c>
-      <c r="C51" s="182" t="s">
+      <c r="C51" s="197" t="s">
         <v>364</v>
       </c>
-      <c r="D51" s="182" t="s">
+      <c r="D51" s="197" t="s">
         <v>713</v>
       </c>
       <c r="E51" s="130" t="s">
@@ -10691,26 +11238,26 @@
       </c>
     </row>
     <row r="52" spans="1:6">
-      <c r="A52" s="181"/>
-      <c r="B52" s="182"/>
-      <c r="C52" s="182"/>
-      <c r="D52" s="182"/>
+      <c r="A52" s="196"/>
+      <c r="B52" s="197"/>
+      <c r="C52" s="197"/>
+      <c r="D52" s="197"/>
       <c r="E52" s="156" t="s">
         <v>337</v>
       </c>
       <c r="F52" s="156"/>
     </row>
     <row r="53" spans="1:6">
-      <c r="A53" s="181">
+      <c r="A53" s="196">
         <v>26</v>
       </c>
-      <c r="B53" s="204" t="s">
+      <c r="B53" s="205" t="s">
         <v>609</v>
       </c>
-      <c r="C53" s="182" t="s">
+      <c r="C53" s="197" t="s">
         <v>368</v>
       </c>
-      <c r="D53" s="183" t="s">
+      <c r="D53" s="200" t="s">
         <v>714</v>
       </c>
       <c r="E53" s="130" t="s">
@@ -10721,26 +11268,26 @@
       </c>
     </row>
     <row r="54" spans="1:6">
-      <c r="A54" s="181"/>
-      <c r="B54" s="182"/>
-      <c r="C54" s="182"/>
-      <c r="D54" s="182"/>
+      <c r="A54" s="196"/>
+      <c r="B54" s="197"/>
+      <c r="C54" s="197"/>
+      <c r="D54" s="197"/>
       <c r="E54" s="156" t="s">
         <v>337</v>
       </c>
       <c r="F54" s="156"/>
     </row>
     <row r="55" spans="1:6">
-      <c r="A55" s="181">
+      <c r="A55" s="196">
         <v>27</v>
       </c>
-      <c r="B55" s="183" t="s">
+      <c r="B55" s="200" t="s">
         <v>610</v>
       </c>
-      <c r="C55" s="187" t="s">
+      <c r="C55" s="203" t="s">
         <v>611</v>
       </c>
-      <c r="D55" s="187" t="s">
+      <c r="D55" s="203" t="s">
         <v>612</v>
       </c>
       <c r="E55" s="156" t="s">
@@ -10751,10 +11298,10 @@
       </c>
     </row>
     <row r="56" spans="1:6">
-      <c r="A56" s="181"/>
-      <c r="B56" s="183"/>
-      <c r="C56" s="187"/>
-      <c r="D56" s="186"/>
+      <c r="A56" s="196"/>
+      <c r="B56" s="200"/>
+      <c r="C56" s="203"/>
+      <c r="D56" s="198"/>
       <c r="E56" s="132" t="s">
         <v>337</v>
       </c>
@@ -10763,16 +11310,16 @@
       </c>
     </row>
     <row r="57" spans="1:6">
-      <c r="A57" s="181">
+      <c r="A57" s="196">
         <v>28</v>
       </c>
-      <c r="B57" s="210" t="s">
+      <c r="B57" s="206" t="s">
         <v>613</v>
       </c>
-      <c r="C57" s="187" t="s">
+      <c r="C57" s="203" t="s">
         <v>614</v>
       </c>
-      <c r="D57" s="187" t="s">
+      <c r="D57" s="203" t="s">
         <v>615</v>
       </c>
       <c r="E57" s="156" t="s">
@@ -10781,10 +11328,10 @@
       <c r="F57" s="156"/>
     </row>
     <row r="58" spans="1:6">
-      <c r="A58" s="181"/>
-      <c r="B58" s="183"/>
-      <c r="C58" s="187"/>
-      <c r="D58" s="186"/>
+      <c r="A58" s="196"/>
+      <c r="B58" s="200"/>
+      <c r="C58" s="203"/>
+      <c r="D58" s="198"/>
       <c r="E58" s="156" t="s">
         <v>337</v>
       </c>
@@ -10793,16 +11340,16 @@
       </c>
     </row>
     <row r="59" spans="1:6">
-      <c r="A59" s="181">
+      <c r="A59" s="196">
         <v>29</v>
       </c>
-      <c r="B59" s="210" t="s">
+      <c r="B59" s="206" t="s">
         <v>617</v>
       </c>
-      <c r="C59" s="187" t="s">
+      <c r="C59" s="203" t="s">
         <v>618</v>
       </c>
-      <c r="D59" s="187" t="s">
+      <c r="D59" s="203" t="s">
         <v>619</v>
       </c>
       <c r="E59" s="156" t="s">
@@ -10813,26 +11360,26 @@
       </c>
     </row>
     <row r="60" spans="1:6">
-      <c r="A60" s="181"/>
-      <c r="B60" s="183"/>
-      <c r="C60" s="187"/>
-      <c r="D60" s="186"/>
+      <c r="A60" s="196"/>
+      <c r="B60" s="200"/>
+      <c r="C60" s="203"/>
+      <c r="D60" s="198"/>
       <c r="E60" s="156" t="s">
         <v>337</v>
       </c>
       <c r="F60" s="157"/>
     </row>
     <row r="61" spans="1:6">
-      <c r="A61" s="181">
+      <c r="A61" s="196">
         <v>30</v>
       </c>
-      <c r="B61" s="210" t="s">
+      <c r="B61" s="206" t="s">
         <v>769</v>
       </c>
-      <c r="C61" s="187" t="s">
+      <c r="C61" s="203" t="s">
         <v>765</v>
       </c>
-      <c r="D61" s="183" t="s">
+      <c r="D61" s="200" t="s">
         <v>766</v>
       </c>
       <c r="E61" s="156" t="s">
@@ -10841,10 +11388,10 @@
       <c r="F61" s="156"/>
     </row>
     <row r="62" spans="1:6">
-      <c r="A62" s="181"/>
-      <c r="B62" s="183"/>
-      <c r="C62" s="187"/>
-      <c r="D62" s="186"/>
+      <c r="A62" s="196"/>
+      <c r="B62" s="200"/>
+      <c r="C62" s="203"/>
+      <c r="D62" s="198"/>
       <c r="E62" s="156" t="s">
         <v>337</v>
       </c>
@@ -10853,16 +11400,16 @@
       </c>
     </row>
     <row r="63" spans="1:6">
-      <c r="A63" s="181">
+      <c r="A63" s="196">
         <v>31</v>
       </c>
-      <c r="B63" s="204" t="s">
+      <c r="B63" s="205" t="s">
         <v>382</v>
       </c>
-      <c r="C63" s="186" t="s">
+      <c r="C63" s="198" t="s">
         <v>383</v>
       </c>
-      <c r="D63" s="187" t="s">
+      <c r="D63" s="203" t="s">
         <v>715</v>
       </c>
       <c r="E63" s="156" t="s">
@@ -10873,26 +11420,26 @@
       </c>
     </row>
     <row r="64" spans="1:6">
-      <c r="A64" s="181"/>
-      <c r="B64" s="204"/>
-      <c r="C64" s="186"/>
-      <c r="D64" s="186"/>
+      <c r="A64" s="196"/>
+      <c r="B64" s="205"/>
+      <c r="C64" s="198"/>
+      <c r="D64" s="198"/>
       <c r="E64" s="156" t="s">
         <v>337</v>
       </c>
       <c r="F64" s="156"/>
     </row>
     <row r="65" spans="1:6">
-      <c r="A65" s="181">
+      <c r="A65" s="196">
         <v>32</v>
       </c>
-      <c r="B65" s="204" t="s">
+      <c r="B65" s="205" t="s">
         <v>622</v>
       </c>
-      <c r="C65" s="186" t="s">
+      <c r="C65" s="198" t="s">
         <v>623</v>
       </c>
-      <c r="D65" s="187" t="s">
+      <c r="D65" s="203" t="s">
         <v>624</v>
       </c>
       <c r="E65" s="156" t="s">
@@ -10903,26 +11450,26 @@
       </c>
     </row>
     <row r="66" spans="1:6">
-      <c r="A66" s="181"/>
-      <c r="B66" s="204"/>
-      <c r="C66" s="186"/>
-      <c r="D66" s="186"/>
+      <c r="A66" s="196"/>
+      <c r="B66" s="205"/>
+      <c r="C66" s="198"/>
+      <c r="D66" s="198"/>
       <c r="E66" s="156" t="s">
         <v>337</v>
       </c>
       <c r="F66" s="156"/>
     </row>
     <row r="67" spans="1:6">
-      <c r="A67" s="181">
+      <c r="A67" s="196">
         <v>33</v>
       </c>
-      <c r="B67" s="204" t="s">
+      <c r="B67" s="205" t="s">
         <v>625</v>
       </c>
-      <c r="C67" s="186" t="s">
+      <c r="C67" s="198" t="s">
         <v>626</v>
       </c>
-      <c r="D67" s="187" t="s">
+      <c r="D67" s="203" t="s">
         <v>627</v>
       </c>
       <c r="E67" s="156" t="s">
@@ -10933,26 +11480,26 @@
       </c>
     </row>
     <row r="68" spans="1:6">
-      <c r="A68" s="181"/>
-      <c r="B68" s="204"/>
-      <c r="C68" s="186"/>
-      <c r="D68" s="186"/>
+      <c r="A68" s="196"/>
+      <c r="B68" s="205"/>
+      <c r="C68" s="198"/>
+      <c r="D68" s="198"/>
       <c r="E68" s="156" t="s">
         <v>337</v>
       </c>
       <c r="F68" s="156"/>
     </row>
     <row r="69" spans="1:6">
-      <c r="A69" s="181">
+      <c r="A69" s="196">
         <v>34</v>
       </c>
-      <c r="B69" s="204" t="s">
+      <c r="B69" s="205" t="s">
         <v>629</v>
       </c>
-      <c r="C69" s="182" t="s">
+      <c r="C69" s="197" t="s">
         <v>630</v>
       </c>
-      <c r="D69" s="187" t="s">
+      <c r="D69" s="203" t="s">
         <v>631</v>
       </c>
       <c r="E69" s="156" t="s">
@@ -10963,26 +11510,26 @@
       </c>
     </row>
     <row r="70" spans="1:6">
-      <c r="A70" s="181"/>
-      <c r="B70" s="204"/>
-      <c r="C70" s="186"/>
-      <c r="D70" s="186"/>
+      <c r="A70" s="196"/>
+      <c r="B70" s="205"/>
+      <c r="C70" s="198"/>
+      <c r="D70" s="198"/>
       <c r="E70" s="156" t="s">
         <v>337</v>
       </c>
       <c r="F70" s="156"/>
     </row>
     <row r="71" spans="1:6">
-      <c r="A71" s="181">
+      <c r="A71" s="196">
         <v>35</v>
       </c>
-      <c r="B71" s="198" t="s">
+      <c r="B71" s="199" t="s">
         <v>633</v>
       </c>
-      <c r="C71" s="186" t="s">
+      <c r="C71" s="198" t="s">
         <v>634</v>
       </c>
-      <c r="D71" s="187" t="s">
+      <c r="D71" s="203" t="s">
         <v>635</v>
       </c>
       <c r="E71" s="156" t="s">
@@ -10993,26 +11540,26 @@
       </c>
     </row>
     <row r="72" spans="1:6">
-      <c r="A72" s="181"/>
-      <c r="B72" s="182"/>
-      <c r="C72" s="186"/>
-      <c r="D72" s="186"/>
+      <c r="A72" s="196"/>
+      <c r="B72" s="197"/>
+      <c r="C72" s="198"/>
+      <c r="D72" s="198"/>
       <c r="E72" s="156" t="s">
         <v>337</v>
       </c>
       <c r="F72" s="156"/>
     </row>
     <row r="73" spans="1:6">
-      <c r="A73" s="181">
+      <c r="A73" s="196">
         <v>36</v>
       </c>
-      <c r="B73" s="198" t="s">
+      <c r="B73" s="199" t="s">
         <v>637</v>
       </c>
-      <c r="C73" s="186" t="s">
+      <c r="C73" s="198" t="s">
         <v>638</v>
       </c>
-      <c r="D73" s="183" t="s">
+      <c r="D73" s="200" t="s">
         <v>761</v>
       </c>
       <c r="E73" s="156" t="s">
@@ -11023,26 +11570,26 @@
       </c>
     </row>
     <row r="74" spans="1:6">
-      <c r="A74" s="181"/>
-      <c r="B74" s="182"/>
-      <c r="C74" s="186"/>
-      <c r="D74" s="182"/>
+      <c r="A74" s="196"/>
+      <c r="B74" s="197"/>
+      <c r="C74" s="198"/>
+      <c r="D74" s="197"/>
       <c r="E74" s="156" t="s">
         <v>337</v>
       </c>
       <c r="F74" s="156"/>
     </row>
     <row r="75" spans="1:6" s="165" customFormat="1">
-      <c r="A75" s="205">
+      <c r="A75" s="207">
         <v>37</v>
       </c>
-      <c r="B75" s="206" t="s">
+      <c r="B75" s="208" t="s">
         <v>837</v>
       </c>
-      <c r="C75" s="208" t="s">
+      <c r="C75" s="210" t="s">
         <v>639</v>
       </c>
-      <c r="D75" s="209" t="s">
+      <c r="D75" s="211" t="s">
         <v>838</v>
       </c>
       <c r="E75" s="164" t="s">
@@ -11053,26 +11600,26 @@
       </c>
     </row>
     <row r="76" spans="1:6" s="165" customFormat="1">
-      <c r="A76" s="205"/>
-      <c r="B76" s="207"/>
-      <c r="C76" s="208"/>
-      <c r="D76" s="208"/>
+      <c r="A76" s="207"/>
+      <c r="B76" s="209"/>
+      <c r="C76" s="210"/>
+      <c r="D76" s="210"/>
       <c r="E76" s="164" t="s">
         <v>337</v>
       </c>
       <c r="F76" s="164"/>
     </row>
     <row r="77" spans="1:6">
-      <c r="A77" s="181">
+      <c r="A77" s="196">
         <v>38</v>
       </c>
-      <c r="B77" s="204" t="s">
+      <c r="B77" s="205" t="s">
         <v>641</v>
       </c>
-      <c r="C77" s="186" t="s">
+      <c r="C77" s="198" t="s">
         <v>642</v>
       </c>
-      <c r="D77" s="187" t="s">
+      <c r="D77" s="203" t="s">
         <v>643</v>
       </c>
       <c r="E77" s="156" t="s">
@@ -11083,26 +11630,26 @@
       </c>
     </row>
     <row r="78" spans="1:6">
-      <c r="A78" s="181"/>
-      <c r="B78" s="182"/>
-      <c r="C78" s="186"/>
-      <c r="D78" s="186"/>
+      <c r="A78" s="196"/>
+      <c r="B78" s="197"/>
+      <c r="C78" s="198"/>
+      <c r="D78" s="198"/>
       <c r="E78" s="156" t="s">
         <v>337</v>
       </c>
       <c r="F78" s="156"/>
     </row>
     <row r="79" spans="1:6">
-      <c r="A79" s="181">
+      <c r="A79" s="196">
         <v>39</v>
       </c>
-      <c r="B79" s="182" t="s">
+      <c r="B79" s="197" t="s">
         <v>645</v>
       </c>
-      <c r="C79" s="186" t="s">
+      <c r="C79" s="198" t="s">
         <v>645</v>
       </c>
-      <c r="D79" s="183" t="s">
+      <c r="D79" s="200" t="s">
         <v>646</v>
       </c>
       <c r="E79" s="156" t="s">
@@ -11113,26 +11660,26 @@
       </c>
     </row>
     <row r="80" spans="1:6">
-      <c r="A80" s="181"/>
-      <c r="B80" s="182"/>
-      <c r="C80" s="186"/>
-      <c r="D80" s="182"/>
+      <c r="A80" s="196"/>
+      <c r="B80" s="197"/>
+      <c r="C80" s="198"/>
+      <c r="D80" s="197"/>
       <c r="E80" s="156" t="s">
         <v>337</v>
       </c>
       <c r="F80" s="156"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="A81" s="181">
+      <c r="A81" s="196">
         <v>40</v>
       </c>
-      <c r="B81" s="198" t="s">
+      <c r="B81" s="199" t="s">
         <v>648</v>
       </c>
-      <c r="C81" s="186" t="s">
+      <c r="C81" s="198" t="s">
         <v>649</v>
       </c>
-      <c r="D81" s="183" t="s">
+      <c r="D81" s="200" t="s">
         <v>650</v>
       </c>
       <c r="E81" s="156" t="s">
@@ -11143,26 +11690,26 @@
       </c>
     </row>
     <row r="82" spans="1:6">
-      <c r="A82" s="181"/>
-      <c r="B82" s="182"/>
-      <c r="C82" s="186"/>
-      <c r="D82" s="182"/>
+      <c r="A82" s="196"/>
+      <c r="B82" s="197"/>
+      <c r="C82" s="198"/>
+      <c r="D82" s="197"/>
       <c r="E82" s="156" t="s">
         <v>337</v>
       </c>
       <c r="F82" s="156"/>
     </row>
     <row r="83" spans="1:6">
-      <c r="A83" s="181">
+      <c r="A83" s="196">
         <v>41</v>
       </c>
-      <c r="B83" s="204" t="s">
+      <c r="B83" s="205" t="s">
         <v>652</v>
       </c>
-      <c r="C83" s="186" t="s">
+      <c r="C83" s="198" t="s">
         <v>653</v>
       </c>
-      <c r="D83" s="183" t="s">
+      <c r="D83" s="200" t="s">
         <v>654</v>
       </c>
       <c r="E83" s="156" t="s">
@@ -11173,10 +11720,10 @@
       </c>
     </row>
     <row r="84" spans="1:6">
-      <c r="A84" s="181"/>
-      <c r="B84" s="182"/>
-      <c r="C84" s="186"/>
-      <c r="D84" s="182"/>
+      <c r="A84" s="196"/>
+      <c r="B84" s="197"/>
+      <c r="C84" s="198"/>
+      <c r="D84" s="197"/>
       <c r="E84" s="132" t="s">
         <v>337</v>
       </c>
@@ -11185,16 +11732,16 @@
       </c>
     </row>
     <row r="85" spans="1:6">
-      <c r="A85" s="181">
+      <c r="A85" s="196">
         <v>42</v>
       </c>
-      <c r="B85" s="198" t="s">
+      <c r="B85" s="199" t="s">
         <v>656</v>
       </c>
-      <c r="C85" s="186" t="s">
+      <c r="C85" s="198" t="s">
         <v>657</v>
       </c>
-      <c r="D85" s="183" t="s">
+      <c r="D85" s="200" t="s">
         <v>658</v>
       </c>
       <c r="E85" s="156" t="s">
@@ -11205,24 +11752,24 @@
       </c>
     </row>
     <row r="86" spans="1:6">
-      <c r="A86" s="181"/>
-      <c r="B86" s="182"/>
-      <c r="C86" s="186"/>
-      <c r="D86" s="182"/>
+      <c r="A86" s="196"/>
+      <c r="B86" s="197"/>
+      <c r="C86" s="198"/>
+      <c r="D86" s="197"/>
       <c r="E86" s="156"/>
       <c r="F86" s="156"/>
     </row>
     <row r="87" spans="1:6">
-      <c r="A87" s="181">
+      <c r="A87" s="196">
         <v>43</v>
       </c>
-      <c r="B87" s="198" t="s">
+      <c r="B87" s="199" t="s">
         <v>661</v>
       </c>
-      <c r="C87" s="186" t="s">
+      <c r="C87" s="198" t="s">
         <v>662</v>
       </c>
-      <c r="D87" s="183" t="s">
+      <c r="D87" s="200" t="s">
         <v>663</v>
       </c>
       <c r="E87" s="156" t="s">
@@ -11233,24 +11780,24 @@
       </c>
     </row>
     <row r="88" spans="1:6">
-      <c r="A88" s="181"/>
-      <c r="B88" s="182"/>
-      <c r="C88" s="186"/>
-      <c r="D88" s="182"/>
+      <c r="A88" s="196"/>
+      <c r="B88" s="197"/>
+      <c r="C88" s="198"/>
+      <c r="D88" s="197"/>
       <c r="E88" s="156" t="s">
         <v>337</v>
       </c>
       <c r="F88" s="156"/>
     </row>
     <row r="89" spans="1:6">
-      <c r="A89" s="181">
+      <c r="A89" s="196">
         <v>44</v>
       </c>
-      <c r="B89" s="198" t="s">
+      <c r="B89" s="199" t="s">
         <v>664</v>
       </c>
-      <c r="C89" s="186"/>
-      <c r="D89" s="182"/>
+      <c r="C89" s="198"/>
+      <c r="D89" s="197"/>
       <c r="E89" s="156" t="s">
         <v>354</v>
       </c>
@@ -11259,26 +11806,26 @@
       </c>
     </row>
     <row r="90" spans="1:6">
-      <c r="A90" s="181"/>
-      <c r="B90" s="182"/>
-      <c r="C90" s="186"/>
-      <c r="D90" s="182"/>
+      <c r="A90" s="196"/>
+      <c r="B90" s="197"/>
+      <c r="C90" s="198"/>
+      <c r="D90" s="197"/>
       <c r="E90" s="156" t="s">
         <v>337</v>
       </c>
       <c r="F90" s="156"/>
     </row>
     <row r="91" spans="1:6">
-      <c r="A91" s="181">
+      <c r="A91" s="196">
         <v>45</v>
       </c>
-      <c r="B91" s="198" t="s">
+      <c r="B91" s="199" t="s">
         <v>666</v>
       </c>
-      <c r="C91" s="186" t="s">
+      <c r="C91" s="198" t="s">
         <v>667</v>
       </c>
-      <c r="D91" s="183" t="s">
+      <c r="D91" s="200" t="s">
         <v>668</v>
       </c>
       <c r="E91" s="156" t="s">
@@ -11289,26 +11836,26 @@
       </c>
     </row>
     <row r="92" spans="1:6">
-      <c r="A92" s="181"/>
-      <c r="B92" s="182"/>
-      <c r="C92" s="186"/>
-      <c r="D92" s="182"/>
+      <c r="A92" s="196"/>
+      <c r="B92" s="197"/>
+      <c r="C92" s="198"/>
+      <c r="D92" s="197"/>
       <c r="E92" s="156" t="s">
         <v>337</v>
       </c>
       <c r="F92" s="156"/>
     </row>
     <row r="93" spans="1:6">
-      <c r="A93" s="181">
+      <c r="A93" s="196">
         <v>46</v>
       </c>
-      <c r="B93" s="198" t="s">
+      <c r="B93" s="199" t="s">
         <v>670</v>
       </c>
-      <c r="C93" s="186" t="s">
+      <c r="C93" s="198" t="s">
         <v>671</v>
       </c>
-      <c r="D93" s="183" t="s">
+      <c r="D93" s="200" t="s">
         <v>672</v>
       </c>
       <c r="E93" s="156" t="s">
@@ -11319,26 +11866,26 @@
       </c>
     </row>
     <row r="94" spans="1:6">
-      <c r="A94" s="181"/>
-      <c r="B94" s="182"/>
-      <c r="C94" s="186"/>
-      <c r="D94" s="182"/>
+      <c r="A94" s="196"/>
+      <c r="B94" s="197"/>
+      <c r="C94" s="198"/>
+      <c r="D94" s="197"/>
       <c r="E94" s="156" t="s">
         <v>337</v>
       </c>
       <c r="F94" s="156"/>
     </row>
     <row r="95" spans="1:6">
-      <c r="A95" s="181">
+      <c r="A95" s="196">
         <v>47</v>
       </c>
-      <c r="B95" s="198" t="s">
+      <c r="B95" s="199" t="s">
         <v>673</v>
       </c>
-      <c r="C95" s="186" t="s">
+      <c r="C95" s="198" t="s">
         <v>674</v>
       </c>
-      <c r="D95" s="183" t="s">
+      <c r="D95" s="200" t="s">
         <v>675</v>
       </c>
       <c r="E95" s="156" t="s">
@@ -11349,26 +11896,26 @@
       </c>
     </row>
     <row r="96" spans="1:6">
-      <c r="A96" s="181"/>
-      <c r="B96" s="182"/>
-      <c r="C96" s="186"/>
-      <c r="D96" s="182"/>
+      <c r="A96" s="196"/>
+      <c r="B96" s="197"/>
+      <c r="C96" s="198"/>
+      <c r="D96" s="197"/>
       <c r="E96" s="156" t="s">
         <v>337</v>
       </c>
       <c r="F96" s="156"/>
     </row>
     <row r="97" spans="1:6">
-      <c r="A97" s="181">
+      <c r="A97" s="196">
         <v>48</v>
       </c>
-      <c r="B97" s="198" t="s">
+      <c r="B97" s="199" t="s">
         <v>677</v>
       </c>
-      <c r="C97" s="186" t="s">
+      <c r="C97" s="198" t="s">
         <v>678</v>
       </c>
-      <c r="D97" s="183" t="s">
+      <c r="D97" s="200" t="s">
         <v>679</v>
       </c>
       <c r="E97" s="156" t="s">
@@ -11379,26 +11926,26 @@
       </c>
     </row>
     <row r="98" spans="1:6">
-      <c r="A98" s="181"/>
-      <c r="B98" s="182"/>
-      <c r="C98" s="186"/>
-      <c r="D98" s="182"/>
+      <c r="A98" s="196"/>
+      <c r="B98" s="197"/>
+      <c r="C98" s="198"/>
+      <c r="D98" s="197"/>
       <c r="E98" s="156" t="s">
         <v>337</v>
       </c>
       <c r="F98" s="156"/>
     </row>
     <row r="99" spans="1:6">
-      <c r="A99" s="181">
+      <c r="A99" s="196">
         <v>49</v>
       </c>
-      <c r="B99" s="198" t="s">
+      <c r="B99" s="199" t="s">
         <v>681</v>
       </c>
-      <c r="C99" s="198" t="s">
+      <c r="C99" s="199" t="s">
         <v>681</v>
       </c>
-      <c r="D99" s="183" t="s">
+      <c r="D99" s="200" t="s">
         <v>716</v>
       </c>
       <c r="E99" s="156" t="s">
@@ -11407,10 +11954,10 @@
       <c r="F99" s="157"/>
     </row>
     <row r="100" spans="1:6">
-      <c r="A100" s="181"/>
-      <c r="B100" s="182"/>
-      <c r="C100" s="186"/>
-      <c r="D100" s="182"/>
+      <c r="A100" s="196"/>
+      <c r="B100" s="197"/>
+      <c r="C100" s="198"/>
+      <c r="D100" s="197"/>
       <c r="E100" s="156" t="s">
         <v>337</v>
       </c>
@@ -11419,16 +11966,16 @@
       </c>
     </row>
     <row r="101" spans="1:6">
-      <c r="A101" s="181">
+      <c r="A101" s="196">
         <v>50</v>
       </c>
-      <c r="B101" s="198" t="s">
+      <c r="B101" s="199" t="s">
         <v>843</v>
       </c>
-      <c r="C101" s="198" t="s">
+      <c r="C101" s="199" t="s">
         <v>844</v>
       </c>
-      <c r="D101" s="183" t="s">
+      <c r="D101" s="200" t="s">
         <v>845</v>
       </c>
       <c r="E101" s="132" t="s">
@@ -11439,10 +11986,10 @@
       </c>
     </row>
     <row r="102" spans="1:6">
-      <c r="A102" s="181"/>
-      <c r="B102" s="182"/>
-      <c r="C102" s="186"/>
-      <c r="D102" s="182"/>
+      <c r="A102" s="196"/>
+      <c r="B102" s="197"/>
+      <c r="C102" s="198"/>
+      <c r="D102" s="197"/>
       <c r="E102" s="156" t="s">
         <v>659</v>
       </c>
@@ -11451,16 +11998,16 @@
       </c>
     </row>
     <row r="103" spans="1:6">
-      <c r="A103" s="181">
+      <c r="A103" s="196">
         <v>51</v>
       </c>
-      <c r="B103" s="198" t="s">
+      <c r="B103" s="199" t="s">
         <v>691</v>
       </c>
-      <c r="C103" s="199" t="s">
+      <c r="C103" s="204" t="s">
         <v>692</v>
       </c>
-      <c r="D103" s="183" t="s">
+      <c r="D103" s="200" t="s">
         <v>693</v>
       </c>
       <c r="E103" s="156" t="s">
@@ -11471,26 +12018,26 @@
       </c>
     </row>
     <row r="104" spans="1:6">
-      <c r="A104" s="181"/>
-      <c r="B104" s="182"/>
-      <c r="C104" s="186"/>
-      <c r="D104" s="182"/>
+      <c r="A104" s="196"/>
+      <c r="B104" s="197"/>
+      <c r="C104" s="198"/>
+      <c r="D104" s="197"/>
       <c r="E104" s="156" t="s">
         <v>337</v>
       </c>
       <c r="F104" s="156"/>
     </row>
     <row r="105" spans="1:6">
-      <c r="A105" s="181">
+      <c r="A105" s="196">
         <v>52</v>
       </c>
-      <c r="B105" s="198" t="s">
+      <c r="B105" s="199" t="s">
         <v>770</v>
       </c>
-      <c r="C105" s="199" t="s">
+      <c r="C105" s="204" t="s">
         <v>720</v>
       </c>
-      <c r="D105" s="183" t="s">
+      <c r="D105" s="200" t="s">
         <v>721</v>
       </c>
       <c r="E105" s="156" t="s">
@@ -11501,26 +12048,26 @@
       </c>
     </row>
     <row r="106" spans="1:6">
-      <c r="A106" s="181"/>
-      <c r="B106" s="182"/>
-      <c r="C106" s="186"/>
-      <c r="D106" s="182"/>
+      <c r="A106" s="196"/>
+      <c r="B106" s="197"/>
+      <c r="C106" s="198"/>
+      <c r="D106" s="197"/>
       <c r="E106" s="156" t="s">
         <v>337</v>
       </c>
       <c r="F106" s="156"/>
     </row>
     <row r="107" spans="1:6">
-      <c r="A107" s="181">
+      <c r="A107" s="196">
         <v>53</v>
       </c>
-      <c r="B107" s="198" t="s">
+      <c r="B107" s="199" t="s">
         <v>879</v>
       </c>
-      <c r="C107" s="199" t="s">
+      <c r="C107" s="204" t="s">
         <v>723</v>
       </c>
-      <c r="D107" s="183" t="s">
+      <c r="D107" s="200" t="s">
         <v>724</v>
       </c>
       <c r="E107" s="156" t="s">
@@ -11529,10 +12076,10 @@
       <c r="F107" s="156"/>
     </row>
     <row r="108" spans="1:6">
-      <c r="A108" s="181"/>
-      <c r="B108" s="182"/>
-      <c r="C108" s="186"/>
-      <c r="D108" s="182"/>
+      <c r="A108" s="196"/>
+      <c r="B108" s="197"/>
+      <c r="C108" s="198"/>
+      <c r="D108" s="197"/>
       <c r="E108" s="156" t="s">
         <v>337</v>
       </c>
@@ -11541,16 +12088,16 @@
       </c>
     </row>
     <row r="109" spans="1:6">
-      <c r="A109" s="181">
+      <c r="A109" s="196">
         <v>54</v>
       </c>
-      <c r="B109" s="198" t="s">
+      <c r="B109" s="199" t="s">
         <v>725</v>
       </c>
-      <c r="C109" s="199" t="s">
+      <c r="C109" s="204" t="s">
         <v>726</v>
       </c>
-      <c r="D109" s="183"/>
+      <c r="D109" s="200"/>
       <c r="E109" s="132" t="s">
         <v>354</v>
       </c>
@@ -11559,10 +12106,10 @@
       </c>
     </row>
     <row r="110" spans="1:6">
-      <c r="A110" s="181"/>
-      <c r="B110" s="182"/>
-      <c r="C110" s="186"/>
-      <c r="D110" s="182"/>
+      <c r="A110" s="196"/>
+      <c r="B110" s="197"/>
+      <c r="C110" s="198"/>
+      <c r="D110" s="197"/>
       <c r="E110" s="156" t="s">
         <v>337</v>
       </c>
@@ -11571,16 +12118,16 @@
       </c>
     </row>
     <row r="111" spans="1:6">
-      <c r="A111" s="181">
+      <c r="A111" s="196">
         <v>55</v>
       </c>
-      <c r="B111" s="198" t="s">
+      <c r="B111" s="199" t="s">
         <v>729</v>
       </c>
-      <c r="C111" s="199" t="s">
+      <c r="C111" s="204" t="s">
         <v>730</v>
       </c>
-      <c r="D111" s="183" t="s">
+      <c r="D111" s="200" t="s">
         <v>731</v>
       </c>
       <c r="E111" s="156" t="s">
@@ -11591,26 +12138,26 @@
       </c>
     </row>
     <row r="112" spans="1:6">
-      <c r="A112" s="181"/>
-      <c r="B112" s="182"/>
-      <c r="C112" s="186"/>
-      <c r="D112" s="182"/>
+      <c r="A112" s="196"/>
+      <c r="B112" s="197"/>
+      <c r="C112" s="198"/>
+      <c r="D112" s="197"/>
       <c r="E112" s="156" t="s">
         <v>337</v>
       </c>
       <c r="F112" s="156"/>
     </row>
     <row r="113" spans="1:6">
-      <c r="A113" s="181">
+      <c r="A113" s="196">
         <v>56</v>
       </c>
-      <c r="B113" s="198" t="s">
+      <c r="B113" s="199" t="s">
         <v>736</v>
       </c>
-      <c r="C113" s="199" t="s">
+      <c r="C113" s="204" t="s">
         <v>737</v>
       </c>
-      <c r="D113" s="183" t="s">
+      <c r="D113" s="200" t="s">
         <v>738</v>
       </c>
       <c r="E113" s="156" t="s">
@@ -11621,10 +12168,10 @@
       </c>
     </row>
     <row r="114" spans="1:6">
-      <c r="A114" s="181"/>
-      <c r="B114" s="182"/>
-      <c r="C114" s="186"/>
-      <c r="D114" s="182"/>
+      <c r="A114" s="196"/>
+      <c r="B114" s="197"/>
+      <c r="C114" s="198"/>
+      <c r="D114" s="197"/>
       <c r="E114" s="156" t="s">
         <v>337</v>
       </c>
@@ -11651,16 +12198,16 @@
       </c>
     </row>
     <row r="116" spans="1:6">
-      <c r="A116" s="181">
+      <c r="A116" s="196">
         <v>58</v>
       </c>
-      <c r="B116" s="198" t="s">
+      <c r="B116" s="199" t="s">
         <v>746</v>
       </c>
-      <c r="C116" s="199" t="s">
+      <c r="C116" s="204" t="s">
         <v>747</v>
       </c>
-      <c r="D116" s="183" t="s">
+      <c r="D116" s="200" t="s">
         <v>748</v>
       </c>
       <c r="E116" s="156" t="s">
@@ -11671,26 +12218,26 @@
       </c>
     </row>
     <row r="117" spans="1:6">
-      <c r="A117" s="181"/>
-      <c r="B117" s="182"/>
-      <c r="C117" s="186"/>
-      <c r="D117" s="182"/>
+      <c r="A117" s="196"/>
+      <c r="B117" s="197"/>
+      <c r="C117" s="198"/>
+      <c r="D117" s="197"/>
       <c r="E117" s="156" t="s">
         <v>337</v>
       </c>
       <c r="F117" s="156"/>
     </row>
     <row r="118" spans="1:6">
-      <c r="A118" s="181">
+      <c r="A118" s="196">
         <v>59</v>
       </c>
-      <c r="B118" s="198" t="s">
+      <c r="B118" s="199" t="s">
         <v>870</v>
       </c>
-      <c r="C118" s="199" t="s">
+      <c r="C118" s="204" t="s">
         <v>871</v>
       </c>
-      <c r="D118" s="183" t="s">
+      <c r="D118" s="200" t="s">
         <v>763</v>
       </c>
       <c r="E118" s="156" t="s">
@@ -11699,10 +12246,10 @@
       <c r="F118" s="156"/>
     </row>
     <row r="119" spans="1:6">
-      <c r="A119" s="181"/>
-      <c r="B119" s="182"/>
-      <c r="C119" s="186"/>
-      <c r="D119" s="182"/>
+      <c r="A119" s="196"/>
+      <c r="B119" s="197"/>
+      <c r="C119" s="198"/>
+      <c r="D119" s="197"/>
       <c r="E119" s="156" t="s">
         <v>337</v>
       </c>
@@ -11801,16 +12348,16 @@
       </c>
     </row>
     <row r="125" spans="1:6">
-      <c r="A125" s="181">
+      <c r="A125" s="196">
         <v>65</v>
       </c>
-      <c r="B125" s="198" t="s">
+      <c r="B125" s="199" t="s">
         <v>816</v>
       </c>
-      <c r="C125" s="199" t="s">
+      <c r="C125" s="204" t="s">
         <v>788</v>
       </c>
-      <c r="D125" s="183" t="s">
+      <c r="D125" s="200" t="s">
         <v>789</v>
       </c>
       <c r="E125" s="156" t="s">
@@ -11819,10 +12366,10 @@
       <c r="F125" s="156"/>
     </row>
     <row r="126" spans="1:6">
-      <c r="A126" s="181"/>
-      <c r="B126" s="182"/>
-      <c r="C126" s="186"/>
-      <c r="D126" s="182"/>
+      <c r="A126" s="196"/>
+      <c r="B126" s="197"/>
+      <c r="C126" s="198"/>
+      <c r="D126" s="197"/>
       <c r="E126" s="156" t="s">
         <v>337</v>
       </c>
@@ -11831,16 +12378,16 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="A127" s="181">
+      <c r="A127" s="196">
         <v>66</v>
       </c>
-      <c r="B127" s="198" t="s">
+      <c r="B127" s="199" t="s">
         <v>796</v>
       </c>
-      <c r="C127" s="199" t="s">
+      <c r="C127" s="204" t="s">
         <v>791</v>
       </c>
-      <c r="D127" s="183" t="s">
+      <c r="D127" s="200" t="s">
         <v>792</v>
       </c>
       <c r="E127" s="156" t="s">
@@ -11849,10 +12396,10 @@
       <c r="F127" s="156"/>
     </row>
     <row r="128" spans="1:6">
-      <c r="A128" s="181"/>
-      <c r="B128" s="182"/>
-      <c r="C128" s="186"/>
-      <c r="D128" s="182"/>
+      <c r="A128" s="196"/>
+      <c r="B128" s="197"/>
+      <c r="C128" s="198"/>
+      <c r="D128" s="197"/>
       <c r="E128" s="156" t="s">
         <v>337</v>
       </c>
@@ -11861,16 +12408,16 @@
       </c>
     </row>
     <row r="129" spans="1:6">
-      <c r="A129" s="181">
+      <c r="A129" s="196">
         <v>67</v>
       </c>
-      <c r="B129" s="198" t="s">
+      <c r="B129" s="199" t="s">
         <v>793</v>
       </c>
-      <c r="C129" s="199" t="s">
+      <c r="C129" s="204" t="s">
         <v>794</v>
       </c>
-      <c r="D129" s="183" t="s">
+      <c r="D129" s="200" t="s">
         <v>795</v>
       </c>
       <c r="E129" s="156" t="s">
@@ -11881,10 +12428,10 @@
       </c>
     </row>
     <row r="130" spans="1:6">
-      <c r="A130" s="181"/>
-      <c r="B130" s="182"/>
-      <c r="C130" s="186"/>
-      <c r="D130" s="182"/>
+      <c r="A130" s="196"/>
+      <c r="B130" s="197"/>
+      <c r="C130" s="198"/>
+      <c r="D130" s="197"/>
       <c r="E130" s="156" t="s">
         <v>337</v>
       </c>
@@ -11988,13 +12535,13 @@
       <c r="A137" s="188">
         <v>74</v>
       </c>
-      <c r="B137" s="191" t="s">
+      <c r="B137" s="190" t="s">
         <v>817</v>
       </c>
-      <c r="C137" s="212" t="s">
+      <c r="C137" s="192" t="s">
         <v>818</v>
       </c>
-      <c r="D137" s="195" t="s">
+      <c r="D137" s="194" t="s">
         <v>819</v>
       </c>
       <c r="E137" s="156" t="s">
@@ -12005,10 +12552,10 @@
       </c>
     </row>
     <row r="138" spans="1:6">
-      <c r="A138" s="190"/>
-      <c r="B138" s="211"/>
-      <c r="C138" s="213"/>
-      <c r="D138" s="197"/>
+      <c r="A138" s="189"/>
+      <c r="B138" s="191"/>
+      <c r="C138" s="193"/>
+      <c r="D138" s="195"/>
       <c r="E138" s="156" t="s">
         <v>337</v>
       </c>
@@ -12036,13 +12583,13 @@
       <c r="A140" s="188">
         <v>76</v>
       </c>
-      <c r="B140" s="191" t="s">
+      <c r="B140" s="190" t="s">
         <v>825</v>
       </c>
-      <c r="C140" s="212" t="s">
+      <c r="C140" s="192" t="s">
         <v>826</v>
       </c>
-      <c r="D140" s="195" t="s">
+      <c r="D140" s="194" t="s">
         <v>827</v>
       </c>
       <c r="E140" s="156" t="s">
@@ -12053,10 +12600,10 @@
       </c>
     </row>
     <row r="141" spans="1:6">
-      <c r="A141" s="190"/>
-      <c r="B141" s="211"/>
-      <c r="C141" s="213"/>
-      <c r="D141" s="197"/>
+      <c r="A141" s="189"/>
+      <c r="B141" s="191"/>
+      <c r="C141" s="193"/>
+      <c r="D141" s="195"/>
       <c r="E141" s="156" t="s">
         <v>337</v>
       </c>
@@ -12101,16 +12648,16 @@
       </c>
     </row>
     <row r="144" spans="1:6">
-      <c r="A144" s="181">
+      <c r="A144" s="196">
         <v>79</v>
       </c>
-      <c r="B144" s="198" t="s">
+      <c r="B144" s="199" t="s">
         <v>839</v>
       </c>
-      <c r="C144" s="186" t="s">
+      <c r="C144" s="198" t="s">
         <v>840</v>
       </c>
-      <c r="D144" s="183" t="s">
+      <c r="D144" s="200" t="s">
         <v>841</v>
       </c>
       <c r="E144" s="156" t="s">
@@ -12121,26 +12668,26 @@
       </c>
     </row>
     <row r="145" spans="1:6">
-      <c r="A145" s="181"/>
-      <c r="B145" s="182"/>
-      <c r="C145" s="186"/>
-      <c r="D145" s="182"/>
+      <c r="A145" s="196"/>
+      <c r="B145" s="197"/>
+      <c r="C145" s="198"/>
+      <c r="D145" s="197"/>
       <c r="E145" s="156" t="s">
         <v>337</v>
       </c>
       <c r="F145" s="156"/>
     </row>
     <row r="146" spans="1:6">
-      <c r="A146" s="181">
+      <c r="A146" s="196">
         <v>80</v>
       </c>
-      <c r="B146" s="198" t="s">
+      <c r="B146" s="199" t="s">
         <v>846</v>
       </c>
-      <c r="C146" s="198" t="s">
+      <c r="C146" s="199" t="s">
         <v>847</v>
       </c>
-      <c r="D146" s="183" t="s">
+      <c r="D146" s="200" t="s">
         <v>848</v>
       </c>
       <c r="E146" s="156" t="s">
@@ -12151,10 +12698,10 @@
       </c>
     </row>
     <row r="147" spans="1:6">
-      <c r="A147" s="181"/>
-      <c r="B147" s="182"/>
-      <c r="C147" s="186"/>
-      <c r="D147" s="182"/>
+      <c r="A147" s="196"/>
+      <c r="B147" s="197"/>
+      <c r="C147" s="198"/>
+      <c r="D147" s="197"/>
       <c r="E147" s="132" t="s">
         <v>659</v>
       </c>
@@ -12163,16 +12710,16 @@
       </c>
     </row>
     <row r="148" spans="1:6">
-      <c r="A148" s="181">
+      <c r="A148" s="196">
         <v>81</v>
       </c>
-      <c r="B148" s="198" t="s">
+      <c r="B148" s="199" t="s">
         <v>850</v>
       </c>
-      <c r="C148" s="199" t="s">
+      <c r="C148" s="204" t="s">
         <v>851</v>
       </c>
-      <c r="D148" s="183" t="s">
+      <c r="D148" s="200" t="s">
         <v>852</v>
       </c>
       <c r="E148" s="156" t="s">
@@ -12183,26 +12730,26 @@
       </c>
     </row>
     <row r="149" spans="1:6">
-      <c r="A149" s="181"/>
-      <c r="B149" s="182"/>
-      <c r="C149" s="186"/>
-      <c r="D149" s="182"/>
+      <c r="A149" s="196"/>
+      <c r="B149" s="197"/>
+      <c r="C149" s="198"/>
+      <c r="D149" s="197"/>
       <c r="E149" s="156" t="s">
         <v>337</v>
       </c>
       <c r="F149" s="156"/>
     </row>
     <row r="150" spans="1:6">
-      <c r="A150" s="181">
+      <c r="A150" s="196">
         <v>82</v>
       </c>
-      <c r="B150" s="198" t="s">
+      <c r="B150" s="199" t="s">
         <v>856</v>
       </c>
-      <c r="C150" s="198" t="s">
+      <c r="C150" s="199" t="s">
         <v>856</v>
       </c>
-      <c r="D150" s="183" t="s">
+      <c r="D150" s="200" t="s">
         <v>859</v>
       </c>
       <c r="E150" s="156" t="s">
@@ -12211,10 +12758,10 @@
       <c r="F150" s="157"/>
     </row>
     <row r="151" spans="1:6">
-      <c r="A151" s="181"/>
-      <c r="B151" s="182"/>
-      <c r="C151" s="182"/>
-      <c r="D151" s="182"/>
+      <c r="A151" s="196"/>
+      <c r="B151" s="197"/>
+      <c r="C151" s="197"/>
+      <c r="D151" s="197"/>
       <c r="E151" s="156" t="s">
         <v>337</v>
       </c>
@@ -12223,16 +12770,16 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="A152" s="181">
+      <c r="A152" s="196">
         <v>83</v>
       </c>
-      <c r="B152" s="198" t="s">
+      <c r="B152" s="199" t="s">
         <v>860</v>
       </c>
-      <c r="C152" s="186" t="s">
+      <c r="C152" s="198" t="s">
         <v>861</v>
       </c>
-      <c r="D152" s="183" t="s">
+      <c r="D152" s="200" t="s">
         <v>862</v>
       </c>
       <c r="E152" s="156" t="s">
@@ -12243,24 +12790,24 @@
       </c>
     </row>
     <row r="153" spans="1:6">
-      <c r="A153" s="181"/>
-      <c r="B153" s="182"/>
-      <c r="C153" s="186"/>
-      <c r="D153" s="182"/>
+      <c r="A153" s="196"/>
+      <c r="B153" s="197"/>
+      <c r="C153" s="198"/>
+      <c r="D153" s="197"/>
       <c r="E153" s="156"/>
       <c r="F153" s="156"/>
     </row>
     <row r="154" spans="1:6">
-      <c r="A154" s="181">
+      <c r="A154" s="196">
         <v>84</v>
       </c>
-      <c r="B154" s="198" t="s">
+      <c r="B154" s="199" t="s">
         <v>865</v>
       </c>
-      <c r="C154" s="186" t="s">
+      <c r="C154" s="198" t="s">
         <v>866</v>
       </c>
-      <c r="D154" s="183" t="s">
+      <c r="D154" s="200" t="s">
         <v>867</v>
       </c>
       <c r="E154" s="156" t="s">
@@ -12271,24 +12818,24 @@
       </c>
     </row>
     <row r="155" spans="1:6">
-      <c r="A155" s="181"/>
-      <c r="B155" s="182"/>
-      <c r="C155" s="186"/>
-      <c r="D155" s="182"/>
+      <c r="A155" s="196"/>
+      <c r="B155" s="197"/>
+      <c r="C155" s="198"/>
+      <c r="D155" s="197"/>
       <c r="E155" s="156"/>
       <c r="F155" s="156"/>
     </row>
     <row r="156" spans="1:6">
-      <c r="A156" s="181">
+      <c r="A156" s="196">
         <v>85</v>
       </c>
-      <c r="B156" s="198" t="s">
+      <c r="B156" s="199" t="s">
         <v>875</v>
       </c>
-      <c r="C156" s="186" t="s">
+      <c r="C156" s="198" t="s">
         <v>876</v>
       </c>
-      <c r="D156" s="183" t="s">
+      <c r="D156" s="200" t="s">
         <v>877</v>
       </c>
       <c r="E156" s="156" t="s">
@@ -12297,10 +12844,10 @@
       <c r="F156" s="156"/>
     </row>
     <row r="157" spans="1:6">
-      <c r="A157" s="181"/>
-      <c r="B157" s="182"/>
-      <c r="C157" s="186"/>
-      <c r="D157" s="182"/>
+      <c r="A157" s="196"/>
+      <c r="B157" s="197"/>
+      <c r="C157" s="198"/>
+      <c r="D157" s="197"/>
       <c r="E157" s="156" t="s">
         <v>337</v>
       </c>
@@ -12309,16 +12856,16 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="18" customHeight="1">
-      <c r="A158" s="181">
+      <c r="A158" s="196">
         <v>86</v>
       </c>
-      <c r="B158" s="182" t="s">
+      <c r="B158" s="197" t="s">
         <v>891</v>
       </c>
-      <c r="C158" s="186" t="s">
+      <c r="C158" s="198" t="s">
         <v>880</v>
       </c>
-      <c r="D158" s="186" t="s">
+      <c r="D158" s="198" t="s">
         <v>881</v>
       </c>
       <c r="E158" s="156" t="s">
@@ -12327,10 +12874,10 @@
       <c r="F158" s="156"/>
     </row>
     <row r="159" spans="1:6">
-      <c r="A159" s="181"/>
-      <c r="B159" s="182"/>
-      <c r="C159" s="186"/>
-      <c r="D159" s="186"/>
+      <c r="A159" s="196"/>
+      <c r="B159" s="197"/>
+      <c r="C159" s="198"/>
+      <c r="D159" s="198"/>
       <c r="E159" s="156" t="s">
         <v>337</v>
       </c>
@@ -12339,16 +12886,16 @@
       </c>
     </row>
     <row r="160" spans="1:6">
-      <c r="A160" s="184">
+      <c r="A160" s="201">
         <v>87</v>
       </c>
-      <c r="B160" s="185" t="s">
+      <c r="B160" s="202" t="s">
         <v>886</v>
       </c>
-      <c r="C160" s="186" t="s">
+      <c r="C160" s="198" t="s">
         <v>887</v>
       </c>
-      <c r="D160" s="187" t="s">
+      <c r="D160" s="203" t="s">
         <v>888</v>
       </c>
       <c r="E160" s="156" t="s">
@@ -12357,10 +12904,10 @@
       <c r="F160" s="156"/>
     </row>
     <row r="161" spans="1:6">
-      <c r="A161" s="184"/>
-      <c r="B161" s="182"/>
-      <c r="C161" s="186"/>
-      <c r="D161" s="186"/>
+      <c r="A161" s="201"/>
+      <c r="B161" s="197"/>
+      <c r="C161" s="198"/>
+      <c r="D161" s="198"/>
       <c r="E161" s="156" t="s">
         <v>337</v>
       </c>
@@ -12369,16 +12916,16 @@
       </c>
     </row>
     <row r="162" spans="1:6" ht="18" customHeight="1">
-      <c r="A162" s="184">
+      <c r="A162" s="201">
         <v>88</v>
       </c>
-      <c r="B162" s="185" t="s">
+      <c r="B162" s="202" t="s">
         <v>892</v>
       </c>
-      <c r="C162" s="186" t="s">
+      <c r="C162" s="198" t="s">
         <v>893</v>
       </c>
-      <c r="D162" s="183" t="s">
+      <c r="D162" s="200" t="s">
         <v>894</v>
       </c>
       <c r="E162" s="156" t="s">
@@ -12387,10 +12934,10 @@
       <c r="F162" s="156"/>
     </row>
     <row r="163" spans="1:6">
-      <c r="A163" s="184"/>
-      <c r="B163" s="182"/>
-      <c r="C163" s="186"/>
-      <c r="D163" s="186"/>
+      <c r="A163" s="201"/>
+      <c r="B163" s="197"/>
+      <c r="C163" s="198"/>
+      <c r="D163" s="198"/>
       <c r="E163" s="156" t="s">
         <v>895</v>
       </c>
@@ -12399,16 +12946,16 @@
       </c>
     </row>
     <row r="164" spans="1:6">
-      <c r="A164" s="184">
+      <c r="A164" s="201">
         <v>89</v>
       </c>
-      <c r="B164" s="185" t="s">
+      <c r="B164" s="202" t="s">
         <v>897</v>
       </c>
-      <c r="C164" s="185" t="s">
+      <c r="C164" s="202" t="s">
         <v>897</v>
       </c>
-      <c r="D164" s="187" t="s">
+      <c r="D164" s="203" t="s">
         <v>898</v>
       </c>
       <c r="E164" s="156" t="s">
@@ -12417,10 +12964,10 @@
       <c r="F164" s="156"/>
     </row>
     <row r="165" spans="1:6">
-      <c r="A165" s="184"/>
-      <c r="B165" s="182"/>
-      <c r="C165" s="182"/>
-      <c r="D165" s="186"/>
+      <c r="A165" s="201"/>
+      <c r="B165" s="197"/>
+      <c r="C165" s="197"/>
+      <c r="D165" s="198"/>
       <c r="E165" s="156" t="s">
         <v>337</v>
       </c>
@@ -12431,26 +12978,254 @@
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <mergeCells count="296">
-    <mergeCell ref="A140:A141"/>
-    <mergeCell ref="B140:B141"/>
-    <mergeCell ref="C140:C141"/>
-    <mergeCell ref="D140:D141"/>
-    <mergeCell ref="A158:A159"/>
-    <mergeCell ref="B158:B159"/>
-    <mergeCell ref="C158:C159"/>
-    <mergeCell ref="D158:D159"/>
-    <mergeCell ref="A144:A145"/>
-    <mergeCell ref="B144:B145"/>
-    <mergeCell ref="C144:C145"/>
-    <mergeCell ref="D144:D145"/>
-    <mergeCell ref="A146:A147"/>
-    <mergeCell ref="B146:B147"/>
-    <mergeCell ref="C146:C147"/>
-    <mergeCell ref="D146:D147"/>
-    <mergeCell ref="A150:A151"/>
-    <mergeCell ref="B150:B151"/>
-    <mergeCell ref="C150:C151"/>
-    <mergeCell ref="D150:D151"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="A162:A163"/>
+    <mergeCell ref="B162:B163"/>
+    <mergeCell ref="C162:C163"/>
+    <mergeCell ref="D162:D163"/>
+    <mergeCell ref="A160:A161"/>
+    <mergeCell ref="B160:B161"/>
+    <mergeCell ref="C160:C161"/>
+    <mergeCell ref="D160:D161"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="D28:D29"/>
+    <mergeCell ref="A30:A32"/>
+    <mergeCell ref="B30:B32"/>
+    <mergeCell ref="C30:C32"/>
+    <mergeCell ref="D30:D32"/>
+    <mergeCell ref="A107:A108"/>
+    <mergeCell ref="B107:B108"/>
+    <mergeCell ref="C107:C108"/>
+    <mergeCell ref="D107:D108"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="D26:D27"/>
+    <mergeCell ref="A81:A82"/>
+    <mergeCell ref="B81:B82"/>
+    <mergeCell ref="C81:C82"/>
+    <mergeCell ref="D81:D82"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="A75:A76"/>
+    <mergeCell ref="B75:B76"/>
+    <mergeCell ref="C75:C76"/>
+    <mergeCell ref="D75:D76"/>
+    <mergeCell ref="A77:A78"/>
+    <mergeCell ref="B77:B78"/>
+    <mergeCell ref="C77:C78"/>
+    <mergeCell ref="D77:D78"/>
+    <mergeCell ref="A43:A44"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="C43:C44"/>
+    <mergeCell ref="D43:D44"/>
+    <mergeCell ref="A45:A46"/>
+    <mergeCell ref="B45:B46"/>
+    <mergeCell ref="C45:C46"/>
+    <mergeCell ref="D45:D46"/>
+    <mergeCell ref="A47:A48"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="C47:C48"/>
+    <mergeCell ref="D47:D48"/>
+    <mergeCell ref="A83:A84"/>
+    <mergeCell ref="B83:B84"/>
+    <mergeCell ref="C83:C84"/>
+    <mergeCell ref="D83:D84"/>
+    <mergeCell ref="A85:A86"/>
+    <mergeCell ref="B85:B86"/>
+    <mergeCell ref="C85:C86"/>
+    <mergeCell ref="D85:D86"/>
+    <mergeCell ref="A89:A90"/>
+    <mergeCell ref="B89:B90"/>
+    <mergeCell ref="C89:C90"/>
+    <mergeCell ref="D89:D90"/>
+    <mergeCell ref="A87:A88"/>
+    <mergeCell ref="B87:B88"/>
+    <mergeCell ref="C87:C88"/>
+    <mergeCell ref="D87:D88"/>
+    <mergeCell ref="A39:A40"/>
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="D39:D40"/>
+    <mergeCell ref="A41:A42"/>
+    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="C41:C42"/>
+    <mergeCell ref="D41:D42"/>
+    <mergeCell ref="A79:A80"/>
+    <mergeCell ref="B79:B80"/>
+    <mergeCell ref="C79:C80"/>
+    <mergeCell ref="D79:D80"/>
+    <mergeCell ref="A59:A60"/>
+    <mergeCell ref="B59:B60"/>
+    <mergeCell ref="C59:C60"/>
+    <mergeCell ref="D59:D60"/>
+    <mergeCell ref="A61:A62"/>
+    <mergeCell ref="B61:B62"/>
+    <mergeCell ref="C61:C62"/>
+    <mergeCell ref="D61:D62"/>
+    <mergeCell ref="A57:A58"/>
+    <mergeCell ref="B57:B58"/>
+    <mergeCell ref="C57:C58"/>
+    <mergeCell ref="D57:D58"/>
+    <mergeCell ref="A33:A34"/>
+    <mergeCell ref="B33:B34"/>
+    <mergeCell ref="C33:C34"/>
+    <mergeCell ref="D33:D34"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="C35:C36"/>
+    <mergeCell ref="D35:D36"/>
+    <mergeCell ref="A37:A38"/>
+    <mergeCell ref="B37:B38"/>
+    <mergeCell ref="C37:C38"/>
+    <mergeCell ref="D37:D38"/>
+    <mergeCell ref="A49:A50"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
+    <mergeCell ref="D49:D50"/>
+    <mergeCell ref="A51:A52"/>
+    <mergeCell ref="B51:B52"/>
+    <mergeCell ref="C51:C52"/>
+    <mergeCell ref="D51:D52"/>
+    <mergeCell ref="A53:A54"/>
+    <mergeCell ref="B53:B54"/>
+    <mergeCell ref="C53:C54"/>
+    <mergeCell ref="D53:D54"/>
+    <mergeCell ref="A55:A56"/>
+    <mergeCell ref="B55:B56"/>
+    <mergeCell ref="C55:C56"/>
+    <mergeCell ref="D55:D56"/>
+    <mergeCell ref="A63:A64"/>
+    <mergeCell ref="B63:B64"/>
+    <mergeCell ref="C63:C64"/>
+    <mergeCell ref="D63:D64"/>
+    <mergeCell ref="A65:A66"/>
+    <mergeCell ref="B65:B66"/>
+    <mergeCell ref="C65:C66"/>
+    <mergeCell ref="D65:D66"/>
+    <mergeCell ref="A67:A68"/>
+    <mergeCell ref="B67:B68"/>
+    <mergeCell ref="C67:C68"/>
+    <mergeCell ref="D67:D68"/>
+    <mergeCell ref="A105:A106"/>
+    <mergeCell ref="B105:B106"/>
+    <mergeCell ref="C105:C106"/>
+    <mergeCell ref="D105:D106"/>
+    <mergeCell ref="A69:A70"/>
+    <mergeCell ref="B69:B70"/>
+    <mergeCell ref="C69:C70"/>
+    <mergeCell ref="D69:D70"/>
+    <mergeCell ref="A71:A72"/>
+    <mergeCell ref="B71:B72"/>
+    <mergeCell ref="C71:C72"/>
+    <mergeCell ref="D71:D72"/>
+    <mergeCell ref="A73:A74"/>
+    <mergeCell ref="B73:B74"/>
+    <mergeCell ref="C73:C74"/>
+    <mergeCell ref="D73:D74"/>
+    <mergeCell ref="A97:A98"/>
+    <mergeCell ref="B97:B98"/>
+    <mergeCell ref="C97:C98"/>
+    <mergeCell ref="D97:D98"/>
+    <mergeCell ref="A99:A100"/>
+    <mergeCell ref="B99:B100"/>
+    <mergeCell ref="C99:C100"/>
+    <mergeCell ref="D99:D100"/>
+    <mergeCell ref="A101:A102"/>
+    <mergeCell ref="B101:B102"/>
+    <mergeCell ref="C101:C102"/>
+    <mergeCell ref="D101:D102"/>
+    <mergeCell ref="A93:A94"/>
+    <mergeCell ref="B93:B94"/>
+    <mergeCell ref="C93:C94"/>
+    <mergeCell ref="D93:D94"/>
+    <mergeCell ref="A95:A96"/>
+    <mergeCell ref="B95:B96"/>
+    <mergeCell ref="C95:C96"/>
+    <mergeCell ref="D95:D96"/>
+    <mergeCell ref="A91:A92"/>
+    <mergeCell ref="B91:B92"/>
+    <mergeCell ref="C91:C92"/>
+    <mergeCell ref="D91:D92"/>
+    <mergeCell ref="A103:A104"/>
+    <mergeCell ref="B103:B104"/>
+    <mergeCell ref="C103:C104"/>
+    <mergeCell ref="D103:D104"/>
+    <mergeCell ref="A129:A130"/>
+    <mergeCell ref="B129:B130"/>
+    <mergeCell ref="C129:C130"/>
+    <mergeCell ref="D129:D130"/>
+    <mergeCell ref="A125:A126"/>
+    <mergeCell ref="B125:B126"/>
+    <mergeCell ref="C125:C126"/>
+    <mergeCell ref="D125:D126"/>
+    <mergeCell ref="A109:A110"/>
+    <mergeCell ref="B109:B110"/>
+    <mergeCell ref="C109:C110"/>
+    <mergeCell ref="D109:D110"/>
+    <mergeCell ref="A111:A112"/>
+    <mergeCell ref="B111:B112"/>
+    <mergeCell ref="C111:C112"/>
+    <mergeCell ref="D111:D112"/>
+    <mergeCell ref="A113:A114"/>
+    <mergeCell ref="B113:B114"/>
+    <mergeCell ref="C113:C114"/>
+    <mergeCell ref="D113:D114"/>
+    <mergeCell ref="A116:A117"/>
+    <mergeCell ref="B116:B117"/>
+    <mergeCell ref="C116:C117"/>
+    <mergeCell ref="D116:D117"/>
+    <mergeCell ref="A118:A119"/>
+    <mergeCell ref="B118:B119"/>
+    <mergeCell ref="C118:C119"/>
+    <mergeCell ref="D118:D119"/>
     <mergeCell ref="A164:A165"/>
     <mergeCell ref="B164:B165"/>
     <mergeCell ref="C164:C165"/>
@@ -12475,258 +13250,30 @@
     <mergeCell ref="B152:B153"/>
     <mergeCell ref="C152:C153"/>
     <mergeCell ref="D152:D153"/>
+    <mergeCell ref="A140:A141"/>
+    <mergeCell ref="B140:B141"/>
+    <mergeCell ref="C140:C141"/>
+    <mergeCell ref="D140:D141"/>
+    <mergeCell ref="A158:A159"/>
+    <mergeCell ref="B158:B159"/>
+    <mergeCell ref="C158:C159"/>
+    <mergeCell ref="D158:D159"/>
+    <mergeCell ref="A144:A145"/>
+    <mergeCell ref="B144:B145"/>
+    <mergeCell ref="C144:C145"/>
+    <mergeCell ref="D144:D145"/>
+    <mergeCell ref="A146:A147"/>
+    <mergeCell ref="B146:B147"/>
+    <mergeCell ref="C146:C147"/>
+    <mergeCell ref="D146:D147"/>
+    <mergeCell ref="A150:A151"/>
+    <mergeCell ref="B150:B151"/>
+    <mergeCell ref="C150:C151"/>
+    <mergeCell ref="D150:D151"/>
     <mergeCell ref="A148:A149"/>
     <mergeCell ref="B148:B149"/>
     <mergeCell ref="C148:C149"/>
     <mergeCell ref="D148:D149"/>
-    <mergeCell ref="A113:A114"/>
-    <mergeCell ref="B113:B114"/>
-    <mergeCell ref="C113:C114"/>
-    <mergeCell ref="D113:D114"/>
-    <mergeCell ref="A116:A117"/>
-    <mergeCell ref="B116:B117"/>
-    <mergeCell ref="C116:C117"/>
-    <mergeCell ref="D116:D117"/>
-    <mergeCell ref="A118:A119"/>
-    <mergeCell ref="B118:B119"/>
-    <mergeCell ref="C118:C119"/>
-    <mergeCell ref="D118:D119"/>
-    <mergeCell ref="A91:A92"/>
-    <mergeCell ref="B91:B92"/>
-    <mergeCell ref="C91:C92"/>
-    <mergeCell ref="D91:D92"/>
-    <mergeCell ref="A103:A104"/>
-    <mergeCell ref="B103:B104"/>
-    <mergeCell ref="C103:C104"/>
-    <mergeCell ref="D103:D104"/>
-    <mergeCell ref="A129:A130"/>
-    <mergeCell ref="B129:B130"/>
-    <mergeCell ref="C129:C130"/>
-    <mergeCell ref="D129:D130"/>
-    <mergeCell ref="A125:A126"/>
-    <mergeCell ref="B125:B126"/>
-    <mergeCell ref="C125:C126"/>
-    <mergeCell ref="D125:D126"/>
-    <mergeCell ref="A109:A110"/>
-    <mergeCell ref="B109:B110"/>
-    <mergeCell ref="C109:C110"/>
-    <mergeCell ref="D109:D110"/>
-    <mergeCell ref="A111:A112"/>
-    <mergeCell ref="B111:B112"/>
-    <mergeCell ref="C111:C112"/>
-    <mergeCell ref="D111:D112"/>
-    <mergeCell ref="A99:A100"/>
-    <mergeCell ref="B99:B100"/>
-    <mergeCell ref="C99:C100"/>
-    <mergeCell ref="D99:D100"/>
-    <mergeCell ref="A101:A102"/>
-    <mergeCell ref="B101:B102"/>
-    <mergeCell ref="C101:C102"/>
-    <mergeCell ref="D101:D102"/>
-    <mergeCell ref="A93:A94"/>
-    <mergeCell ref="B93:B94"/>
-    <mergeCell ref="C93:C94"/>
-    <mergeCell ref="D93:D94"/>
-    <mergeCell ref="A95:A96"/>
-    <mergeCell ref="B95:B96"/>
-    <mergeCell ref="C95:C96"/>
-    <mergeCell ref="D95:D96"/>
-    <mergeCell ref="A67:A68"/>
-    <mergeCell ref="B67:B68"/>
-    <mergeCell ref="C67:C68"/>
-    <mergeCell ref="D67:D68"/>
-    <mergeCell ref="A105:A106"/>
-    <mergeCell ref="B105:B106"/>
-    <mergeCell ref="C105:C106"/>
-    <mergeCell ref="D105:D106"/>
-    <mergeCell ref="A69:A70"/>
-    <mergeCell ref="B69:B70"/>
-    <mergeCell ref="C69:C70"/>
-    <mergeCell ref="D69:D70"/>
-    <mergeCell ref="A71:A72"/>
-    <mergeCell ref="B71:B72"/>
-    <mergeCell ref="C71:C72"/>
-    <mergeCell ref="D71:D72"/>
-    <mergeCell ref="A73:A74"/>
-    <mergeCell ref="B73:B74"/>
-    <mergeCell ref="C73:C74"/>
-    <mergeCell ref="D73:D74"/>
-    <mergeCell ref="A97:A98"/>
-    <mergeCell ref="B97:B98"/>
-    <mergeCell ref="C97:C98"/>
-    <mergeCell ref="D97:D98"/>
-    <mergeCell ref="A55:A56"/>
-    <mergeCell ref="B55:B56"/>
-    <mergeCell ref="C55:C56"/>
-    <mergeCell ref="D55:D56"/>
-    <mergeCell ref="A63:A64"/>
-    <mergeCell ref="B63:B64"/>
-    <mergeCell ref="C63:C64"/>
-    <mergeCell ref="D63:D64"/>
-    <mergeCell ref="A65:A66"/>
-    <mergeCell ref="B65:B66"/>
-    <mergeCell ref="C65:C66"/>
-    <mergeCell ref="D65:D66"/>
-    <mergeCell ref="A49:A50"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
-    <mergeCell ref="D49:D50"/>
-    <mergeCell ref="A51:A52"/>
-    <mergeCell ref="B51:B52"/>
-    <mergeCell ref="C51:C52"/>
-    <mergeCell ref="D51:D52"/>
-    <mergeCell ref="A53:A54"/>
-    <mergeCell ref="B53:B54"/>
-    <mergeCell ref="C53:C54"/>
-    <mergeCell ref="D53:D54"/>
-    <mergeCell ref="A33:A34"/>
-    <mergeCell ref="B33:B34"/>
-    <mergeCell ref="C33:C34"/>
-    <mergeCell ref="D33:D34"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="B35:B36"/>
-    <mergeCell ref="C35:C36"/>
-    <mergeCell ref="D35:D36"/>
-    <mergeCell ref="A37:A38"/>
-    <mergeCell ref="B37:B38"/>
-    <mergeCell ref="C37:C38"/>
-    <mergeCell ref="D37:D38"/>
-    <mergeCell ref="A39:A40"/>
-    <mergeCell ref="B39:B40"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="D39:D40"/>
-    <mergeCell ref="A41:A42"/>
-    <mergeCell ref="B41:B42"/>
-    <mergeCell ref="C41:C42"/>
-    <mergeCell ref="D41:D42"/>
-    <mergeCell ref="A79:A80"/>
-    <mergeCell ref="B79:B80"/>
-    <mergeCell ref="C79:C80"/>
-    <mergeCell ref="D79:D80"/>
-    <mergeCell ref="A59:A60"/>
-    <mergeCell ref="B59:B60"/>
-    <mergeCell ref="C59:C60"/>
-    <mergeCell ref="D59:D60"/>
-    <mergeCell ref="A61:A62"/>
-    <mergeCell ref="B61:B62"/>
-    <mergeCell ref="C61:C62"/>
-    <mergeCell ref="D61:D62"/>
-    <mergeCell ref="A57:A58"/>
-    <mergeCell ref="B57:B58"/>
-    <mergeCell ref="C57:C58"/>
-    <mergeCell ref="D57:D58"/>
-    <mergeCell ref="A83:A84"/>
-    <mergeCell ref="B83:B84"/>
-    <mergeCell ref="C83:C84"/>
-    <mergeCell ref="D83:D84"/>
-    <mergeCell ref="A85:A86"/>
-    <mergeCell ref="B85:B86"/>
-    <mergeCell ref="C85:C86"/>
-    <mergeCell ref="D85:D86"/>
-    <mergeCell ref="A89:A90"/>
-    <mergeCell ref="B89:B90"/>
-    <mergeCell ref="C89:C90"/>
-    <mergeCell ref="D89:D90"/>
-    <mergeCell ref="A87:A88"/>
-    <mergeCell ref="B87:B88"/>
-    <mergeCell ref="C87:C88"/>
-    <mergeCell ref="D87:D88"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="A75:A76"/>
-    <mergeCell ref="B75:B76"/>
-    <mergeCell ref="C75:C76"/>
-    <mergeCell ref="D75:D76"/>
-    <mergeCell ref="A77:A78"/>
-    <mergeCell ref="B77:B78"/>
-    <mergeCell ref="C77:C78"/>
-    <mergeCell ref="D77:D78"/>
-    <mergeCell ref="A43:A44"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="C43:C44"/>
-    <mergeCell ref="D43:D44"/>
-    <mergeCell ref="A45:A46"/>
-    <mergeCell ref="B45:B46"/>
-    <mergeCell ref="C45:C46"/>
-    <mergeCell ref="D45:D46"/>
-    <mergeCell ref="A47:A48"/>
-    <mergeCell ref="B47:B48"/>
-    <mergeCell ref="C47:C48"/>
-    <mergeCell ref="D47:D48"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="D26:D27"/>
-    <mergeCell ref="A81:A82"/>
-    <mergeCell ref="B81:B82"/>
-    <mergeCell ref="C81:C82"/>
-    <mergeCell ref="D81:D82"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="C24:C25"/>
-    <mergeCell ref="D24:D25"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="A162:A163"/>
-    <mergeCell ref="B162:B163"/>
-    <mergeCell ref="C162:C163"/>
-    <mergeCell ref="D162:D163"/>
-    <mergeCell ref="A160:A161"/>
-    <mergeCell ref="B160:B161"/>
-    <mergeCell ref="C160:C161"/>
-    <mergeCell ref="D160:D161"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="C28:C29"/>
-    <mergeCell ref="D28:D29"/>
-    <mergeCell ref="A30:A32"/>
-    <mergeCell ref="B30:B32"/>
-    <mergeCell ref="C30:C32"/>
-    <mergeCell ref="D30:D32"/>
-    <mergeCell ref="A107:A108"/>
-    <mergeCell ref="B107:B108"/>
-    <mergeCell ref="C107:C108"/>
-    <mergeCell ref="D107:D108"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
@@ -12771,117 +13318,117 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="49.5" customHeight="1">
-      <c r="B1" s="233" t="s">
+      <c r="B1" s="224" t="s">
         <v>756</v>
       </c>
-      <c r="C1" s="233"/>
-      <c r="D1" s="233"/>
-      <c r="E1" s="233"/>
-      <c r="F1" s="233"/>
-      <c r="G1" s="233"/>
-      <c r="H1" s="233"/>
-      <c r="I1" s="233"/>
-      <c r="J1" s="233"/>
-      <c r="K1" s="233"/>
-      <c r="L1" s="233"/>
-      <c r="M1" s="233"/>
-      <c r="N1" s="233"/>
-      <c r="O1" s="233"/>
-      <c r="P1" s="233"/>
-      <c r="Q1" s="233"/>
+      <c r="C1" s="224"/>
+      <c r="D1" s="224"/>
+      <c r="E1" s="224"/>
+      <c r="F1" s="224"/>
+      <c r="G1" s="224"/>
+      <c r="H1" s="224"/>
+      <c r="I1" s="224"/>
+      <c r="J1" s="224"/>
+      <c r="K1" s="224"/>
+      <c r="L1" s="224"/>
+      <c r="M1" s="224"/>
+      <c r="N1" s="224"/>
+      <c r="O1" s="224"/>
+      <c r="P1" s="224"/>
+      <c r="Q1" s="224"/>
     </row>
     <row r="2" spans="1:22" ht="12">
       <c r="B2" s="221" t="s">
         <v>25</v>
       </c>
-      <c r="C2" s="222"/>
-      <c r="D2" s="223" t="s">
+      <c r="C2" s="223"/>
+      <c r="D2" s="225" t="s">
         <v>749</v>
       </c>
-      <c r="E2" s="224"/>
+      <c r="E2" s="226"/>
       <c r="F2" s="29" t="s">
         <v>26</v>
       </c>
       <c r="G2" s="221" t="s">
         <v>751</v>
       </c>
-      <c r="H2" s="225"/>
-      <c r="I2" s="225"/>
-      <c r="J2" s="225"/>
-      <c r="K2" s="225"/>
-      <c r="L2" s="225"/>
-      <c r="M2" s="222"/>
+      <c r="H2" s="222"/>
+      <c r="I2" s="222"/>
+      <c r="J2" s="222"/>
+      <c r="K2" s="222"/>
+      <c r="L2" s="222"/>
+      <c r="M2" s="223"/>
       <c r="N2" s="30" t="s">
         <v>27</v>
       </c>
-      <c r="O2" s="226" t="s">
+      <c r="O2" s="227" t="s">
         <v>753</v>
       </c>
-      <c r="P2" s="227"/>
+      <c r="P2" s="228"/>
       <c r="Q2" s="31"/>
     </row>
     <row r="3" spans="1:22" ht="12">
       <c r="B3" s="221" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="222"/>
-      <c r="D3" s="223" t="s">
+      <c r="C3" s="223"/>
+      <c r="D3" s="225" t="s">
         <v>750</v>
       </c>
-      <c r="E3" s="224"/>
+      <c r="E3" s="226"/>
       <c r="F3" s="29" t="s">
         <v>26</v>
       </c>
       <c r="G3" s="221" t="s">
         <v>752</v>
       </c>
-      <c r="H3" s="225"/>
-      <c r="I3" s="225"/>
-      <c r="J3" s="225"/>
-      <c r="K3" s="225"/>
-      <c r="L3" s="225"/>
-      <c r="M3" s="222"/>
+      <c r="H3" s="222"/>
+      <c r="I3" s="222"/>
+      <c r="J3" s="222"/>
+      <c r="K3" s="222"/>
+      <c r="L3" s="222"/>
+      <c r="M3" s="223"/>
       <c r="N3" s="30" t="s">
         <v>27</v>
       </c>
-      <c r="O3" s="226" t="s">
+      <c r="O3" s="227" t="s">
         <v>754</v>
       </c>
-      <c r="P3" s="227"/>
+      <c r="P3" s="228"/>
       <c r="Q3" s="31"/>
     </row>
     <row r="4" spans="1:22" ht="12">
       <c r="B4" s="221" t="s">
         <v>29</v>
       </c>
-      <c r="C4" s="222"/>
-      <c r="D4" s="228" t="s">
+      <c r="C4" s="223"/>
+      <c r="D4" s="229" t="s">
         <v>755</v>
       </c>
-      <c r="E4" s="229"/>
+      <c r="E4" s="230"/>
       <c r="F4" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="G4" s="230" t="s">
+      <c r="G4" s="231" t="s">
         <v>755</v>
       </c>
-      <c r="H4" s="231"/>
-      <c r="I4" s="231"/>
-      <c r="J4" s="232"/>
+      <c r="H4" s="232"/>
+      <c r="I4" s="232"/>
+      <c r="J4" s="233"/>
       <c r="K4" s="30" t="s">
         <v>31</v>
       </c>
       <c r="L4" s="221" t="s">
         <v>32</v>
       </c>
-      <c r="M4" s="222"/>
+      <c r="M4" s="223"/>
       <c r="N4" s="30" t="s">
         <v>33</v>
       </c>
       <c r="O4" s="221" t="s">
         <v>34</v>
       </c>
-      <c r="P4" s="222"/>
+      <c r="P4" s="223"/>
       <c r="Q4" s="31"/>
     </row>
     <row r="5" spans="1:22" ht="12">
@@ -16014,11 +16561,11 @@
       <c r="B106" s="221" t="s">
         <v>46</v>
       </c>
-      <c r="C106" s="225"/>
-      <c r="D106" s="225"/>
-      <c r="E106" s="225"/>
-      <c r="F106" s="225"/>
-      <c r="G106" s="222"/>
+      <c r="C106" s="222"/>
+      <c r="D106" s="222"/>
+      <c r="E106" s="222"/>
+      <c r="F106" s="222"/>
+      <c r="G106" s="223"/>
       <c r="H106" s="30" t="s">
         <v>47</v>
       </c>
@@ -16032,11 +16579,11 @@
       <c r="B107" s="221" t="s">
         <v>48</v>
       </c>
-      <c r="C107" s="225"/>
-      <c r="D107" s="225"/>
-      <c r="E107" s="225"/>
-      <c r="F107" s="225"/>
-      <c r="G107" s="222"/>
+      <c r="C107" s="222"/>
+      <c r="D107" s="222"/>
+      <c r="E107" s="222"/>
+      <c r="F107" s="222"/>
+      <c r="G107" s="223"/>
       <c r="H107" s="30" t="s">
         <v>47</v>
       </c>
@@ -16047,11 +16594,11 @@
       <c r="B108" s="221" t="s">
         <v>49</v>
       </c>
-      <c r="C108" s="225"/>
-      <c r="D108" s="225"/>
-      <c r="E108" s="225"/>
-      <c r="F108" s="225"/>
-      <c r="G108" s="222"/>
+      <c r="C108" s="222"/>
+      <c r="D108" s="222"/>
+      <c r="E108" s="222"/>
+      <c r="F108" s="222"/>
+      <c r="G108" s="223"/>
       <c r="H108" s="30" t="s">
         <v>47</v>
       </c>
@@ -16062,11 +16609,11 @@
       <c r="B109" s="221" t="s">
         <v>50</v>
       </c>
-      <c r="C109" s="225"/>
-      <c r="D109" s="225"/>
-      <c r="E109" s="225"/>
-      <c r="F109" s="225"/>
-      <c r="G109" s="222"/>
+      <c r="C109" s="222"/>
+      <c r="D109" s="222"/>
+      <c r="E109" s="222"/>
+      <c r="F109" s="222"/>
+      <c r="G109" s="223"/>
       <c r="H109" s="30" t="s">
         <v>47</v>
       </c>
@@ -16088,6 +16635,8 @@
   </sheetData>
   <autoFilter ref="B5:Q5" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
   <mergeCells count="18">
+    <mergeCell ref="L4:M4"/>
+    <mergeCell ref="O4:P4"/>
     <mergeCell ref="B106:G106"/>
     <mergeCell ref="B107:G107"/>
     <mergeCell ref="B108:G108"/>
@@ -16104,8 +16653,6 @@
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="D4:E4"/>
     <mergeCell ref="G4:J4"/>
-    <mergeCell ref="L4:M4"/>
-    <mergeCell ref="O4:P4"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="C6:C10 C13:C16">
@@ -50390,24 +50937,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="162" customHeight="1">
-      <c r="C1" s="260" t="s">
+      <c r="C1" s="286" t="s">
         <v>366</v>
       </c>
-      <c r="D1" s="260"/>
-      <c r="E1" s="260"/>
-      <c r="F1" s="260"/>
-      <c r="G1" s="260"/>
-      <c r="H1" s="260"/>
-      <c r="I1" s="260"/>
-      <c r="J1" s="260"/>
-      <c r="K1" s="260"/>
+      <c r="D1" s="286"/>
+      <c r="E1" s="286"/>
+      <c r="F1" s="286"/>
+      <c r="G1" s="286"/>
+      <c r="H1" s="286"/>
+      <c r="I1" s="286"/>
+      <c r="J1" s="286"/>
+      <c r="K1" s="286"/>
       <c r="L1" s="138" t="s">
         <v>386</v>
       </c>
-      <c r="M1" s="238">
+      <c r="M1" s="265">
         <v>102</v>
       </c>
-      <c r="N1" s="238"/>
+      <c r="N1" s="265"/>
       <c r="R1" s="23">
         <f ca="1">D16</f>
         <v>0</v>
@@ -50429,30 +50976,30 @@
       <c r="A2" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="237" t="s">
+      <c r="B2" s="264" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="237"/>
+      <c r="C2" s="264"/>
       <c r="D2" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="239" t="s">
+      <c r="E2" s="266" t="s">
         <v>757</v>
       </c>
-      <c r="F2" s="239"/>
-      <c r="G2" s="240"/>
-      <c r="H2" s="240"/>
-      <c r="I2" s="246" t="s">
+      <c r="F2" s="266"/>
+      <c r="G2" s="267"/>
+      <c r="H2" s="267"/>
+      <c r="I2" s="273" t="s">
         <v>203</v>
       </c>
-      <c r="J2" s="247"/>
-      <c r="K2" s="248"/>
-      <c r="L2" s="255" t="str">
+      <c r="J2" s="274"/>
+      <c r="K2" s="275"/>
+      <c r="L2" s="282" t="str">
         <f ca="1">IFERROR(INDEX('고객 리스트'!$A$4:$D$83,MATCH(N2,'고객 리스트'!$A$4:$A$83,0),2)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="M2" s="256"/>
-      <c r="N2" s="244" t="str">
+      <c r="M2" s="283"/>
+      <c r="N2" s="271" t="str">
         <f ca="1">MID(CELL("filename",A1),FIND("]",CELL("filename",A1))+1,255)</f>
         <v>LKA 01</v>
       </c>
@@ -50479,21 +51026,21 @@
       <c r="A3" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="237" t="s">
+      <c r="B3" s="264" t="s">
         <v>330</v>
       </c>
-      <c r="C3" s="237"/>
-      <c r="D3" s="237"/>
-      <c r="E3" s="237"/>
-      <c r="F3" s="237"/>
-      <c r="G3" s="237"/>
-      <c r="H3" s="237"/>
-      <c r="I3" s="249"/>
-      <c r="J3" s="250"/>
-      <c r="K3" s="251"/>
-      <c r="L3" s="257"/>
-      <c r="M3" s="258"/>
-      <c r="N3" s="245"/>
+      <c r="C3" s="264"/>
+      <c r="D3" s="264"/>
+      <c r="E3" s="264"/>
+      <c r="F3" s="264"/>
+      <c r="G3" s="264"/>
+      <c r="H3" s="264"/>
+      <c r="I3" s="276"/>
+      <c r="J3" s="277"/>
+      <c r="K3" s="278"/>
+      <c r="L3" s="284"/>
+      <c r="M3" s="285"/>
+      <c r="N3" s="272"/>
       <c r="Q3" s="3"/>
       <c r="R3" s="3"/>
       <c r="S3" s="3"/>
@@ -50516,26 +51063,26 @@
       <c r="A4" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="237" t="s">
+      <c r="B4" s="264" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="237"/>
-      <c r="D4" s="237"/>
-      <c r="E4" s="237"/>
-      <c r="F4" s="237"/>
-      <c r="G4" s="237"/>
-      <c r="H4" s="237"/>
-      <c r="I4" s="252" t="s">
+      <c r="C4" s="264"/>
+      <c r="D4" s="264"/>
+      <c r="E4" s="264"/>
+      <c r="F4" s="264"/>
+      <c r="G4" s="264"/>
+      <c r="H4" s="264"/>
+      <c r="I4" s="279" t="s">
         <v>9</v>
       </c>
-      <c r="J4" s="253"/>
-      <c r="K4" s="254"/>
-      <c r="L4" s="241" t="str">
+      <c r="J4" s="280"/>
+      <c r="K4" s="281"/>
+      <c r="L4" s="268" t="str">
         <f ca="1">IFERROR(VLOOKUP($N$2&amp;"_"&amp;$A$6,'물품 입고 내역'!$A$5:$N$105,6,0)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="M4" s="242"/>
-      <c r="N4" s="243"/>
+      <c r="M4" s="269"/>
+      <c r="N4" s="270"/>
       <c r="T4" s="57" t="s">
         <v>1</v>
       </c>
@@ -50570,11 +51117,11 @@
       <c r="F5" s="133" t="s">
         <v>324</v>
       </c>
-      <c r="G5" s="237" t="s">
+      <c r="G5" s="264" t="s">
         <v>385</v>
       </c>
-      <c r="H5" s="237"/>
-      <c r="I5" s="237"/>
+      <c r="H5" s="264"/>
+      <c r="I5" s="264"/>
       <c r="J5" s="26" t="s">
         <v>322</v>
       </c>
@@ -51162,11 +51709,11 @@
       </c>
     </row>
     <row r="16" spans="1:23" s="2" customFormat="1" ht="41.25">
-      <c r="A16" s="237" t="s">
+      <c r="A16" s="264" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="237"/>
-      <c r="C16" s="237"/>
+      <c r="B16" s="264"/>
+      <c r="C16" s="264"/>
       <c r="D16" s="4">
         <f ca="1">SUM(D6:D15)</f>
         <v>0</v>
@@ -51189,45 +51736,45 @@
       <c r="N16" s="14"/>
     </row>
     <row r="17" spans="1:14" s="2" customFormat="1" ht="54">
-      <c r="A17" s="259" t="s">
+      <c r="A17" s="238" t="s">
         <v>332</v>
       </c>
-      <c r="B17" s="259"/>
-      <c r="C17" s="259"/>
-      <c r="D17" s="259"/>
-      <c r="E17" s="259"/>
-      <c r="F17" s="259" t="s">
+      <c r="B17" s="238"/>
+      <c r="C17" s="238"/>
+      <c r="D17" s="238"/>
+      <c r="E17" s="238"/>
+      <c r="F17" s="238" t="s">
         <v>333</v>
       </c>
-      <c r="G17" s="259"/>
-      <c r="H17" s="259"/>
-      <c r="I17" s="259"/>
-      <c r="J17" s="259"/>
-      <c r="K17" s="259"/>
-      <c r="L17" s="237" t="s">
+      <c r="G17" s="238"/>
+      <c r="H17" s="238"/>
+      <c r="I17" s="238"/>
+      <c r="J17" s="238"/>
+      <c r="K17" s="238"/>
+      <c r="L17" s="264" t="s">
         <v>15</v>
       </c>
-      <c r="M17" s="237"/>
+      <c r="M17" s="264"/>
       <c r="N17" s="136">
         <f ca="1">SUM(N6:N16)</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:14" s="2" customFormat="1" ht="54">
-      <c r="A18" s="286" t="str">
+      <c r="A18" s="242" t="str">
         <f ca="1">IFERROR(VLOOKUP($N$2&amp;"_"&amp;$A$6,'물품 입고 내역'!$A$5:$O$522,4,0)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="B18" s="286"/>
-      <c r="C18" s="286"/>
-      <c r="D18" s="286"/>
-      <c r="E18" s="286"/>
-      <c r="F18" s="283"/>
-      <c r="G18" s="283"/>
-      <c r="H18" s="283"/>
-      <c r="I18" s="283"/>
-      <c r="J18" s="283"/>
-      <c r="K18" s="283"/>
+      <c r="B18" s="242"/>
+      <c r="C18" s="242"/>
+      <c r="D18" s="242"/>
+      <c r="E18" s="242"/>
+      <c r="F18" s="239"/>
+      <c r="G18" s="239"/>
+      <c r="H18" s="239"/>
+      <c r="I18" s="239"/>
+      <c r="J18" s="239"/>
+      <c r="K18" s="239"/>
       <c r="L18" s="141" t="s">
         <v>16</v>
       </c>
@@ -51241,17 +51788,17 @@
       </c>
     </row>
     <row r="19" spans="1:14" s="2" customFormat="1" ht="54">
-      <c r="A19" s="286"/>
-      <c r="B19" s="286"/>
-      <c r="C19" s="286"/>
-      <c r="D19" s="286"/>
-      <c r="E19" s="286"/>
-      <c r="F19" s="283"/>
-      <c r="G19" s="283"/>
-      <c r="H19" s="283"/>
-      <c r="I19" s="283"/>
-      <c r="J19" s="283"/>
-      <c r="K19" s="283"/>
+      <c r="A19" s="242"/>
+      <c r="B19" s="242"/>
+      <c r="C19" s="242"/>
+      <c r="D19" s="242"/>
+      <c r="E19" s="242"/>
+      <c r="F19" s="239"/>
+      <c r="G19" s="239"/>
+      <c r="H19" s="239"/>
+      <c r="I19" s="239"/>
+      <c r="J19" s="239"/>
+      <c r="K19" s="239"/>
       <c r="L19" s="141" t="s">
         <v>468</v>
       </c>
@@ -51265,17 +51812,17 @@
       </c>
     </row>
     <row r="20" spans="1:14" s="2" customFormat="1" ht="54">
-      <c r="A20" s="286"/>
-      <c r="B20" s="286"/>
-      <c r="C20" s="286"/>
-      <c r="D20" s="286"/>
-      <c r="E20" s="286"/>
-      <c r="F20" s="283"/>
-      <c r="G20" s="283"/>
-      <c r="H20" s="283"/>
-      <c r="I20" s="283"/>
-      <c r="J20" s="283"/>
-      <c r="K20" s="283"/>
+      <c r="A20" s="242"/>
+      <c r="B20" s="242"/>
+      <c r="C20" s="242"/>
+      <c r="D20" s="242"/>
+      <c r="E20" s="242"/>
+      <c r="F20" s="239"/>
+      <c r="G20" s="239"/>
+      <c r="H20" s="239"/>
+      <c r="I20" s="239"/>
+      <c r="J20" s="239"/>
+      <c r="K20" s="239"/>
       <c r="L20" s="141" t="s">
         <v>469</v>
       </c>
@@ -51289,18 +51836,18 @@
       </c>
     </row>
     <row r="21" spans="1:14" s="2" customFormat="1" ht="54">
-      <c r="A21" s="286"/>
-      <c r="B21" s="286"/>
-      <c r="C21" s="286"/>
-      <c r="D21" s="286"/>
-      <c r="E21" s="286"/>
-      <c r="F21" s="283"/>
-      <c r="G21" s="283"/>
-      <c r="H21" s="283"/>
-      <c r="I21" s="283"/>
-      <c r="J21" s="283"/>
-      <c r="K21" s="283"/>
-      <c r="L21" s="284" t="s">
+      <c r="A21" s="242"/>
+      <c r="B21" s="242"/>
+      <c r="C21" s="242"/>
+      <c r="D21" s="242"/>
+      <c r="E21" s="242"/>
+      <c r="F21" s="239"/>
+      <c r="G21" s="239"/>
+      <c r="H21" s="239"/>
+      <c r="I21" s="239"/>
+      <c r="J21" s="239"/>
+      <c r="K21" s="239"/>
+      <c r="L21" s="240" t="s">
         <v>334</v>
       </c>
       <c r="M21" s="126" t="s">
@@ -51312,18 +51859,18 @@
       </c>
     </row>
     <row r="22" spans="1:14" s="2" customFormat="1" ht="54">
-      <c r="A22" s="286"/>
-      <c r="B22" s="286"/>
-      <c r="C22" s="286"/>
-      <c r="D22" s="286"/>
-      <c r="E22" s="286"/>
-      <c r="F22" s="283"/>
-      <c r="G22" s="283"/>
-      <c r="H22" s="283"/>
-      <c r="I22" s="283"/>
-      <c r="J22" s="283"/>
-      <c r="K22" s="283"/>
-      <c r="L22" s="285"/>
+      <c r="A22" s="242"/>
+      <c r="B22" s="242"/>
+      <c r="C22" s="242"/>
+      <c r="D22" s="242"/>
+      <c r="E22" s="242"/>
+      <c r="F22" s="239"/>
+      <c r="G22" s="239"/>
+      <c r="H22" s="239"/>
+      <c r="I22" s="239"/>
+      <c r="J22" s="239"/>
+      <c r="K22" s="239"/>
+      <c r="L22" s="241"/>
       <c r="M22" s="127" t="s">
         <v>18</v>
       </c>
@@ -51333,18 +51880,18 @@
       </c>
     </row>
     <row r="23" spans="1:14" s="2" customFormat="1" ht="54">
-      <c r="A23" s="286"/>
-      <c r="B23" s="286"/>
-      <c r="C23" s="286"/>
-      <c r="D23" s="286"/>
-      <c r="E23" s="286"/>
-      <c r="F23" s="283"/>
-      <c r="G23" s="283"/>
-      <c r="H23" s="283"/>
-      <c r="I23" s="283"/>
-      <c r="J23" s="283"/>
-      <c r="K23" s="283"/>
-      <c r="L23" s="285"/>
+      <c r="A23" s="242"/>
+      <c r="B23" s="242"/>
+      <c r="C23" s="242"/>
+      <c r="D23" s="242"/>
+      <c r="E23" s="242"/>
+      <c r="F23" s="239"/>
+      <c r="G23" s="239"/>
+      <c r="H23" s="239"/>
+      <c r="I23" s="239"/>
+      <c r="J23" s="239"/>
+      <c r="K23" s="239"/>
+      <c r="L23" s="241"/>
       <c r="M23" s="139" t="s">
         <v>19</v>
       </c>
@@ -51354,18 +51901,18 @@
       </c>
     </row>
     <row r="24" spans="1:14" s="2" customFormat="1" ht="54">
-      <c r="A24" s="286"/>
-      <c r="B24" s="286"/>
-      <c r="C24" s="286"/>
-      <c r="D24" s="286"/>
-      <c r="E24" s="286"/>
-      <c r="F24" s="283"/>
-      <c r="G24" s="283"/>
-      <c r="H24" s="283"/>
-      <c r="I24" s="283"/>
-      <c r="J24" s="283"/>
-      <c r="K24" s="283"/>
-      <c r="L24" s="285"/>
+      <c r="A24" s="242"/>
+      <c r="B24" s="242"/>
+      <c r="C24" s="242"/>
+      <c r="D24" s="242"/>
+      <c r="E24" s="242"/>
+      <c r="F24" s="239"/>
+      <c r="G24" s="239"/>
+      <c r="H24" s="239"/>
+      <c r="I24" s="239"/>
+      <c r="J24" s="239"/>
+      <c r="K24" s="239"/>
+      <c r="L24" s="241"/>
       <c r="M24" s="15" t="s">
         <v>20</v>
       </c>
@@ -51391,162 +51938,162 @@
       <c r="N25" s="151"/>
     </row>
     <row r="26" spans="1:14" s="2" customFormat="1" ht="39">
-      <c r="A26" s="282" t="s">
+      <c r="A26" s="237" t="s">
         <v>327</v>
       </c>
-      <c r="B26" s="282"/>
-      <c r="C26" s="282"/>
-      <c r="D26" s="282"/>
-      <c r="E26" s="282"/>
-      <c r="F26" s="282"/>
-      <c r="G26" s="282"/>
-      <c r="H26" s="282"/>
-      <c r="I26" s="282"/>
-      <c r="J26" s="282"/>
-      <c r="K26" s="282"/>
-      <c r="L26" s="282"/>
-      <c r="M26" s="282"/>
-      <c r="N26" s="282"/>
+      <c r="B26" s="237"/>
+      <c r="C26" s="237"/>
+      <c r="D26" s="237"/>
+      <c r="E26" s="237"/>
+      <c r="F26" s="237"/>
+      <c r="G26" s="237"/>
+      <c r="H26" s="237"/>
+      <c r="I26" s="237"/>
+      <c r="J26" s="237"/>
+      <c r="K26" s="237"/>
+      <c r="L26" s="237"/>
+      <c r="M26" s="237"/>
+      <c r="N26" s="237"/>
     </row>
     <row r="27" spans="1:14" s="2" customFormat="1" ht="37.5">
-      <c r="A27" s="263" t="s">
+      <c r="A27" s="245" t="s">
         <v>470</v>
       </c>
-      <c r="B27" s="263"/>
-      <c r="C27" s="263"/>
-      <c r="D27" s="263"/>
-      <c r="E27" s="263"/>
-      <c r="F27" s="263"/>
-      <c r="G27" s="263"/>
-      <c r="H27" s="263"/>
-      <c r="I27" s="263"/>
-      <c r="J27" s="263"/>
-      <c r="K27" s="263"/>
-      <c r="L27" s="263"/>
-      <c r="M27" s="263"/>
-      <c r="N27" s="263"/>
+      <c r="B27" s="245"/>
+      <c r="C27" s="245"/>
+      <c r="D27" s="245"/>
+      <c r="E27" s="245"/>
+      <c r="F27" s="245"/>
+      <c r="G27" s="245"/>
+      <c r="H27" s="245"/>
+      <c r="I27" s="245"/>
+      <c r="J27" s="245"/>
+      <c r="K27" s="245"/>
+      <c r="L27" s="245"/>
+      <c r="M27" s="245"/>
+      <c r="N27" s="245"/>
     </row>
     <row r="28" spans="1:14" s="2" customFormat="1" ht="39">
-      <c r="A28" s="279" t="s">
+      <c r="A28" s="261" t="s">
         <v>853</v>
       </c>
-      <c r="B28" s="279"/>
-      <c r="C28" s="279"/>
-      <c r="D28" s="279"/>
-      <c r="E28" s="279"/>
-      <c r="F28" s="279"/>
-      <c r="G28" s="279"/>
-      <c r="H28" s="279"/>
-      <c r="I28" s="279"/>
-      <c r="J28" s="279"/>
-      <c r="K28" s="279"/>
-      <c r="L28" s="279"/>
-      <c r="M28" s="279"/>
-      <c r="N28" s="279"/>
+      <c r="B28" s="261"/>
+      <c r="C28" s="261"/>
+      <c r="D28" s="261"/>
+      <c r="E28" s="261"/>
+      <c r="F28" s="261"/>
+      <c r="G28" s="261"/>
+      <c r="H28" s="261"/>
+      <c r="I28" s="261"/>
+      <c r="J28" s="261"/>
+      <c r="K28" s="261"/>
+      <c r="L28" s="261"/>
+      <c r="M28" s="261"/>
+      <c r="N28" s="261"/>
     </row>
     <row r="29" spans="1:14" s="2" customFormat="1" ht="37.5">
-      <c r="A29" s="263" t="s">
+      <c r="A29" s="245" t="s">
         <v>854</v>
       </c>
-      <c r="B29" s="263"/>
-      <c r="C29" s="263"/>
-      <c r="D29" s="263"/>
-      <c r="E29" s="263"/>
-      <c r="F29" s="263"/>
-      <c r="G29" s="263"/>
-      <c r="H29" s="263"/>
-      <c r="I29" s="263"/>
-      <c r="J29" s="263"/>
-      <c r="K29" s="263"/>
-      <c r="L29" s="263"/>
-      <c r="M29" s="263"/>
-      <c r="N29" s="263"/>
+      <c r="B29" s="245"/>
+      <c r="C29" s="245"/>
+      <c r="D29" s="245"/>
+      <c r="E29" s="245"/>
+      <c r="F29" s="245"/>
+      <c r="G29" s="245"/>
+      <c r="H29" s="245"/>
+      <c r="I29" s="245"/>
+      <c r="J29" s="245"/>
+      <c r="K29" s="245"/>
+      <c r="L29" s="245"/>
+      <c r="M29" s="245"/>
+      <c r="N29" s="245"/>
     </row>
     <row r="30" spans="1:14" s="2" customFormat="1" ht="40.15" customHeight="1">
-      <c r="A30" s="264" t="s">
+      <c r="A30" s="246" t="s">
         <v>21</v>
       </c>
-      <c r="B30" s="265"/>
-      <c r="C30" s="270"/>
-      <c r="D30" s="271"/>
-      <c r="E30" s="272"/>
+      <c r="B30" s="247"/>
+      <c r="C30" s="252"/>
+      <c r="D30" s="253"/>
+      <c r="E30" s="254"/>
       <c r="F30" s="178"/>
       <c r="G30" s="16"/>
-      <c r="H30" s="280" t="s">
+      <c r="H30" s="262" t="s">
         <v>471</v>
       </c>
-      <c r="I30" s="280"/>
-      <c r="J30" s="281"/>
-      <c r="K30" s="261" t="s">
+      <c r="I30" s="262"/>
+      <c r="J30" s="263"/>
+      <c r="K30" s="243" t="s">
         <v>22</v>
       </c>
-      <c r="L30" s="262"/>
-      <c r="M30" s="262"/>
-      <c r="N30" s="262"/>
+      <c r="L30" s="244"/>
+      <c r="M30" s="244"/>
+      <c r="N30" s="244"/>
     </row>
     <row r="31" spans="1:14" s="2" customFormat="1" ht="40.15" customHeight="1">
-      <c r="A31" s="266"/>
-      <c r="B31" s="267"/>
-      <c r="C31" s="273"/>
-      <c r="D31" s="274"/>
-      <c r="E31" s="275"/>
+      <c r="A31" s="248"/>
+      <c r="B31" s="249"/>
+      <c r="C31" s="255"/>
+      <c r="D31" s="256"/>
+      <c r="E31" s="257"/>
       <c r="F31" s="27"/>
       <c r="G31" s="27"/>
       <c r="H31" s="16"/>
       <c r="I31" s="16"/>
       <c r="J31" s="179"/>
-      <c r="K31" s="261"/>
-      <c r="L31" s="262"/>
-      <c r="M31" s="262"/>
-      <c r="N31" s="262"/>
+      <c r="K31" s="243"/>
+      <c r="L31" s="244"/>
+      <c r="M31" s="244"/>
+      <c r="N31" s="244"/>
     </row>
     <row r="32" spans="1:14" s="2" customFormat="1" ht="40.15" customHeight="1">
-      <c r="A32" s="266"/>
-      <c r="B32" s="267"/>
-      <c r="C32" s="273"/>
-      <c r="D32" s="274"/>
-      <c r="E32" s="275"/>
+      <c r="A32" s="248"/>
+      <c r="B32" s="249"/>
+      <c r="C32" s="255"/>
+      <c r="D32" s="256"/>
+      <c r="E32" s="257"/>
       <c r="F32" s="27"/>
       <c r="G32" s="27"/>
       <c r="H32" s="27"/>
       <c r="I32" s="16"/>
       <c r="J32" s="16"/>
-      <c r="K32" s="261"/>
-      <c r="L32" s="262"/>
-      <c r="M32" s="262"/>
-      <c r="N32" s="262"/>
+      <c r="K32" s="243"/>
+      <c r="L32" s="244"/>
+      <c r="M32" s="244"/>
+      <c r="N32" s="244"/>
     </row>
     <row r="33" spans="1:22" s="2" customFormat="1" ht="40.15" customHeight="1">
-      <c r="A33" s="266"/>
-      <c r="B33" s="267"/>
-      <c r="C33" s="273"/>
-      <c r="D33" s="274"/>
-      <c r="E33" s="275"/>
+      <c r="A33" s="248"/>
+      <c r="B33" s="249"/>
+      <c r="C33" s="255"/>
+      <c r="D33" s="256"/>
+      <c r="E33" s="257"/>
       <c r="F33" s="27"/>
       <c r="G33" s="27"/>
       <c r="H33" s="27"/>
       <c r="I33" s="16"/>
       <c r="J33" s="16"/>
-      <c r="K33" s="261"/>
-      <c r="L33" s="262"/>
-      <c r="M33" s="262"/>
-      <c r="N33" s="262"/>
+      <c r="K33" s="243"/>
+      <c r="L33" s="244"/>
+      <c r="M33" s="244"/>
+      <c r="N33" s="244"/>
     </row>
     <row r="34" spans="1:22" s="2" customFormat="1" ht="40.15" customHeight="1">
-      <c r="A34" s="268"/>
-      <c r="B34" s="269"/>
-      <c r="C34" s="276"/>
-      <c r="D34" s="277"/>
-      <c r="E34" s="278"/>
+      <c r="A34" s="250"/>
+      <c r="B34" s="251"/>
+      <c r="C34" s="258"/>
+      <c r="D34" s="259"/>
+      <c r="E34" s="260"/>
       <c r="F34" s="27"/>
       <c r="G34" s="27"/>
       <c r="H34" s="27"/>
       <c r="I34" s="16"/>
       <c r="J34" s="16"/>
-      <c r="K34" s="261"/>
-      <c r="L34" s="262"/>
-      <c r="M34" s="262"/>
-      <c r="N34" s="262"/>
+      <c r="K34" s="243"/>
+      <c r="L34" s="244"/>
+      <c r="M34" s="244"/>
+      <c r="N34" s="244"/>
     </row>
     <row r="35" spans="1:22" s="2" customFormat="1" ht="31.5">
       <c r="A35" s="3"/>
@@ -51635,19 +52182,6 @@
     <row r="68" ht="23.25" customHeight="1"/>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="A26:N26"/>
-    <mergeCell ref="F17:K17"/>
-    <mergeCell ref="F18:K24"/>
-    <mergeCell ref="L21:L24"/>
-    <mergeCell ref="A18:E24"/>
-    <mergeCell ref="K30:K34"/>
-    <mergeCell ref="L30:N34"/>
-    <mergeCell ref="A27:N27"/>
-    <mergeCell ref="A30:B34"/>
-    <mergeCell ref="C30:E34"/>
-    <mergeCell ref="A29:N29"/>
-    <mergeCell ref="A28:N28"/>
-    <mergeCell ref="H30:J30"/>
     <mergeCell ref="A16:C16"/>
     <mergeCell ref="L17:M17"/>
     <mergeCell ref="M1:N1"/>
@@ -51663,6 +52197,19 @@
     <mergeCell ref="A17:E17"/>
     <mergeCell ref="C1:K1"/>
     <mergeCell ref="G5:I5"/>
+    <mergeCell ref="K30:K34"/>
+    <mergeCell ref="L30:N34"/>
+    <mergeCell ref="A27:N27"/>
+    <mergeCell ref="A30:B34"/>
+    <mergeCell ref="C30:E34"/>
+    <mergeCell ref="A29:N29"/>
+    <mergeCell ref="A28:N28"/>
+    <mergeCell ref="H30:J30"/>
+    <mergeCell ref="A26:N26"/>
+    <mergeCell ref="F17:K17"/>
+    <mergeCell ref="F18:K24"/>
+    <mergeCell ref="L21:L24"/>
+    <mergeCell ref="A18:E24"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="L6:L15">
@@ -51713,24 +52260,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="162" customHeight="1">
-      <c r="C1" s="260" t="s">
+      <c r="C1" s="286" t="s">
         <v>366</v>
       </c>
-      <c r="D1" s="260"/>
-      <c r="E1" s="260"/>
-      <c r="F1" s="260"/>
-      <c r="G1" s="260"/>
-      <c r="H1" s="260"/>
-      <c r="I1" s="260"/>
-      <c r="J1" s="260"/>
-      <c r="K1" s="260"/>
+      <c r="D1" s="286"/>
+      <c r="E1" s="286"/>
+      <c r="F1" s="286"/>
+      <c r="G1" s="286"/>
+      <c r="H1" s="286"/>
+      <c r="I1" s="286"/>
+      <c r="J1" s="286"/>
+      <c r="K1" s="286"/>
       <c r="L1" s="138" t="s">
         <v>386</v>
       </c>
-      <c r="M1" s="238">
+      <c r="M1" s="265">
         <v>102</v>
       </c>
-      <c r="N1" s="238"/>
+      <c r="N1" s="265"/>
       <c r="R1" s="23">
         <f ca="1">D16</f>
         <v>0</v>
@@ -51752,30 +52299,30 @@
       <c r="A2" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="237" t="s">
+      <c r="B2" s="264" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="237"/>
+      <c r="C2" s="264"/>
       <c r="D2" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="239" t="s">
+      <c r="E2" s="266" t="s">
         <v>757</v>
       </c>
-      <c r="F2" s="239"/>
-      <c r="G2" s="240"/>
-      <c r="H2" s="240"/>
-      <c r="I2" s="246" t="s">
+      <c r="F2" s="266"/>
+      <c r="G2" s="267"/>
+      <c r="H2" s="267"/>
+      <c r="I2" s="273" t="s">
         <v>203</v>
       </c>
-      <c r="J2" s="247"/>
-      <c r="K2" s="248"/>
-      <c r="L2" s="255" t="str">
+      <c r="J2" s="274"/>
+      <c r="K2" s="275"/>
+      <c r="L2" s="282" t="str">
         <f ca="1">IFERROR(INDEX('고객 리스트'!$A$4:$D$83,MATCH(N2,'고객 리스트'!$A$4:$A$83,0),2)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="M2" s="256"/>
-      <c r="N2" s="244" t="str">
+      <c r="M2" s="283"/>
+      <c r="N2" s="271" t="str">
         <f ca="1">MID(CELL("filename",A1),FIND("]",CELL("filename",A1))+1,255)</f>
         <v>LKA XX</v>
       </c>
@@ -51802,21 +52349,21 @@
       <c r="A3" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="237" t="s">
+      <c r="B3" s="264" t="s">
         <v>330</v>
       </c>
-      <c r="C3" s="237"/>
-      <c r="D3" s="237"/>
-      <c r="E3" s="237"/>
-      <c r="F3" s="237"/>
-      <c r="G3" s="237"/>
-      <c r="H3" s="237"/>
-      <c r="I3" s="249"/>
-      <c r="J3" s="250"/>
-      <c r="K3" s="251"/>
-      <c r="L3" s="257"/>
-      <c r="M3" s="258"/>
-      <c r="N3" s="245"/>
+      <c r="C3" s="264"/>
+      <c r="D3" s="264"/>
+      <c r="E3" s="264"/>
+      <c r="F3" s="264"/>
+      <c r="G3" s="264"/>
+      <c r="H3" s="264"/>
+      <c r="I3" s="276"/>
+      <c r="J3" s="277"/>
+      <c r="K3" s="278"/>
+      <c r="L3" s="284"/>
+      <c r="M3" s="285"/>
+      <c r="N3" s="272"/>
       <c r="Q3" s="3"/>
       <c r="R3" s="3"/>
       <c r="S3" s="3"/>
@@ -51839,26 +52386,26 @@
       <c r="A4" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="237" t="s">
+      <c r="B4" s="264" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="237"/>
-      <c r="D4" s="237"/>
-      <c r="E4" s="237"/>
-      <c r="F4" s="237"/>
-      <c r="G4" s="237"/>
-      <c r="H4" s="237"/>
-      <c r="I4" s="252" t="s">
+      <c r="C4" s="264"/>
+      <c r="D4" s="264"/>
+      <c r="E4" s="264"/>
+      <c r="F4" s="264"/>
+      <c r="G4" s="264"/>
+      <c r="H4" s="264"/>
+      <c r="I4" s="279" t="s">
         <v>9</v>
       </c>
-      <c r="J4" s="253"/>
-      <c r="K4" s="254"/>
-      <c r="L4" s="241" t="str">
+      <c r="J4" s="280"/>
+      <c r="K4" s="281"/>
+      <c r="L4" s="268" t="str">
         <f ca="1">IFERROR(VLOOKUP($N$2&amp;"_"&amp;$A$6,'물품 입고 내역'!$A$5:$N$105,6,0)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="M4" s="242"/>
-      <c r="N4" s="243"/>
+      <c r="M4" s="269"/>
+      <c r="N4" s="270"/>
       <c r="T4" s="57" t="s">
         <v>1</v>
       </c>
@@ -51893,11 +52440,11 @@
       <c r="F5" s="133" t="s">
         <v>324</v>
       </c>
-      <c r="G5" s="237" t="s">
+      <c r="G5" s="264" t="s">
         <v>385</v>
       </c>
-      <c r="H5" s="237"/>
-      <c r="I5" s="237"/>
+      <c r="H5" s="264"/>
+      <c r="I5" s="264"/>
       <c r="J5" s="26" t="s">
         <v>322</v>
       </c>
@@ -52485,11 +53032,11 @@
       </c>
     </row>
     <row r="16" spans="1:23" s="2" customFormat="1" ht="41.25">
-      <c r="A16" s="237" t="s">
+      <c r="A16" s="264" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="237"/>
-      <c r="C16" s="237"/>
+      <c r="B16" s="264"/>
+      <c r="C16" s="264"/>
       <c r="D16" s="4">
         <f ca="1">SUM(D6:D15)</f>
         <v>0</v>
@@ -52512,45 +53059,45 @@
       <c r="N16" s="14"/>
     </row>
     <row r="17" spans="1:14" s="2" customFormat="1" ht="54">
-      <c r="A17" s="259" t="s">
+      <c r="A17" s="238" t="s">
         <v>332</v>
       </c>
-      <c r="B17" s="259"/>
-      <c r="C17" s="259"/>
-      <c r="D17" s="259"/>
-      <c r="E17" s="259"/>
-      <c r="F17" s="259" t="s">
+      <c r="B17" s="238"/>
+      <c r="C17" s="238"/>
+      <c r="D17" s="238"/>
+      <c r="E17" s="238"/>
+      <c r="F17" s="238" t="s">
         <v>333</v>
       </c>
-      <c r="G17" s="259"/>
-      <c r="H17" s="259"/>
-      <c r="I17" s="259"/>
-      <c r="J17" s="259"/>
-      <c r="K17" s="259"/>
-      <c r="L17" s="237" t="s">
+      <c r="G17" s="238"/>
+      <c r="H17" s="238"/>
+      <c r="I17" s="238"/>
+      <c r="J17" s="238"/>
+      <c r="K17" s="238"/>
+      <c r="L17" s="264" t="s">
         <v>15</v>
       </c>
-      <c r="M17" s="237"/>
+      <c r="M17" s="264"/>
       <c r="N17" s="136">
         <f ca="1">SUM(N6:N16)</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:14" s="2" customFormat="1" ht="54">
-      <c r="A18" s="286" t="str">
+      <c r="A18" s="242" t="str">
         <f ca="1">IFERROR(VLOOKUP($N$2&amp;"_"&amp;$A$6,'물품 입고 내역'!$A$5:$O$522,4,0)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="B18" s="286"/>
-      <c r="C18" s="286"/>
-      <c r="D18" s="286"/>
-      <c r="E18" s="286"/>
-      <c r="F18" s="283"/>
-      <c r="G18" s="283"/>
-      <c r="H18" s="283"/>
-      <c r="I18" s="283"/>
-      <c r="J18" s="283"/>
-      <c r="K18" s="283"/>
+      <c r="B18" s="242"/>
+      <c r="C18" s="242"/>
+      <c r="D18" s="242"/>
+      <c r="E18" s="242"/>
+      <c r="F18" s="239"/>
+      <c r="G18" s="239"/>
+      <c r="H18" s="239"/>
+      <c r="I18" s="239"/>
+      <c r="J18" s="239"/>
+      <c r="K18" s="239"/>
       <c r="L18" s="141" t="s">
         <v>16</v>
       </c>
@@ -52564,17 +53111,17 @@
       </c>
     </row>
     <row r="19" spans="1:14" s="2" customFormat="1" ht="54">
-      <c r="A19" s="286"/>
-      <c r="B19" s="286"/>
-      <c r="C19" s="286"/>
-      <c r="D19" s="286"/>
-      <c r="E19" s="286"/>
-      <c r="F19" s="283"/>
-      <c r="G19" s="283"/>
-      <c r="H19" s="283"/>
-      <c r="I19" s="283"/>
-      <c r="J19" s="283"/>
-      <c r="K19" s="283"/>
+      <c r="A19" s="242"/>
+      <c r="B19" s="242"/>
+      <c r="C19" s="242"/>
+      <c r="D19" s="242"/>
+      <c r="E19" s="242"/>
+      <c r="F19" s="239"/>
+      <c r="G19" s="239"/>
+      <c r="H19" s="239"/>
+      <c r="I19" s="239"/>
+      <c r="J19" s="239"/>
+      <c r="K19" s="239"/>
       <c r="L19" s="141" t="s">
         <v>468</v>
       </c>
@@ -52588,17 +53135,17 @@
       </c>
     </row>
     <row r="20" spans="1:14" s="2" customFormat="1" ht="54">
-      <c r="A20" s="286"/>
-      <c r="B20" s="286"/>
-      <c r="C20" s="286"/>
-      <c r="D20" s="286"/>
-      <c r="E20" s="286"/>
-      <c r="F20" s="283"/>
-      <c r="G20" s="283"/>
-      <c r="H20" s="283"/>
-      <c r="I20" s="283"/>
-      <c r="J20" s="283"/>
-      <c r="K20" s="283"/>
+      <c r="A20" s="242"/>
+      <c r="B20" s="242"/>
+      <c r="C20" s="242"/>
+      <c r="D20" s="242"/>
+      <c r="E20" s="242"/>
+      <c r="F20" s="239"/>
+      <c r="G20" s="239"/>
+      <c r="H20" s="239"/>
+      <c r="I20" s="239"/>
+      <c r="J20" s="239"/>
+      <c r="K20" s="239"/>
       <c r="L20" s="141" t="s">
         <v>469</v>
       </c>
@@ -52612,18 +53159,18 @@
       </c>
     </row>
     <row r="21" spans="1:14" s="2" customFormat="1" ht="54">
-      <c r="A21" s="286"/>
-      <c r="B21" s="286"/>
-      <c r="C21" s="286"/>
-      <c r="D21" s="286"/>
-      <c r="E21" s="286"/>
-      <c r="F21" s="283"/>
-      <c r="G21" s="283"/>
-      <c r="H21" s="283"/>
-      <c r="I21" s="283"/>
-      <c r="J21" s="283"/>
-      <c r="K21" s="283"/>
-      <c r="L21" s="284" t="s">
+      <c r="A21" s="242"/>
+      <c r="B21" s="242"/>
+      <c r="C21" s="242"/>
+      <c r="D21" s="242"/>
+      <c r="E21" s="242"/>
+      <c r="F21" s="239"/>
+      <c r="G21" s="239"/>
+      <c r="H21" s="239"/>
+      <c r="I21" s="239"/>
+      <c r="J21" s="239"/>
+      <c r="K21" s="239"/>
+      <c r="L21" s="240" t="s">
         <v>334</v>
       </c>
       <c r="M21" s="126" t="s">
@@ -52635,18 +53182,18 @@
       </c>
     </row>
     <row r="22" spans="1:14" s="2" customFormat="1" ht="54">
-      <c r="A22" s="286"/>
-      <c r="B22" s="286"/>
-      <c r="C22" s="286"/>
-      <c r="D22" s="286"/>
-      <c r="E22" s="286"/>
-      <c r="F22" s="283"/>
-      <c r="G22" s="283"/>
-      <c r="H22" s="283"/>
-      <c r="I22" s="283"/>
-      <c r="J22" s="283"/>
-      <c r="K22" s="283"/>
-      <c r="L22" s="285"/>
+      <c r="A22" s="242"/>
+      <c r="B22" s="242"/>
+      <c r="C22" s="242"/>
+      <c r="D22" s="242"/>
+      <c r="E22" s="242"/>
+      <c r="F22" s="239"/>
+      <c r="G22" s="239"/>
+      <c r="H22" s="239"/>
+      <c r="I22" s="239"/>
+      <c r="J22" s="239"/>
+      <c r="K22" s="239"/>
+      <c r="L22" s="241"/>
       <c r="M22" s="127" t="s">
         <v>18</v>
       </c>
@@ -52656,18 +53203,18 @@
       </c>
     </row>
     <row r="23" spans="1:14" s="2" customFormat="1" ht="54">
-      <c r="A23" s="286"/>
-      <c r="B23" s="286"/>
-      <c r="C23" s="286"/>
-      <c r="D23" s="286"/>
-      <c r="E23" s="286"/>
-      <c r="F23" s="283"/>
-      <c r="G23" s="283"/>
-      <c r="H23" s="283"/>
-      <c r="I23" s="283"/>
-      <c r="J23" s="283"/>
-      <c r="K23" s="283"/>
-      <c r="L23" s="285"/>
+      <c r="A23" s="242"/>
+      <c r="B23" s="242"/>
+      <c r="C23" s="242"/>
+      <c r="D23" s="242"/>
+      <c r="E23" s="242"/>
+      <c r="F23" s="239"/>
+      <c r="G23" s="239"/>
+      <c r="H23" s="239"/>
+      <c r="I23" s="239"/>
+      <c r="J23" s="239"/>
+      <c r="K23" s="239"/>
+      <c r="L23" s="241"/>
       <c r="M23" s="139" t="s">
         <v>19</v>
       </c>
@@ -52677,18 +53224,18 @@
       </c>
     </row>
     <row r="24" spans="1:14" s="2" customFormat="1" ht="54">
-      <c r="A24" s="286"/>
-      <c r="B24" s="286"/>
-      <c r="C24" s="286"/>
-      <c r="D24" s="286"/>
-      <c r="E24" s="286"/>
-      <c r="F24" s="283"/>
-      <c r="G24" s="283"/>
-      <c r="H24" s="283"/>
-      <c r="I24" s="283"/>
-      <c r="J24" s="283"/>
-      <c r="K24" s="283"/>
-      <c r="L24" s="285"/>
+      <c r="A24" s="242"/>
+      <c r="B24" s="242"/>
+      <c r="C24" s="242"/>
+      <c r="D24" s="242"/>
+      <c r="E24" s="242"/>
+      <c r="F24" s="239"/>
+      <c r="G24" s="239"/>
+      <c r="H24" s="239"/>
+      <c r="I24" s="239"/>
+      <c r="J24" s="239"/>
+      <c r="K24" s="239"/>
+      <c r="L24" s="241"/>
       <c r="M24" s="15" t="s">
         <v>20</v>
       </c>
@@ -52714,162 +53261,162 @@
       <c r="N25" s="151"/>
     </row>
     <row r="26" spans="1:14" s="2" customFormat="1" ht="39">
-      <c r="A26" s="282" t="s">
+      <c r="A26" s="237" t="s">
         <v>327</v>
       </c>
-      <c r="B26" s="282"/>
-      <c r="C26" s="282"/>
-      <c r="D26" s="282"/>
-      <c r="E26" s="282"/>
-      <c r="F26" s="282"/>
-      <c r="G26" s="282"/>
-      <c r="H26" s="282"/>
-      <c r="I26" s="282"/>
-      <c r="J26" s="282"/>
-      <c r="K26" s="282"/>
-      <c r="L26" s="282"/>
-      <c r="M26" s="282"/>
-      <c r="N26" s="282"/>
+      <c r="B26" s="237"/>
+      <c r="C26" s="237"/>
+      <c r="D26" s="237"/>
+      <c r="E26" s="237"/>
+      <c r="F26" s="237"/>
+      <c r="G26" s="237"/>
+      <c r="H26" s="237"/>
+      <c r="I26" s="237"/>
+      <c r="J26" s="237"/>
+      <c r="K26" s="237"/>
+      <c r="L26" s="237"/>
+      <c r="M26" s="237"/>
+      <c r="N26" s="237"/>
     </row>
     <row r="27" spans="1:14" s="2" customFormat="1" ht="37.5">
-      <c r="A27" s="263" t="s">
+      <c r="A27" s="245" t="s">
         <v>470</v>
       </c>
-      <c r="B27" s="263"/>
-      <c r="C27" s="263"/>
-      <c r="D27" s="263"/>
-      <c r="E27" s="263"/>
-      <c r="F27" s="263"/>
-      <c r="G27" s="263"/>
-      <c r="H27" s="263"/>
-      <c r="I27" s="263"/>
-      <c r="J27" s="263"/>
-      <c r="K27" s="263"/>
-      <c r="L27" s="263"/>
-      <c r="M27" s="263"/>
-      <c r="N27" s="263"/>
+      <c r="B27" s="245"/>
+      <c r="C27" s="245"/>
+      <c r="D27" s="245"/>
+      <c r="E27" s="245"/>
+      <c r="F27" s="245"/>
+      <c r="G27" s="245"/>
+      <c r="H27" s="245"/>
+      <c r="I27" s="245"/>
+      <c r="J27" s="245"/>
+      <c r="K27" s="245"/>
+      <c r="L27" s="245"/>
+      <c r="M27" s="245"/>
+      <c r="N27" s="245"/>
     </row>
     <row r="28" spans="1:14" s="2" customFormat="1" ht="39">
-      <c r="A28" s="279" t="s">
+      <c r="A28" s="261" t="s">
         <v>853</v>
       </c>
-      <c r="B28" s="279"/>
-      <c r="C28" s="279"/>
-      <c r="D28" s="279"/>
-      <c r="E28" s="279"/>
-      <c r="F28" s="279"/>
-      <c r="G28" s="279"/>
-      <c r="H28" s="279"/>
-      <c r="I28" s="279"/>
-      <c r="J28" s="279"/>
-      <c r="K28" s="279"/>
-      <c r="L28" s="279"/>
-      <c r="M28" s="279"/>
-      <c r="N28" s="279"/>
+      <c r="B28" s="261"/>
+      <c r="C28" s="261"/>
+      <c r="D28" s="261"/>
+      <c r="E28" s="261"/>
+      <c r="F28" s="261"/>
+      <c r="G28" s="261"/>
+      <c r="H28" s="261"/>
+      <c r="I28" s="261"/>
+      <c r="J28" s="261"/>
+      <c r="K28" s="261"/>
+      <c r="L28" s="261"/>
+      <c r="M28" s="261"/>
+      <c r="N28" s="261"/>
     </row>
     <row r="29" spans="1:14" s="2" customFormat="1" ht="37.5">
-      <c r="A29" s="263" t="s">
+      <c r="A29" s="245" t="s">
         <v>854</v>
       </c>
-      <c r="B29" s="263"/>
-      <c r="C29" s="263"/>
-      <c r="D29" s="263"/>
-      <c r="E29" s="263"/>
-      <c r="F29" s="263"/>
-      <c r="G29" s="263"/>
-      <c r="H29" s="263"/>
-      <c r="I29" s="263"/>
-      <c r="J29" s="263"/>
-      <c r="K29" s="263"/>
-      <c r="L29" s="263"/>
-      <c r="M29" s="263"/>
-      <c r="N29" s="263"/>
+      <c r="B29" s="245"/>
+      <c r="C29" s="245"/>
+      <c r="D29" s="245"/>
+      <c r="E29" s="245"/>
+      <c r="F29" s="245"/>
+      <c r="G29" s="245"/>
+      <c r="H29" s="245"/>
+      <c r="I29" s="245"/>
+      <c r="J29" s="245"/>
+      <c r="K29" s="245"/>
+      <c r="L29" s="245"/>
+      <c r="M29" s="245"/>
+      <c r="N29" s="245"/>
     </row>
     <row r="30" spans="1:14" s="2" customFormat="1" ht="40.15" customHeight="1">
-      <c r="A30" s="264" t="s">
+      <c r="A30" s="246" t="s">
         <v>21</v>
       </c>
-      <c r="B30" s="265"/>
-      <c r="C30" s="270"/>
-      <c r="D30" s="271"/>
-      <c r="E30" s="272"/>
+      <c r="B30" s="247"/>
+      <c r="C30" s="252"/>
+      <c r="D30" s="253"/>
+      <c r="E30" s="254"/>
       <c r="F30" s="178"/>
       <c r="G30" s="16"/>
-      <c r="H30" s="280" t="s">
+      <c r="H30" s="262" t="s">
         <v>471</v>
       </c>
-      <c r="I30" s="280"/>
-      <c r="J30" s="281"/>
-      <c r="K30" s="261" t="s">
+      <c r="I30" s="262"/>
+      <c r="J30" s="263"/>
+      <c r="K30" s="243" t="s">
         <v>22</v>
       </c>
-      <c r="L30" s="262"/>
-      <c r="M30" s="262"/>
-      <c r="N30" s="262"/>
+      <c r="L30" s="244"/>
+      <c r="M30" s="244"/>
+      <c r="N30" s="244"/>
     </row>
     <row r="31" spans="1:14" s="2" customFormat="1" ht="40.15" customHeight="1">
-      <c r="A31" s="266"/>
-      <c r="B31" s="267"/>
-      <c r="C31" s="273"/>
-      <c r="D31" s="274"/>
-      <c r="E31" s="275"/>
+      <c r="A31" s="248"/>
+      <c r="B31" s="249"/>
+      <c r="C31" s="255"/>
+      <c r="D31" s="256"/>
+      <c r="E31" s="257"/>
       <c r="F31" s="27"/>
       <c r="G31" s="27"/>
       <c r="H31" s="16"/>
       <c r="I31" s="16"/>
       <c r="J31" s="179"/>
-      <c r="K31" s="261"/>
-      <c r="L31" s="262"/>
-      <c r="M31" s="262"/>
-      <c r="N31" s="262"/>
+      <c r="K31" s="243"/>
+      <c r="L31" s="244"/>
+      <c r="M31" s="244"/>
+      <c r="N31" s="244"/>
     </row>
     <row r="32" spans="1:14" s="2" customFormat="1" ht="40.15" customHeight="1">
-      <c r="A32" s="266"/>
-      <c r="B32" s="267"/>
-      <c r="C32" s="273"/>
-      <c r="D32" s="274"/>
-      <c r="E32" s="275"/>
+      <c r="A32" s="248"/>
+      <c r="B32" s="249"/>
+      <c r="C32" s="255"/>
+      <c r="D32" s="256"/>
+      <c r="E32" s="257"/>
       <c r="F32" s="27"/>
       <c r="G32" s="27"/>
       <c r="H32" s="27"/>
       <c r="I32" s="16"/>
       <c r="J32" s="16"/>
-      <c r="K32" s="261"/>
-      <c r="L32" s="262"/>
-      <c r="M32" s="262"/>
-      <c r="N32" s="262"/>
+      <c r="K32" s="243"/>
+      <c r="L32" s="244"/>
+      <c r="M32" s="244"/>
+      <c r="N32" s="244"/>
     </row>
     <row r="33" spans="1:22" s="2" customFormat="1" ht="40.15" customHeight="1">
-      <c r="A33" s="266"/>
-      <c r="B33" s="267"/>
-      <c r="C33" s="273"/>
-      <c r="D33" s="274"/>
-      <c r="E33" s="275"/>
+      <c r="A33" s="248"/>
+      <c r="B33" s="249"/>
+      <c r="C33" s="255"/>
+      <c r="D33" s="256"/>
+      <c r="E33" s="257"/>
       <c r="F33" s="27"/>
       <c r="G33" s="27"/>
       <c r="H33" s="27"/>
       <c r="I33" s="16"/>
       <c r="J33" s="16"/>
-      <c r="K33" s="261"/>
-      <c r="L33" s="262"/>
-      <c r="M33" s="262"/>
-      <c r="N33" s="262"/>
+      <c r="K33" s="243"/>
+      <c r="L33" s="244"/>
+      <c r="M33" s="244"/>
+      <c r="N33" s="244"/>
     </row>
     <row r="34" spans="1:22" s="2" customFormat="1" ht="40.15" customHeight="1">
-      <c r="A34" s="268"/>
-      <c r="B34" s="269"/>
-      <c r="C34" s="276"/>
-      <c r="D34" s="277"/>
-      <c r="E34" s="278"/>
+      <c r="A34" s="250"/>
+      <c r="B34" s="251"/>
+      <c r="C34" s="258"/>
+      <c r="D34" s="259"/>
+      <c r="E34" s="260"/>
       <c r="F34" s="27"/>
       <c r="G34" s="27"/>
       <c r="H34" s="27"/>
       <c r="I34" s="16"/>
       <c r="J34" s="16"/>
-      <c r="K34" s="261"/>
-      <c r="L34" s="262"/>
-      <c r="M34" s="262"/>
-      <c r="N34" s="262"/>
+      <c r="K34" s="243"/>
+      <c r="L34" s="244"/>
+      <c r="M34" s="244"/>
+      <c r="N34" s="244"/>
     </row>
     <row r="35" spans="1:22" s="2" customFormat="1" ht="31.5">
       <c r="A35" s="3"/>
@@ -52958,12 +53505,14 @@
     <row r="68" ht="23.25" customHeight="1"/>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="A29:N29"/>
-    <mergeCell ref="A30:B34"/>
-    <mergeCell ref="C30:E34"/>
-    <mergeCell ref="K30:K34"/>
-    <mergeCell ref="L30:N34"/>
-    <mergeCell ref="H30:J30"/>
+    <mergeCell ref="C1:K1"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="E2:H2"/>
+    <mergeCell ref="I2:K3"/>
+    <mergeCell ref="L2:M3"/>
+    <mergeCell ref="N2:N3"/>
+    <mergeCell ref="B3:H3"/>
     <mergeCell ref="A28:N28"/>
     <mergeCell ref="B4:H4"/>
     <mergeCell ref="I4:K4"/>
@@ -52978,14 +53527,12 @@
     <mergeCell ref="L21:L24"/>
     <mergeCell ref="A26:N26"/>
     <mergeCell ref="A27:N27"/>
-    <mergeCell ref="C1:K1"/>
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="E2:H2"/>
-    <mergeCell ref="I2:K3"/>
-    <mergeCell ref="L2:M3"/>
-    <mergeCell ref="N2:N3"/>
-    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="A29:N29"/>
+    <mergeCell ref="A30:B34"/>
+    <mergeCell ref="C30:E34"/>
+    <mergeCell ref="K30:K34"/>
+    <mergeCell ref="L30:N34"/>
+    <mergeCell ref="H30:J30"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="L6:L15">
